--- a/backend/catalogues_src/Grade 11 Technical Science Catalogue.xlsx
+++ b/backend/catalogues_src/Grade 11 Technical Science Catalogue.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -190,8 +190,14 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -382,6 +388,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -977,7 +989,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -1173,6 +1185,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="17" fontId="21" fillId="33" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="21" fillId="33" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="17" fontId="21" fillId="33" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1558,16 +1576,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L160"/>
+  <dimension ref="B2:L160"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="8.12844036697248" customWidth="1" style="25" min="1" max="1"/>
     <col width="15.6238532110092" customWidth="1" style="25" min="2" max="3"/>
     <col width="30.6238532110092" customWidth="1" style="25" min="4" max="32"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="13" customWidth="1" style="24" min="6" max="6"/>
+    <col width="13" customWidth="1" style="24" min="7" max="7"/>
     <col width="9" customWidth="1" style="25" min="33" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="66" t="inlineStr">
         <is>
@@ -1597,17 +1617,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="G3" s="33" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -1622,9 +1642,9 @@
       <c r="B4" s="69" t="n"/>
       <c r="C4" s="70" t="n"/>
       <c r="D4" s="71" t="n"/>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="70" t="n"/>
-      <c r="G4" s="70" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
+      <c r="G4" s="71" t="n"/>
       <c r="H4" s="35" t="n"/>
       <c r="I4" s="35" t="n"/>
       <c r="J4" s="35" t="n"/>
@@ -1639,9 +1659,9 @@
       </c>
       <c r="C5" s="39" t="n"/>
       <c r="D5" s="40" t="n"/>
-      <c r="E5" s="41" t="n"/>
+      <c r="E5" s="40" t="n"/>
       <c r="F5" s="40" t="n"/>
-      <c r="G5" s="42" t="n"/>
+      <c r="G5" s="40" t="n"/>
       <c r="H5" s="35" t="n"/>
       <c r="I5" s="35" t="n"/>
       <c r="J5" s="35" t="n"/>
@@ -1655,10 +1675,10 @@
         </is>
       </c>
       <c r="C6" s="44" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="46" t="n"/>
-      <c r="F6" s="45" t="n"/>
-      <c r="G6" s="47" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="40" t="n"/>
+      <c r="G6" s="40" t="n"/>
       <c r="H6" s="35" t="n"/>
       <c r="I6" s="35" t="n"/>
       <c r="J6" s="35" t="n"/>
@@ -1673,9 +1693,9 @@
       </c>
       <c r="C7" s="39" t="n"/>
       <c r="D7" s="40" t="n"/>
-      <c r="E7" s="41" t="n"/>
+      <c r="E7" s="40" t="n"/>
       <c r="F7" s="40" t="n"/>
-      <c r="G7" s="42" t="n"/>
+      <c r="G7" s="40" t="n"/>
       <c r="H7" s="35" t="n"/>
       <c r="I7" s="35" t="n"/>
       <c r="J7" s="35" t="n"/>
@@ -1690,9 +1710,9 @@
       </c>
       <c r="C8" s="39" t="n"/>
       <c r="D8" s="40" t="n"/>
-      <c r="E8" s="41" t="n"/>
+      <c r="E8" s="40" t="n"/>
       <c r="F8" s="40" t="n"/>
-      <c r="G8" s="42" t="n"/>
+      <c r="G8" s="40" t="n"/>
       <c r="H8" s="35" t="n"/>
       <c r="I8" s="35" t="n"/>
       <c r="J8" s="35" t="n"/>
@@ -1707,9 +1727,9 @@
       </c>
       <c r="C9" s="39" t="n"/>
       <c r="D9" s="40" t="n"/>
-      <c r="E9" s="41" t="n"/>
+      <c r="E9" s="40" t="n"/>
       <c r="F9" s="40" t="n"/>
-      <c r="G9" s="42" t="n"/>
+      <c r="G9" s="40" t="n"/>
       <c r="H9" s="35" t="n"/>
       <c r="I9" s="35" t="n"/>
       <c r="J9" s="35" t="n"/>
@@ -1724,9 +1744,9 @@
       </c>
       <c r="C10" s="39" t="n"/>
       <c r="D10" s="40" t="n"/>
-      <c r="E10" s="41" t="n"/>
+      <c r="E10" s="40" t="n"/>
       <c r="F10" s="40" t="n"/>
-      <c r="G10" s="42" t="n"/>
+      <c r="G10" s="40" t="n"/>
       <c r="H10" s="35" t="n"/>
       <c r="I10" s="35" t="n"/>
       <c r="J10" s="35" t="n"/>
@@ -1741,9 +1761,9 @@
       </c>
       <c r="C11" s="39" t="n"/>
       <c r="D11" s="40" t="n"/>
-      <c r="E11" s="48" t="n"/>
-      <c r="F11" s="49" t="n"/>
-      <c r="G11" s="50" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="40" t="n"/>
       <c r="H11" s="35" t="n"/>
       <c r="I11" s="35" t="n"/>
       <c r="J11" s="35" t="n"/>
@@ -1758,9 +1778,9 @@
       </c>
       <c r="C12" s="39" t="n"/>
       <c r="D12" s="40" t="n"/>
-      <c r="E12" s="41" t="n"/>
+      <c r="E12" s="40" t="n"/>
       <c r="F12" s="40" t="n"/>
-      <c r="G12" s="42" t="n"/>
+      <c r="G12" s="40" t="n"/>
       <c r="H12" s="35" t="n"/>
       <c r="I12" s="35" t="n"/>
       <c r="J12" s="35" t="n"/>
@@ -1775,9 +1795,9 @@
       </c>
       <c r="C13" s="39" t="n"/>
       <c r="D13" s="40" t="n"/>
-      <c r="E13" s="41" t="n"/>
+      <c r="E13" s="40" t="n"/>
       <c r="F13" s="40" t="n"/>
-      <c r="G13" s="42" t="n"/>
+      <c r="G13" s="40" t="n"/>
       <c r="H13" s="35" t="n"/>
       <c r="I13" s="35" t="n"/>
       <c r="J13" s="35" t="n"/>
@@ -1792,9 +1812,9 @@
       </c>
       <c r="C14" s="39" t="n"/>
       <c r="D14" s="40" t="n"/>
-      <c r="E14" s="41" t="n"/>
+      <c r="E14" s="40" t="n"/>
       <c r="F14" s="40" t="n"/>
-      <c r="G14" s="42" t="n"/>
+      <c r="G14" s="40" t="n"/>
       <c r="H14" s="35" t="n"/>
       <c r="I14" s="35" t="n"/>
       <c r="J14" s="35" t="n"/>
@@ -1809,9 +1829,9 @@
       </c>
       <c r="C15" s="39" t="n"/>
       <c r="D15" s="40" t="n"/>
-      <c r="E15" s="41" t="n"/>
+      <c r="E15" s="40" t="n"/>
       <c r="F15" s="40" t="n"/>
-      <c r="G15" s="42" t="n"/>
+      <c r="G15" s="40" t="n"/>
       <c r="H15" s="35" t="n"/>
       <c r="I15" s="35" t="n"/>
       <c r="J15" s="35" t="n"/>
@@ -1826,9 +1846,9 @@
       </c>
       <c r="C16" s="39" t="n"/>
       <c r="D16" s="40" t="n"/>
-      <c r="E16" s="41" t="n"/>
+      <c r="E16" s="40" t="n"/>
       <c r="F16" s="40" t="n"/>
-      <c r="G16" s="42" t="n"/>
+      <c r="G16" s="40" t="n"/>
       <c r="H16" s="35" t="n"/>
       <c r="I16" s="35" t="n"/>
       <c r="J16" s="35" t="n"/>
@@ -1843,9 +1863,9 @@
       </c>
       <c r="C17" s="39" t="n"/>
       <c r="D17" s="40" t="n"/>
-      <c r="E17" s="41" t="n"/>
+      <c r="E17" s="40" t="n"/>
       <c r="F17" s="40" t="n"/>
-      <c r="G17" s="42" t="n"/>
+      <c r="G17" s="40" t="n"/>
       <c r="H17" s="35" t="n"/>
       <c r="I17" s="35" t="n"/>
       <c r="J17" s="35" t="n"/>
@@ -1860,9 +1880,9 @@
       </c>
       <c r="C18" s="39" t="n"/>
       <c r="D18" s="40" t="n"/>
-      <c r="E18" s="41" t="n"/>
+      <c r="E18" s="40" t="n"/>
       <c r="F18" s="40" t="n"/>
-      <c r="G18" s="42" t="n"/>
+      <c r="G18" s="40" t="n"/>
       <c r="H18" s="35" t="n"/>
       <c r="I18" s="35" t="n"/>
       <c r="J18" s="35" t="n"/>
@@ -1877,9 +1897,9 @@
       </c>
       <c r="C19" s="39" t="n"/>
       <c r="D19" s="40" t="n"/>
-      <c r="E19" s="41" t="n"/>
+      <c r="E19" s="40" t="n"/>
       <c r="F19" s="40" t="n"/>
-      <c r="G19" s="42" t="n"/>
+      <c r="G19" s="40" t="n"/>
       <c r="H19" s="35" t="n"/>
       <c r="I19" s="35" t="n"/>
       <c r="J19" s="35" t="n"/>
@@ -1893,10 +1913,10 @@
         </is>
       </c>
       <c r="C20" s="52" t="n"/>
-      <c r="D20" s="53" t="n"/>
-      <c r="E20" s="54" t="n"/>
-      <c r="F20" s="53" t="n"/>
-      <c r="G20" s="55" t="n"/>
+      <c r="D20" s="40" t="n"/>
+      <c r="E20" s="40" t="n"/>
+      <c r="F20" s="40" t="n"/>
+      <c r="G20" s="40" t="n"/>
       <c r="H20" s="35" t="n"/>
       <c r="I20" s="35" t="n"/>
       <c r="J20" s="35" t="n"/>
@@ -1945,7 +1965,7 @@
       </c>
       <c r="E23" s="33" t="inlineStr">
         <is>
-          <t>Redox  Reactions</t>
+          <t>Redox Reactions</t>
         </is>
       </c>
       <c r="F23" s="33" t="inlineStr">
@@ -1953,7 +1973,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="G23" s="33" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -1968,7 +1988,7 @@
       <c r="D24" s="71" t="n"/>
       <c r="E24" s="71" t="n"/>
       <c r="F24" s="71" t="n"/>
-      <c r="G24" s="70" t="n"/>
+      <c r="G24" s="71" t="n"/>
       <c r="H24" s="35" t="n"/>
       <c r="I24" s="61" t="n"/>
       <c r="J24" s="60" t="n"/>
@@ -1981,9 +2001,9 @@
       </c>
       <c r="C25" s="39" t="n"/>
       <c r="D25" s="40" t="n"/>
-      <c r="E25" s="41" t="n"/>
+      <c r="E25" s="40" t="n"/>
       <c r="F25" s="40" t="n"/>
-      <c r="G25" s="58" t="n"/>
+      <c r="G25" s="40" t="n"/>
       <c r="H25" s="35" t="n"/>
       <c r="I25" s="61" t="n"/>
       <c r="J25" s="60" t="n"/>
@@ -1995,10 +2015,10 @@
         </is>
       </c>
       <c r="C26" s="44" t="n"/>
-      <c r="D26" s="45" t="n"/>
-      <c r="E26" s="46" t="n"/>
-      <c r="F26" s="45" t="n"/>
-      <c r="G26" s="45" t="n"/>
+      <c r="D26" s="40" t="n"/>
+      <c r="E26" s="40" t="n"/>
+      <c r="F26" s="40" t="n"/>
+      <c r="G26" s="40" t="n"/>
       <c r="H26" s="35" t="n"/>
       <c r="I26" s="61" t="n"/>
       <c r="J26" s="60" t="n"/>
@@ -2011,7 +2031,7 @@
       </c>
       <c r="C27" s="39" t="n"/>
       <c r="D27" s="40" t="n"/>
-      <c r="E27" s="41" t="n"/>
+      <c r="E27" s="40" t="n"/>
       <c r="F27" s="40" t="n"/>
       <c r="G27" s="40" t="n"/>
       <c r="H27" s="35" t="n"/>
@@ -2026,7 +2046,7 @@
       </c>
       <c r="C28" s="39" t="n"/>
       <c r="D28" s="40" t="n"/>
-      <c r="E28" s="41" t="n"/>
+      <c r="E28" s="40" t="n"/>
       <c r="F28" s="40" t="n"/>
       <c r="G28" s="40" t="n"/>
       <c r="H28" s="35" t="n"/>
@@ -2041,7 +2061,7 @@
       </c>
       <c r="C29" s="39" t="n"/>
       <c r="D29" s="40" t="n"/>
-      <c r="E29" s="41" t="n"/>
+      <c r="E29" s="40" t="n"/>
       <c r="F29" s="40" t="n"/>
       <c r="G29" s="40" t="n"/>
       <c r="H29" s="35" t="n"/>
@@ -2056,7 +2076,7 @@
       </c>
       <c r="C30" s="39" t="n"/>
       <c r="D30" s="40" t="n"/>
-      <c r="E30" s="41" t="n"/>
+      <c r="E30" s="40" t="n"/>
       <c r="F30" s="40" t="n"/>
       <c r="G30" s="40" t="n"/>
       <c r="H30" s="35" t="n"/>
@@ -2070,10 +2090,10 @@
         </is>
       </c>
       <c r="C31" s="39" t="n"/>
-      <c r="D31" s="49" t="n"/>
-      <c r="E31" s="48" t="n"/>
-      <c r="F31" s="49" t="n"/>
-      <c r="G31" s="49" t="n"/>
+      <c r="D31" s="40" t="n"/>
+      <c r="E31" s="40" t="n"/>
+      <c r="F31" s="40" t="n"/>
+      <c r="G31" s="40" t="n"/>
       <c r="H31" s="35" t="n"/>
       <c r="I31" s="61" t="n"/>
       <c r="J31" s="60" t="n"/>
@@ -2086,7 +2106,7 @@
       </c>
       <c r="C32" s="39" t="n"/>
       <c r="D32" s="40" t="n"/>
-      <c r="E32" s="41" t="n"/>
+      <c r="E32" s="40" t="n"/>
       <c r="F32" s="40" t="n"/>
       <c r="G32" s="40" t="n"/>
       <c r="H32" s="35" t="n"/>
@@ -2101,7 +2121,7 @@
       </c>
       <c r="C33" s="39" t="n"/>
       <c r="D33" s="40" t="n"/>
-      <c r="E33" s="41" t="n"/>
+      <c r="E33" s="40" t="n"/>
       <c r="F33" s="40" t="n"/>
       <c r="G33" s="40" t="n"/>
       <c r="H33" s="35" t="n"/>
@@ -2116,7 +2136,7 @@
       </c>
       <c r="C34" s="39" t="n"/>
       <c r="D34" s="40" t="n"/>
-      <c r="E34" s="41" t="n"/>
+      <c r="E34" s="40" t="n"/>
       <c r="F34" s="40" t="n"/>
       <c r="G34" s="40" t="n"/>
       <c r="H34" s="35" t="n"/>
@@ -2131,7 +2151,7 @@
       </c>
       <c r="C35" s="39" t="n"/>
       <c r="D35" s="40" t="n"/>
-      <c r="E35" s="41" t="n"/>
+      <c r="E35" s="40" t="n"/>
       <c r="F35" s="40" t="n"/>
       <c r="G35" s="40" t="n"/>
       <c r="H35" s="35" t="n"/>
@@ -2146,7 +2166,7 @@
       </c>
       <c r="C36" s="39" t="n"/>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="41" t="n"/>
+      <c r="E36" s="40" t="n"/>
       <c r="F36" s="40" t="n"/>
       <c r="G36" s="40" t="n"/>
       <c r="H36" s="35" t="n"/>
@@ -2161,7 +2181,7 @@
       </c>
       <c r="C37" s="39" t="n"/>
       <c r="D37" s="40" t="n"/>
-      <c r="E37" s="41" t="n"/>
+      <c r="E37" s="40" t="n"/>
       <c r="F37" s="40" t="n"/>
       <c r="G37" s="40" t="n"/>
       <c r="H37" s="35" t="n"/>
@@ -2176,7 +2196,7 @@
       </c>
       <c r="C38" s="39" t="n"/>
       <c r="D38" s="40" t="n"/>
-      <c r="E38" s="41" t="n"/>
+      <c r="E38" s="40" t="n"/>
       <c r="F38" s="40" t="n"/>
       <c r="G38" s="40" t="n"/>
       <c r="H38" s="35" t="n"/>
@@ -2191,7 +2211,7 @@
       </c>
       <c r="C39" s="39" t="n"/>
       <c r="D39" s="40" t="n"/>
-      <c r="E39" s="41" t="n"/>
+      <c r="E39" s="40" t="n"/>
       <c r="F39" s="40" t="n"/>
       <c r="G39" s="40" t="n"/>
       <c r="H39" s="35" t="n"/>
@@ -2205,10 +2225,10 @@
         </is>
       </c>
       <c r="C40" s="52" t="n"/>
-      <c r="D40" s="53" t="n"/>
-      <c r="E40" s="54" t="n"/>
-      <c r="F40" s="53" t="n"/>
-      <c r="G40" s="53" t="n"/>
+      <c r="D40" s="40" t="n"/>
+      <c r="E40" s="40" t="n"/>
+      <c r="F40" s="40" t="n"/>
+      <c r="G40" s="40" t="n"/>
       <c r="H40" s="35" t="n"/>
       <c r="I40" s="61" t="n"/>
       <c r="J40" s="60" t="n"/>
@@ -2253,17 +2273,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="E43" s="15" t="inlineStr">
+      <c r="E43" s="33" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="F43" s="15" t="inlineStr">
+      <c r="F43" s="33" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="G43" s="15" t="inlineStr">
+      <c r="G43" s="33" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -2278,9 +2298,9 @@
       <c r="B44" s="69" t="n"/>
       <c r="C44" s="70" t="n"/>
       <c r="D44" s="71" t="n"/>
-      <c r="E44" s="70" t="n"/>
-      <c r="F44" s="70" t="n"/>
-      <c r="G44" s="70" t="n"/>
+      <c r="E44" s="71" t="n"/>
+      <c r="F44" s="71" t="n"/>
+      <c r="G44" s="71" t="n"/>
       <c r="H44" s="35" t="n"/>
       <c r="I44" s="35" t="n"/>
       <c r="J44" s="35" t="n"/>
@@ -2295,9 +2315,9 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="59" t="n"/>
+      <c r="E45" s="40" t="n"/>
       <c r="F45" s="40" t="n"/>
-      <c r="G45" s="42" t="n"/>
+      <c r="G45" s="40" t="n"/>
       <c r="H45" s="35" t="n"/>
       <c r="I45" s="35" t="n"/>
       <c r="J45" s="35" t="n"/>
@@ -2311,10 +2331,10 @@
         </is>
       </c>
       <c r="C46" s="44" t="n"/>
-      <c r="D46" s="45" t="n"/>
-      <c r="E46" s="46" t="n"/>
+      <c r="D46" s="40" t="n"/>
+      <c r="E46" s="40" t="n"/>
       <c r="F46" s="40" t="n"/>
-      <c r="G46" s="47" t="n"/>
+      <c r="G46" s="40" t="n"/>
       <c r="H46" s="35" t="n"/>
       <c r="I46" s="35" t="n"/>
       <c r="J46" s="35" t="n"/>
@@ -2329,9 +2349,9 @@
       </c>
       <c r="C47" s="39" t="n"/>
       <c r="D47" s="40" t="n"/>
-      <c r="E47" s="41" t="n"/>
+      <c r="E47" s="40" t="n"/>
       <c r="F47" s="40" t="n"/>
-      <c r="G47" s="42" t="n"/>
+      <c r="G47" s="40" t="n"/>
       <c r="H47" s="35" t="n"/>
       <c r="I47" s="35" t="n"/>
       <c r="J47" s="35" t="n"/>
@@ -2346,9 +2366,9 @@
       </c>
       <c r="C48" s="39" t="n"/>
       <c r="D48" s="40" t="n"/>
-      <c r="E48" s="41" t="n"/>
+      <c r="E48" s="40" t="n"/>
       <c r="F48" s="40" t="n"/>
-      <c r="G48" s="42" t="n"/>
+      <c r="G48" s="40" t="n"/>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="35" t="n"/>
       <c r="J48" s="35" t="n"/>
@@ -2363,9 +2383,9 @@
       </c>
       <c r="C49" s="39" t="n"/>
       <c r="D49" s="40" t="n"/>
-      <c r="E49" s="41" t="n"/>
+      <c r="E49" s="40" t="n"/>
       <c r="F49" s="40" t="n"/>
-      <c r="G49" s="42" t="n"/>
+      <c r="G49" s="40" t="n"/>
       <c r="H49" s="35" t="n"/>
       <c r="I49" s="35" t="n"/>
       <c r="J49" s="35" t="n"/>
@@ -2380,9 +2400,9 @@
       </c>
       <c r="C50" s="39" t="n"/>
       <c r="D50" s="40" t="n"/>
-      <c r="E50" s="41" t="n"/>
+      <c r="E50" s="40" t="n"/>
       <c r="F50" s="40" t="n"/>
-      <c r="G50" s="42" t="n"/>
+      <c r="G50" s="40" t="n"/>
       <c r="H50" s="35" t="n"/>
       <c r="I50" s="35" t="n"/>
       <c r="J50" s="35" t="n"/>
@@ -2397,9 +2417,9 @@
       </c>
       <c r="C51" s="39" t="n"/>
       <c r="D51" s="40" t="n"/>
-      <c r="E51" s="41" t="n"/>
-      <c r="F51" s="49" t="n"/>
-      <c r="G51" s="50" t="n"/>
+      <c r="E51" s="40" t="n"/>
+      <c r="F51" s="40" t="n"/>
+      <c r="G51" s="40" t="n"/>
       <c r="H51" s="35" t="n"/>
       <c r="I51" s="35" t="n"/>
       <c r="J51" s="35" t="n"/>
@@ -2414,9 +2434,9 @@
       </c>
       <c r="C52" s="39" t="n"/>
       <c r="D52" s="40" t="n"/>
-      <c r="E52" s="41" t="n"/>
+      <c r="E52" s="40" t="n"/>
       <c r="F52" s="40" t="n"/>
-      <c r="G52" s="42" t="n"/>
+      <c r="G52" s="40" t="n"/>
       <c r="H52" s="35" t="n"/>
       <c r="I52" s="35" t="n"/>
       <c r="J52" s="35" t="n"/>
@@ -2431,9 +2451,9 @@
       </c>
       <c r="C53" s="39" t="n"/>
       <c r="D53" s="40" t="n"/>
-      <c r="E53" s="41" t="n"/>
+      <c r="E53" s="40" t="n"/>
       <c r="F53" s="40" t="n"/>
-      <c r="G53" s="42" t="n"/>
+      <c r="G53" s="40" t="n"/>
       <c r="H53" s="35" t="n"/>
       <c r="I53" s="35" t="n"/>
       <c r="J53" s="35" t="n"/>
@@ -2448,9 +2468,9 @@
       </c>
       <c r="C54" s="39" t="n"/>
       <c r="D54" s="40" t="n"/>
-      <c r="E54" s="41" t="n"/>
+      <c r="E54" s="40" t="n"/>
       <c r="F54" s="40" t="n"/>
-      <c r="G54" s="42" t="n"/>
+      <c r="G54" s="40" t="n"/>
       <c r="H54" s="35" t="n"/>
       <c r="I54" s="35" t="n"/>
       <c r="J54" s="35" t="n"/>
@@ -2465,9 +2485,9 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="41" t="n"/>
+      <c r="E55" s="40" t="n"/>
       <c r="F55" s="40" t="n"/>
-      <c r="G55" s="42" t="n"/>
+      <c r="G55" s="40" t="n"/>
       <c r="H55" s="35" t="n"/>
       <c r="I55" s="35" t="n"/>
       <c r="J55" s="35" t="n"/>
@@ -2482,9 +2502,9 @@
       </c>
       <c r="C56" s="39" t="n"/>
       <c r="D56" s="40" t="n"/>
-      <c r="E56" s="41" t="n"/>
+      <c r="E56" s="40" t="n"/>
       <c r="F56" s="40" t="n"/>
-      <c r="G56" s="42" t="n"/>
+      <c r="G56" s="40" t="n"/>
       <c r="H56" s="35" t="n"/>
       <c r="I56" s="35" t="n"/>
       <c r="J56" s="35" t="n"/>
@@ -2499,9 +2519,9 @@
       </c>
       <c r="C57" s="39" t="n"/>
       <c r="D57" s="40" t="n"/>
-      <c r="E57" s="41" t="n"/>
+      <c r="E57" s="40" t="n"/>
       <c r="F57" s="40" t="n"/>
-      <c r="G57" s="42" t="n"/>
+      <c r="G57" s="40" t="n"/>
       <c r="H57" s="35" t="n"/>
       <c r="I57" s="35" t="n"/>
       <c r="J57" s="35" t="n"/>
@@ -2516,9 +2536,9 @@
       </c>
       <c r="C58" s="39" t="n"/>
       <c r="D58" s="40" t="n"/>
-      <c r="E58" s="41" t="n"/>
+      <c r="E58" s="40" t="n"/>
       <c r="F58" s="40" t="n"/>
-      <c r="G58" s="42" t="n"/>
+      <c r="G58" s="40" t="n"/>
       <c r="H58" s="35" t="n"/>
       <c r="I58" s="35" t="n"/>
       <c r="J58" s="35" t="n"/>
@@ -2533,9 +2553,9 @@
       </c>
       <c r="C59" s="39" t="n"/>
       <c r="D59" s="40" t="n"/>
-      <c r="E59" s="41" t="n"/>
+      <c r="E59" s="40" t="n"/>
       <c r="F59" s="40" t="n"/>
-      <c r="G59" s="42" t="n"/>
+      <c r="G59" s="40" t="n"/>
       <c r="H59" s="35" t="n"/>
       <c r="I59" s="35" t="n"/>
       <c r="J59" s="35" t="n"/>
@@ -2549,10 +2569,10 @@
         </is>
       </c>
       <c r="C60" s="52" t="n"/>
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="54" t="n"/>
-      <c r="F60" s="53" t="n"/>
-      <c r="G60" s="55" t="n"/>
+      <c r="D60" s="40" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
+      <c r="G60" s="40" t="n"/>
       <c r="H60" s="35" t="n"/>
       <c r="I60" s="35" t="n"/>
       <c r="J60" s="35" t="n"/>
@@ -2601,7 +2621,7 @@
       </c>
       <c r="E63" s="33" t="inlineStr">
         <is>
-          <t>Redox  Reactions</t>
+          <t>Redox Reactions</t>
         </is>
       </c>
       <c r="F63" s="33" t="inlineStr">
@@ -2609,7 +2629,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="G63" s="15" t="inlineStr">
+      <c r="G63" s="33" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -2624,7 +2644,7 @@
       <c r="D64" s="71" t="n"/>
       <c r="E64" s="71" t="n"/>
       <c r="F64" s="71" t="n"/>
-      <c r="G64" s="70" t="n"/>
+      <c r="G64" s="71" t="n"/>
       <c r="I64" s="60" t="n"/>
       <c r="J64" s="60" t="n"/>
     </row>
@@ -2636,9 +2656,9 @@
       </c>
       <c r="C65" s="39" t="n"/>
       <c r="D65" s="40" t="n"/>
-      <c r="E65" s="41" t="n"/>
+      <c r="E65" s="40" t="n"/>
       <c r="F65" s="40" t="n"/>
-      <c r="G65" s="58" t="n"/>
+      <c r="G65" s="40" t="n"/>
       <c r="H65" s="57" t="n"/>
       <c r="I65" s="60" t="n"/>
       <c r="J65" s="57" t="n"/>
@@ -2650,10 +2670,10 @@
         </is>
       </c>
       <c r="C66" s="44" t="n"/>
-      <c r="D66" s="45" t="n"/>
-      <c r="E66" s="46" t="n"/>
-      <c r="F66" s="45" t="n"/>
-      <c r="G66" s="45" t="n"/>
+      <c r="D66" s="40" t="n"/>
+      <c r="E66" s="40" t="n"/>
+      <c r="F66" s="40" t="n"/>
+      <c r="G66" s="40" t="n"/>
       <c r="H66" s="57" t="n"/>
       <c r="I66" s="60" t="n"/>
       <c r="J66" s="57" t="n"/>
@@ -2666,7 +2686,7 @@
       </c>
       <c r="C67" s="39" t="n"/>
       <c r="D67" s="40" t="n"/>
-      <c r="E67" s="41" t="n"/>
+      <c r="E67" s="40" t="n"/>
       <c r="F67" s="40" t="n"/>
       <c r="G67" s="40" t="n"/>
       <c r="H67" s="57" t="n"/>
@@ -2681,7 +2701,7 @@
       </c>
       <c r="C68" s="39" t="n"/>
       <c r="D68" s="40" t="n"/>
-      <c r="E68" s="41" t="n"/>
+      <c r="E68" s="40" t="n"/>
       <c r="F68" s="40" t="n"/>
       <c r="G68" s="40" t="n"/>
       <c r="H68" s="57" t="n"/>
@@ -2696,7 +2716,7 @@
       </c>
       <c r="C69" s="39" t="n"/>
       <c r="D69" s="40" t="n"/>
-      <c r="E69" s="41" t="n"/>
+      <c r="E69" s="40" t="n"/>
       <c r="F69" s="40" t="n"/>
       <c r="G69" s="40" t="n"/>
       <c r="H69" s="57" t="n"/>
@@ -2711,7 +2731,7 @@
       </c>
       <c r="C70" s="39" t="n"/>
       <c r="D70" s="40" t="n"/>
-      <c r="E70" s="41" t="n"/>
+      <c r="E70" s="40" t="n"/>
       <c r="F70" s="40" t="n"/>
       <c r="G70" s="40" t="n"/>
       <c r="H70" s="57" t="n"/>
@@ -2725,10 +2745,10 @@
         </is>
       </c>
       <c r="C71" s="39" t="n"/>
-      <c r="D71" s="49" t="n"/>
-      <c r="E71" s="48" t="n"/>
-      <c r="F71" s="49" t="n"/>
-      <c r="G71" s="49" t="n"/>
+      <c r="D71" s="40" t="n"/>
+      <c r="E71" s="40" t="n"/>
+      <c r="F71" s="40" t="n"/>
+      <c r="G71" s="40" t="n"/>
       <c r="H71" s="57" t="n"/>
       <c r="I71" s="60" t="n"/>
       <c r="J71" s="57" t="n"/>
@@ -2741,7 +2761,7 @@
       </c>
       <c r="C72" s="39" t="n"/>
       <c r="D72" s="40" t="n"/>
-      <c r="E72" s="41" t="n"/>
+      <c r="E72" s="40" t="n"/>
       <c r="F72" s="40" t="n"/>
       <c r="G72" s="40" t="n"/>
       <c r="H72" s="57" t="n"/>
@@ -2756,7 +2776,7 @@
       </c>
       <c r="C73" s="39" t="n"/>
       <c r="D73" s="40" t="n"/>
-      <c r="E73" s="41" t="n"/>
+      <c r="E73" s="40" t="n"/>
       <c r="F73" s="40" t="n"/>
       <c r="G73" s="40" t="n"/>
       <c r="H73" s="57" t="n"/>
@@ -2771,7 +2791,7 @@
       </c>
       <c r="C74" s="39" t="n"/>
       <c r="D74" s="40" t="n"/>
-      <c r="E74" s="41" t="n"/>
+      <c r="E74" s="40" t="n"/>
       <c r="F74" s="40" t="n"/>
       <c r="G74" s="40" t="n"/>
       <c r="H74" s="57" t="n"/>
@@ -2786,7 +2806,7 @@
       </c>
       <c r="C75" s="39" t="n"/>
       <c r="D75" s="40" t="n"/>
-      <c r="E75" s="41" t="n"/>
+      <c r="E75" s="40" t="n"/>
       <c r="F75" s="40" t="n"/>
       <c r="G75" s="40" t="n"/>
       <c r="H75" s="57" t="n"/>
@@ -2801,7 +2821,7 @@
       </c>
       <c r="C76" s="39" t="n"/>
       <c r="D76" s="40" t="n"/>
-      <c r="E76" s="41" t="n"/>
+      <c r="E76" s="40" t="n"/>
       <c r="F76" s="40" t="n"/>
       <c r="G76" s="40" t="n"/>
       <c r="H76" s="57" t="n"/>
@@ -2816,7 +2836,7 @@
       </c>
       <c r="C77" s="39" t="n"/>
       <c r="D77" s="40" t="n"/>
-      <c r="E77" s="41" t="n"/>
+      <c r="E77" s="40" t="n"/>
       <c r="F77" s="40" t="n"/>
       <c r="G77" s="40" t="n"/>
       <c r="H77" s="57" t="n"/>
@@ -2831,7 +2851,7 @@
       </c>
       <c r="C78" s="39" t="n"/>
       <c r="D78" s="40" t="n"/>
-      <c r="E78" s="41" t="n"/>
+      <c r="E78" s="40" t="n"/>
       <c r="F78" s="40" t="n"/>
       <c r="G78" s="40" t="n"/>
       <c r="H78" s="57" t="n"/>
@@ -2846,7 +2866,7 @@
       </c>
       <c r="C79" s="39" t="n"/>
       <c r="D79" s="40" t="n"/>
-      <c r="E79" s="41" t="n"/>
+      <c r="E79" s="40" t="n"/>
       <c r="F79" s="40" t="n"/>
       <c r="G79" s="40" t="n"/>
       <c r="H79" s="57" t="n"/>
@@ -2860,10 +2880,10 @@
         </is>
       </c>
       <c r="C80" s="52" t="n"/>
-      <c r="D80" s="53" t="n"/>
-      <c r="E80" s="54" t="n"/>
-      <c r="F80" s="53" t="n"/>
-      <c r="G80" s="53" t="n"/>
+      <c r="D80" s="40" t="n"/>
+      <c r="E80" s="40" t="n"/>
+      <c r="F80" s="40" t="n"/>
+      <c r="G80" s="40" t="n"/>
       <c r="H80" s="57" t="n"/>
       <c r="I80" s="60" t="n"/>
       <c r="J80" s="57" t="n"/>
@@ -2908,17 +2928,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="E83" s="15" t="inlineStr">
+      <c r="E83" s="33" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="F83" s="15" t="inlineStr">
+      <c r="F83" s="33" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="G83" s="15" t="inlineStr">
+      <c r="G83" s="33" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -2933,9 +2953,9 @@
       <c r="B84" s="69" t="n"/>
       <c r="C84" s="70" t="n"/>
       <c r="D84" s="71" t="n"/>
-      <c r="E84" s="70" t="n"/>
-      <c r="F84" s="70" t="n"/>
-      <c r="G84" s="70" t="n"/>
+      <c r="E84" s="71" t="n"/>
+      <c r="F84" s="71" t="n"/>
+      <c r="G84" s="71" t="n"/>
       <c r="H84" s="35" t="n"/>
       <c r="I84" s="35" t="n"/>
       <c r="J84" s="35" t="n"/>
@@ -2950,8 +2970,8 @@
       </c>
       <c r="C85" s="39" t="n"/>
       <c r="D85" s="40" t="n"/>
-      <c r="E85" s="58" t="n"/>
-      <c r="F85" s="41" t="n"/>
+      <c r="E85" s="40" t="n"/>
+      <c r="F85" s="40" t="n"/>
       <c r="G85" s="40" t="n"/>
       <c r="H85" s="35" t="n"/>
       <c r="I85" s="35" t="n"/>
@@ -2966,10 +2986,10 @@
         </is>
       </c>
       <c r="C86" s="44" t="n"/>
-      <c r="D86" s="45" t="n"/>
-      <c r="E86" s="45" t="n"/>
-      <c r="F86" s="41" t="n"/>
-      <c r="G86" s="45" t="n"/>
+      <c r="D86" s="40" t="n"/>
+      <c r="E86" s="40" t="n"/>
+      <c r="F86" s="40" t="n"/>
+      <c r="G86" s="40" t="n"/>
       <c r="H86" s="35" t="n"/>
       <c r="I86" s="35" t="n"/>
       <c r="J86" s="35" t="n"/>
@@ -2985,7 +3005,7 @@
       <c r="C87" s="39" t="n"/>
       <c r="D87" s="40" t="n"/>
       <c r="E87" s="40" t="n"/>
-      <c r="F87" s="41" t="n"/>
+      <c r="F87" s="40" t="n"/>
       <c r="G87" s="40" t="n"/>
       <c r="H87" s="35" t="n"/>
       <c r="I87" s="35" t="n"/>
@@ -3002,7 +3022,7 @@
       <c r="C88" s="39" t="n"/>
       <c r="D88" s="40" t="n"/>
       <c r="E88" s="40" t="n"/>
-      <c r="F88" s="41" t="n"/>
+      <c r="F88" s="40" t="n"/>
       <c r="G88" s="40" t="n"/>
       <c r="H88" s="35" t="n"/>
       <c r="I88" s="35" t="n"/>
@@ -3019,7 +3039,7 @@
       <c r="C89" s="39" t="n"/>
       <c r="D89" s="40" t="n"/>
       <c r="E89" s="40" t="n"/>
-      <c r="F89" s="41" t="n"/>
+      <c r="F89" s="40" t="n"/>
       <c r="G89" s="40" t="n"/>
       <c r="H89" s="35" t="n"/>
       <c r="I89" s="35" t="n"/>
@@ -3036,7 +3056,7 @@
       <c r="C90" s="39" t="n"/>
       <c r="D90" s="40" t="n"/>
       <c r="E90" s="40" t="n"/>
-      <c r="F90" s="41" t="n"/>
+      <c r="F90" s="40" t="n"/>
       <c r="G90" s="40" t="n"/>
       <c r="H90" s="35" t="n"/>
       <c r="I90" s="35" t="n"/>
@@ -3053,8 +3073,8 @@
       <c r="C91" s="39" t="n"/>
       <c r="D91" s="40" t="n"/>
       <c r="E91" s="40" t="n"/>
-      <c r="F91" s="48" t="n"/>
-      <c r="G91" s="49" t="n"/>
+      <c r="F91" s="40" t="n"/>
+      <c r="G91" s="40" t="n"/>
       <c r="H91" s="35" t="n"/>
       <c r="I91" s="35" t="n"/>
       <c r="J91" s="35" t="n"/>
@@ -3070,7 +3090,7 @@
       <c r="C92" s="39" t="n"/>
       <c r="D92" s="40" t="n"/>
       <c r="E92" s="40" t="n"/>
-      <c r="F92" s="41" t="n"/>
+      <c r="F92" s="40" t="n"/>
       <c r="G92" s="40" t="n"/>
       <c r="H92" s="35" t="n"/>
       <c r="I92" s="35" t="n"/>
@@ -3087,7 +3107,7 @@
       <c r="C93" s="39" t="n"/>
       <c r="D93" s="40" t="n"/>
       <c r="E93" s="40" t="n"/>
-      <c r="F93" s="41" t="n"/>
+      <c r="F93" s="40" t="n"/>
       <c r="G93" s="40" t="n"/>
       <c r="H93" s="35" t="n"/>
       <c r="I93" s="35" t="n"/>
@@ -3104,7 +3124,7 @@
       <c r="C94" s="39" t="n"/>
       <c r="D94" s="40" t="n"/>
       <c r="E94" s="40" t="n"/>
-      <c r="F94" s="41" t="n"/>
+      <c r="F94" s="40" t="n"/>
       <c r="G94" s="40" t="n"/>
       <c r="H94" s="35" t="n"/>
       <c r="I94" s="35" t="n"/>
@@ -3121,7 +3141,7 @@
       <c r="C95" s="39" t="n"/>
       <c r="D95" s="40" t="n"/>
       <c r="E95" s="40" t="n"/>
-      <c r="F95" s="41" t="n"/>
+      <c r="F95" s="40" t="n"/>
       <c r="G95" s="40" t="n"/>
       <c r="H95" s="35" t="n"/>
       <c r="I95" s="35" t="n"/>
@@ -3138,7 +3158,7 @@
       <c r="C96" s="39" t="n"/>
       <c r="D96" s="40" t="n"/>
       <c r="E96" s="40" t="n"/>
-      <c r="F96" s="41" t="n"/>
+      <c r="F96" s="40" t="n"/>
       <c r="G96" s="40" t="n"/>
       <c r="H96" s="35" t="n"/>
       <c r="I96" s="35" t="n"/>
@@ -3155,7 +3175,7 @@
       <c r="C97" s="39" t="n"/>
       <c r="D97" s="40" t="n"/>
       <c r="E97" s="40" t="n"/>
-      <c r="F97" s="41" t="n"/>
+      <c r="F97" s="40" t="n"/>
       <c r="G97" s="40" t="n"/>
       <c r="H97" s="35" t="n"/>
       <c r="I97" s="35" t="n"/>
@@ -3172,7 +3192,7 @@
       <c r="C98" s="39" t="n"/>
       <c r="D98" s="40" t="n"/>
       <c r="E98" s="40" t="n"/>
-      <c r="F98" s="41" t="n"/>
+      <c r="F98" s="40" t="n"/>
       <c r="G98" s="40" t="n"/>
       <c r="H98" s="35" t="n"/>
       <c r="I98" s="35" t="n"/>
@@ -3189,7 +3209,7 @@
       <c r="C99" s="39" t="n"/>
       <c r="D99" s="40" t="n"/>
       <c r="E99" s="40" t="n"/>
-      <c r="F99" s="41" t="n"/>
+      <c r="F99" s="40" t="n"/>
       <c r="G99" s="40" t="n"/>
       <c r="H99" s="35" t="n"/>
       <c r="I99" s="35" t="n"/>
@@ -3204,10 +3224,10 @@
         </is>
       </c>
       <c r="C100" s="52" t="n"/>
-      <c r="D100" s="53" t="n"/>
-      <c r="E100" s="53" t="n"/>
-      <c r="F100" s="54" t="n"/>
-      <c r="G100" s="53" t="n"/>
+      <c r="D100" s="40" t="n"/>
+      <c r="E100" s="40" t="n"/>
+      <c r="F100" s="40" t="n"/>
+      <c r="G100" s="40" t="n"/>
       <c r="H100" s="35" t="n"/>
       <c r="I100" s="35" t="n"/>
       <c r="J100" s="35" t="n"/>
@@ -3256,7 +3276,7 @@
       </c>
       <c r="E103" s="33" t="inlineStr">
         <is>
-          <t>Redox  Reactions</t>
+          <t>Redox Reactions</t>
         </is>
       </c>
       <c r="F103" s="33" t="inlineStr">
@@ -3264,7 +3284,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="G103" s="15" t="inlineStr">
+      <c r="G103" s="33" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -3279,7 +3299,7 @@
       <c r="D104" s="71" t="n"/>
       <c r="E104" s="71" t="n"/>
       <c r="F104" s="71" t="n"/>
-      <c r="G104" s="70" t="n"/>
+      <c r="G104" s="71" t="n"/>
       <c r="H104" s="35" t="n"/>
       <c r="I104" s="60" t="n"/>
       <c r="J104" s="60" t="n"/>
@@ -3292,9 +3312,9 @@
       </c>
       <c r="C105" s="39" t="n"/>
       <c r="D105" s="40" t="n"/>
-      <c r="E105" s="41" t="n"/>
+      <c r="E105" s="40" t="n"/>
       <c r="F105" s="40" t="n"/>
-      <c r="G105" s="58" t="n"/>
+      <c r="G105" s="40" t="n"/>
       <c r="H105" s="35" t="n"/>
       <c r="I105" s="60" t="n"/>
       <c r="J105" s="57" t="n"/>
@@ -3306,10 +3326,10 @@
         </is>
       </c>
       <c r="C106" s="44" t="n"/>
-      <c r="D106" s="45" t="n"/>
-      <c r="E106" s="46" t="n"/>
-      <c r="F106" s="45" t="n"/>
-      <c r="G106" s="45" t="n"/>
+      <c r="D106" s="40" t="n"/>
+      <c r="E106" s="40" t="n"/>
+      <c r="F106" s="40" t="n"/>
+      <c r="G106" s="40" t="n"/>
       <c r="H106" s="35" t="n"/>
       <c r="I106" s="60" t="n"/>
       <c r="J106" s="57" t="n"/>
@@ -3322,7 +3342,7 @@
       </c>
       <c r="C107" s="39" t="n"/>
       <c r="D107" s="40" t="n"/>
-      <c r="E107" s="41" t="n"/>
+      <c r="E107" s="40" t="n"/>
       <c r="F107" s="40" t="n"/>
       <c r="G107" s="40" t="n"/>
       <c r="H107" s="35" t="n"/>
@@ -3337,7 +3357,7 @@
       </c>
       <c r="C108" s="39" t="n"/>
       <c r="D108" s="40" t="n"/>
-      <c r="E108" s="41" t="n"/>
+      <c r="E108" s="40" t="n"/>
       <c r="F108" s="40" t="n"/>
       <c r="G108" s="40" t="n"/>
       <c r="H108" s="35" t="n"/>
@@ -3352,7 +3372,7 @@
       </c>
       <c r="C109" s="39" t="n"/>
       <c r="D109" s="40" t="n"/>
-      <c r="E109" s="41" t="n"/>
+      <c r="E109" s="40" t="n"/>
       <c r="F109" s="40" t="n"/>
       <c r="G109" s="40" t="n"/>
       <c r="H109" s="35" t="n"/>
@@ -3367,7 +3387,7 @@
       </c>
       <c r="C110" s="39" t="n"/>
       <c r="D110" s="40" t="n"/>
-      <c r="E110" s="41" t="n"/>
+      <c r="E110" s="40" t="n"/>
       <c r="F110" s="40" t="n"/>
       <c r="G110" s="40" t="n"/>
       <c r="H110" s="35" t="n"/>
@@ -3381,10 +3401,10 @@
         </is>
       </c>
       <c r="C111" s="39" t="n"/>
-      <c r="D111" s="49" t="n"/>
-      <c r="E111" s="48" t="n"/>
-      <c r="F111" s="49" t="n"/>
-      <c r="G111" s="49" t="n"/>
+      <c r="D111" s="40" t="n"/>
+      <c r="E111" s="40" t="n"/>
+      <c r="F111" s="40" t="n"/>
+      <c r="G111" s="40" t="n"/>
       <c r="H111" s="35" t="n"/>
       <c r="I111" s="60" t="n"/>
       <c r="J111" s="57" t="n"/>
@@ -3397,7 +3417,7 @@
       </c>
       <c r="C112" s="39" t="n"/>
       <c r="D112" s="40" t="n"/>
-      <c r="E112" s="41" t="n"/>
+      <c r="E112" s="40" t="n"/>
       <c r="F112" s="40" t="n"/>
       <c r="G112" s="40" t="n"/>
       <c r="H112" s="35" t="n"/>
@@ -3412,7 +3432,7 @@
       </c>
       <c r="C113" s="39" t="n"/>
       <c r="D113" s="40" t="n"/>
-      <c r="E113" s="41" t="n"/>
+      <c r="E113" s="40" t="n"/>
       <c r="F113" s="40" t="n"/>
       <c r="G113" s="40" t="n"/>
       <c r="H113" s="35" t="n"/>
@@ -3427,7 +3447,7 @@
       </c>
       <c r="C114" s="39" t="n"/>
       <c r="D114" s="40" t="n"/>
-      <c r="E114" s="41" t="n"/>
+      <c r="E114" s="40" t="n"/>
       <c r="F114" s="40" t="n"/>
       <c r="G114" s="40" t="n"/>
       <c r="H114" s="35" t="n"/>
@@ -3442,7 +3462,7 @@
       </c>
       <c r="C115" s="39" t="n"/>
       <c r="D115" s="40" t="n"/>
-      <c r="E115" s="41" t="n"/>
+      <c r="E115" s="40" t="n"/>
       <c r="F115" s="40" t="n"/>
       <c r="G115" s="40" t="n"/>
       <c r="H115" s="35" t="n"/>
@@ -3457,7 +3477,7 @@
       </c>
       <c r="C116" s="39" t="n"/>
       <c r="D116" s="40" t="n"/>
-      <c r="E116" s="41" t="n"/>
+      <c r="E116" s="40" t="n"/>
       <c r="F116" s="40" t="n"/>
       <c r="G116" s="40" t="n"/>
       <c r="H116" s="35" t="n"/>
@@ -3472,7 +3492,7 @@
       </c>
       <c r="C117" s="39" t="n"/>
       <c r="D117" s="40" t="n"/>
-      <c r="E117" s="41" t="n"/>
+      <c r="E117" s="40" t="n"/>
       <c r="F117" s="40" t="n"/>
       <c r="G117" s="40" t="n"/>
       <c r="H117" s="35" t="n"/>
@@ -3487,7 +3507,7 @@
       </c>
       <c r="C118" s="39" t="n"/>
       <c r="D118" s="40" t="n"/>
-      <c r="E118" s="41" t="n"/>
+      <c r="E118" s="40" t="n"/>
       <c r="F118" s="40" t="n"/>
       <c r="G118" s="40" t="n"/>
       <c r="H118" s="35" t="n"/>
@@ -3502,7 +3522,7 @@
       </c>
       <c r="C119" s="39" t="n"/>
       <c r="D119" s="40" t="n"/>
-      <c r="E119" s="41" t="n"/>
+      <c r="E119" s="40" t="n"/>
       <c r="F119" s="40" t="n"/>
       <c r="G119" s="40" t="n"/>
       <c r="H119" s="35" t="n"/>
@@ -3516,10 +3536,10 @@
         </is>
       </c>
       <c r="C120" s="52" t="n"/>
-      <c r="D120" s="53" t="n"/>
-      <c r="E120" s="54" t="n"/>
-      <c r="F120" s="53" t="n"/>
-      <c r="G120" s="53" t="n"/>
+      <c r="D120" s="40" t="n"/>
+      <c r="E120" s="40" t="n"/>
+      <c r="F120" s="40" t="n"/>
+      <c r="G120" s="40" t="n"/>
       <c r="H120" s="35" t="n"/>
       <c r="I120" s="60" t="n"/>
       <c r="J120" s="57" t="n"/>
@@ -3564,17 +3584,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="E123" s="15" t="inlineStr">
+      <c r="E123" s="33" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="F123" s="15" t="inlineStr">
+      <c r="F123" s="33" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="G123" s="15" t="inlineStr">
+      <c r="G123" s="33" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -3589,9 +3609,9 @@
       <c r="B124" s="69" t="n"/>
       <c r="C124" s="70" t="n"/>
       <c r="D124" s="71" t="n"/>
-      <c r="E124" s="70" t="n"/>
-      <c r="F124" s="70" t="n"/>
-      <c r="G124" s="70" t="n"/>
+      <c r="E124" s="71" t="n"/>
+      <c r="F124" s="71" t="n"/>
+      <c r="G124" s="71" t="n"/>
       <c r="H124" s="35" t="n"/>
       <c r="I124" s="35" t="n"/>
       <c r="J124" s="35" t="n"/>
@@ -3606,8 +3626,8 @@
       </c>
       <c r="C125" s="39" t="n"/>
       <c r="D125" s="40" t="n"/>
-      <c r="E125" s="58" t="n"/>
-      <c r="F125" s="41" t="n"/>
+      <c r="E125" s="40" t="n"/>
+      <c r="F125" s="40" t="n"/>
       <c r="G125" s="40" t="n"/>
       <c r="H125" s="35" t="n"/>
       <c r="I125" s="35" t="n"/>
@@ -3622,10 +3642,10 @@
         </is>
       </c>
       <c r="C126" s="44" t="n"/>
-      <c r="D126" s="45" t="n"/>
-      <c r="E126" s="45" t="n"/>
-      <c r="F126" s="41" t="n"/>
-      <c r="G126" s="45" t="n"/>
+      <c r="D126" s="40" t="n"/>
+      <c r="E126" s="40" t="n"/>
+      <c r="F126" s="40" t="n"/>
+      <c r="G126" s="40" t="n"/>
       <c r="H126" s="35" t="n"/>
       <c r="I126" s="35" t="n"/>
       <c r="J126" s="35" t="n"/>
@@ -3641,7 +3661,7 @@
       <c r="C127" s="39" t="n"/>
       <c r="D127" s="40" t="n"/>
       <c r="E127" s="40" t="n"/>
-      <c r="F127" s="41" t="n"/>
+      <c r="F127" s="40" t="n"/>
       <c r="G127" s="40" t="n"/>
       <c r="H127" s="35" t="n"/>
       <c r="I127" s="35" t="n"/>
@@ -3658,7 +3678,7 @@
       <c r="C128" s="39" t="n"/>
       <c r="D128" s="40" t="n"/>
       <c r="E128" s="40" t="n"/>
-      <c r="F128" s="41" t="n"/>
+      <c r="F128" s="40" t="n"/>
       <c r="G128" s="40" t="n"/>
       <c r="H128" s="35" t="n"/>
       <c r="I128" s="35" t="n"/>
@@ -3675,7 +3695,7 @@
       <c r="C129" s="39" t="n"/>
       <c r="D129" s="40" t="n"/>
       <c r="E129" s="40" t="n"/>
-      <c r="F129" s="41" t="n"/>
+      <c r="F129" s="40" t="n"/>
       <c r="G129" s="40" t="n"/>
       <c r="H129" s="35" t="n"/>
       <c r="I129" s="35" t="n"/>
@@ -3692,7 +3712,7 @@
       <c r="C130" s="39" t="n"/>
       <c r="D130" s="40" t="n"/>
       <c r="E130" s="40" t="n"/>
-      <c r="F130" s="41" t="n"/>
+      <c r="F130" s="40" t="n"/>
       <c r="G130" s="40" t="n"/>
       <c r="H130" s="35" t="n"/>
       <c r="I130" s="35" t="n"/>
@@ -3709,8 +3729,8 @@
       <c r="C131" s="39" t="n"/>
       <c r="D131" s="40" t="n"/>
       <c r="E131" s="40" t="n"/>
-      <c r="F131" s="48" t="n"/>
-      <c r="G131" s="49" t="n"/>
+      <c r="F131" s="40" t="n"/>
+      <c r="G131" s="40" t="n"/>
       <c r="H131" s="35" t="n"/>
       <c r="I131" s="35" t="n"/>
       <c r="J131" s="35" t="n"/>
@@ -3726,7 +3746,7 @@
       <c r="C132" s="39" t="n"/>
       <c r="D132" s="40" t="n"/>
       <c r="E132" s="40" t="n"/>
-      <c r="F132" s="41" t="n"/>
+      <c r="F132" s="40" t="n"/>
       <c r="G132" s="40" t="n"/>
       <c r="H132" s="35" t="n"/>
       <c r="I132" s="35" t="n"/>
@@ -3743,7 +3763,7 @@
       <c r="C133" s="39" t="n"/>
       <c r="D133" s="40" t="n"/>
       <c r="E133" s="40" t="n"/>
-      <c r="F133" s="41" t="n"/>
+      <c r="F133" s="40" t="n"/>
       <c r="G133" s="40" t="n"/>
       <c r="H133" s="35" t="n"/>
       <c r="I133" s="35" t="n"/>
@@ -3760,7 +3780,7 @@
       <c r="C134" s="39" t="n"/>
       <c r="D134" s="40" t="n"/>
       <c r="E134" s="40" t="n"/>
-      <c r="F134" s="41" t="n"/>
+      <c r="F134" s="40" t="n"/>
       <c r="G134" s="40" t="n"/>
       <c r="H134" s="35" t="n"/>
       <c r="I134" s="35" t="n"/>
@@ -3777,7 +3797,7 @@
       <c r="C135" s="39" t="n"/>
       <c r="D135" s="40" t="n"/>
       <c r="E135" s="40" t="n"/>
-      <c r="F135" s="41" t="n"/>
+      <c r="F135" s="40" t="n"/>
       <c r="G135" s="40" t="n"/>
       <c r="H135" s="35" t="n"/>
       <c r="I135" s="35" t="n"/>
@@ -3794,7 +3814,7 @@
       <c r="C136" s="39" t="n"/>
       <c r="D136" s="40" t="n"/>
       <c r="E136" s="40" t="n"/>
-      <c r="F136" s="41" t="n"/>
+      <c r="F136" s="40" t="n"/>
       <c r="G136" s="40" t="n"/>
       <c r="H136" s="35" t="n"/>
       <c r="I136" s="35" t="n"/>
@@ -3811,7 +3831,7 @@
       <c r="C137" s="39" t="n"/>
       <c r="D137" s="40" t="n"/>
       <c r="E137" s="40" t="n"/>
-      <c r="F137" s="41" t="n"/>
+      <c r="F137" s="40" t="n"/>
       <c r="G137" s="40" t="n"/>
       <c r="H137" s="35" t="n"/>
       <c r="I137" s="35" t="n"/>
@@ -3828,7 +3848,7 @@
       <c r="C138" s="39" t="n"/>
       <c r="D138" s="40" t="n"/>
       <c r="E138" s="40" t="n"/>
-      <c r="F138" s="41" t="n"/>
+      <c r="F138" s="40" t="n"/>
       <c r="G138" s="40" t="n"/>
       <c r="H138" s="35" t="n"/>
       <c r="I138" s="35" t="n"/>
@@ -3845,7 +3865,7 @@
       <c r="C139" s="39" t="n"/>
       <c r="D139" s="40" t="n"/>
       <c r="E139" s="40" t="n"/>
-      <c r="F139" s="41" t="n"/>
+      <c r="F139" s="40" t="n"/>
       <c r="G139" s="40" t="n"/>
       <c r="H139" s="35" t="n"/>
       <c r="I139" s="35" t="n"/>
@@ -3860,10 +3880,10 @@
         </is>
       </c>
       <c r="C140" s="52" t="n"/>
-      <c r="D140" s="53" t="n"/>
-      <c r="E140" s="53" t="n"/>
-      <c r="F140" s="54" t="n"/>
-      <c r="G140" s="53" t="n"/>
+      <c r="D140" s="40" t="n"/>
+      <c r="E140" s="40" t="n"/>
+      <c r="F140" s="40" t="n"/>
+      <c r="G140" s="40" t="n"/>
       <c r="H140" s="35" t="n"/>
       <c r="I140" s="35" t="n"/>
       <c r="J140" s="35" t="n"/>
@@ -3912,7 +3932,7 @@
       </c>
       <c r="E143" s="33" t="inlineStr">
         <is>
-          <t>Redox  Reactions</t>
+          <t>Redox Reactions</t>
         </is>
       </c>
       <c r="F143" s="33" t="inlineStr">
@@ -3920,7 +3940,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="G143" s="15" t="inlineStr">
+      <c r="G143" s="33" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -3935,7 +3955,7 @@
       <c r="D144" s="71" t="n"/>
       <c r="E144" s="71" t="n"/>
       <c r="F144" s="71" t="n"/>
-      <c r="G144" s="70" t="n"/>
+      <c r="G144" s="71" t="n"/>
       <c r="H144" s="35" t="n"/>
       <c r="I144" s="60" t="n"/>
       <c r="J144" s="60" t="n"/>
@@ -3948,9 +3968,9 @@
       </c>
       <c r="C145" s="39" t="n"/>
       <c r="D145" s="40" t="n"/>
-      <c r="E145" s="41" t="n"/>
+      <c r="E145" s="40" t="n"/>
       <c r="F145" s="40" t="n"/>
-      <c r="G145" s="58" t="n"/>
+      <c r="G145" s="40" t="n"/>
       <c r="H145" s="35" t="n"/>
       <c r="I145" s="60" t="n"/>
       <c r="J145" s="57" t="n"/>
@@ -3962,10 +3982,10 @@
         </is>
       </c>
       <c r="C146" s="44" t="n"/>
-      <c r="D146" s="45" t="n"/>
-      <c r="E146" s="46" t="n"/>
-      <c r="F146" s="45" t="n"/>
-      <c r="G146" s="45" t="n"/>
+      <c r="D146" s="40" t="n"/>
+      <c r="E146" s="40" t="n"/>
+      <c r="F146" s="40" t="n"/>
+      <c r="G146" s="40" t="n"/>
       <c r="H146" s="35" t="n"/>
       <c r="I146" s="60" t="n"/>
       <c r="J146" s="57" t="n"/>
@@ -3978,7 +3998,7 @@
       </c>
       <c r="C147" s="39" t="n"/>
       <c r="D147" s="40" t="n"/>
-      <c r="E147" s="41" t="n"/>
+      <c r="E147" s="40" t="n"/>
       <c r="F147" s="40" t="n"/>
       <c r="G147" s="40" t="n"/>
       <c r="H147" s="35" t="n"/>
@@ -3993,7 +4013,7 @@
       </c>
       <c r="C148" s="39" t="n"/>
       <c r="D148" s="40" t="n"/>
-      <c r="E148" s="41" t="n"/>
+      <c r="E148" s="40" t="n"/>
       <c r="F148" s="40" t="n"/>
       <c r="G148" s="40" t="n"/>
       <c r="H148" s="35" t="n"/>
@@ -4008,7 +4028,7 @@
       </c>
       <c r="C149" s="39" t="n"/>
       <c r="D149" s="40" t="n"/>
-      <c r="E149" s="41" t="n"/>
+      <c r="E149" s="40" t="n"/>
       <c r="F149" s="40" t="n"/>
       <c r="G149" s="40" t="n"/>
       <c r="H149" s="35" t="n"/>
@@ -4023,7 +4043,7 @@
       </c>
       <c r="C150" s="39" t="n"/>
       <c r="D150" s="40" t="n"/>
-      <c r="E150" s="41" t="n"/>
+      <c r="E150" s="40" t="n"/>
       <c r="F150" s="40" t="n"/>
       <c r="G150" s="40" t="n"/>
       <c r="H150" s="35" t="n"/>
@@ -4037,10 +4057,10 @@
         </is>
       </c>
       <c r="C151" s="39" t="n"/>
-      <c r="D151" s="49" t="n"/>
-      <c r="E151" s="48" t="n"/>
-      <c r="F151" s="49" t="n"/>
-      <c r="G151" s="49" t="n"/>
+      <c r="D151" s="40" t="n"/>
+      <c r="E151" s="40" t="n"/>
+      <c r="F151" s="40" t="n"/>
+      <c r="G151" s="40" t="n"/>
       <c r="H151" s="35" t="n"/>
       <c r="I151" s="60" t="n"/>
       <c r="J151" s="57" t="n"/>
@@ -4053,7 +4073,7 @@
       </c>
       <c r="C152" s="39" t="n"/>
       <c r="D152" s="40" t="n"/>
-      <c r="E152" s="41" t="n"/>
+      <c r="E152" s="40" t="n"/>
       <c r="F152" s="40" t="n"/>
       <c r="G152" s="40" t="n"/>
       <c r="H152" s="35" t="n"/>
@@ -4067,10 +4087,10 @@
         </is>
       </c>
       <c r="C153" s="39" t="n"/>
-      <c r="D153" s="62" t="n"/>
-      <c r="E153" s="63" t="n"/>
-      <c r="F153" s="62" t="n"/>
-      <c r="G153" s="62" t="n"/>
+      <c r="D153" s="40" t="n"/>
+      <c r="E153" s="40" t="n"/>
+      <c r="F153" s="40" t="n"/>
+      <c r="G153" s="40" t="n"/>
       <c r="H153" s="35" t="n"/>
     </row>
     <row r="154">
@@ -4080,10 +4100,10 @@
         </is>
       </c>
       <c r="C154" s="39" t="n"/>
-      <c r="D154" s="62" t="n"/>
-      <c r="E154" s="63" t="n"/>
-      <c r="F154" s="62" t="n"/>
-      <c r="G154" s="62" t="n"/>
+      <c r="D154" s="40" t="n"/>
+      <c r="E154" s="40" t="n"/>
+      <c r="F154" s="40" t="n"/>
+      <c r="G154" s="40" t="n"/>
       <c r="H154" s="35" t="n"/>
     </row>
     <row r="155">
@@ -4093,10 +4113,10 @@
         </is>
       </c>
       <c r="C155" s="39" t="n"/>
-      <c r="D155" s="62" t="n"/>
-      <c r="E155" s="63" t="n"/>
-      <c r="F155" s="62" t="n"/>
-      <c r="G155" s="62" t="n"/>
+      <c r="D155" s="40" t="n"/>
+      <c r="E155" s="40" t="n"/>
+      <c r="F155" s="40" t="n"/>
+      <c r="G155" s="40" t="n"/>
       <c r="H155" s="35" t="n"/>
     </row>
     <row r="156">
@@ -4106,10 +4126,10 @@
         </is>
       </c>
       <c r="C156" s="39" t="n"/>
-      <c r="D156" s="62" t="n"/>
-      <c r="E156" s="63" t="n"/>
-      <c r="F156" s="62" t="n"/>
-      <c r="G156" s="62" t="n"/>
+      <c r="D156" s="40" t="n"/>
+      <c r="E156" s="40" t="n"/>
+      <c r="F156" s="40" t="n"/>
+      <c r="G156" s="40" t="n"/>
       <c r="H156" s="35" t="n"/>
     </row>
     <row r="157">
@@ -4119,10 +4139,10 @@
         </is>
       </c>
       <c r="C157" s="39" t="n"/>
-      <c r="D157" s="62" t="n"/>
-      <c r="E157" s="63" t="n"/>
-      <c r="F157" s="62" t="n"/>
-      <c r="G157" s="62" t="n"/>
+      <c r="D157" s="40" t="n"/>
+      <c r="E157" s="40" t="n"/>
+      <c r="F157" s="40" t="n"/>
+      <c r="G157" s="40" t="n"/>
       <c r="H157" s="35" t="n"/>
     </row>
     <row r="158">
@@ -4132,10 +4152,10 @@
         </is>
       </c>
       <c r="C158" s="39" t="n"/>
-      <c r="D158" s="62" t="n"/>
-      <c r="E158" s="63" t="n"/>
-      <c r="F158" s="62" t="n"/>
-      <c r="G158" s="62" t="n"/>
+      <c r="D158" s="40" t="n"/>
+      <c r="E158" s="40" t="n"/>
+      <c r="F158" s="40" t="n"/>
+      <c r="G158" s="40" t="n"/>
       <c r="H158" s="35" t="n"/>
     </row>
     <row r="159">
@@ -4145,10 +4165,10 @@
         </is>
       </c>
       <c r="C159" s="39" t="n"/>
-      <c r="D159" s="62" t="n"/>
-      <c r="E159" s="63" t="n"/>
-      <c r="F159" s="62" t="n"/>
-      <c r="G159" s="62" t="n"/>
+      <c r="D159" s="40" t="n"/>
+      <c r="E159" s="40" t="n"/>
+      <c r="F159" s="40" t="n"/>
+      <c r="G159" s="40" t="n"/>
       <c r="H159" s="35" t="n"/>
     </row>
     <row r="160" ht="15" customHeight="1" s="24">
@@ -4158,24 +4178,24 @@
         </is>
       </c>
       <c r="C160" s="52" t="n"/>
-      <c r="D160" s="64" t="n"/>
-      <c r="E160" s="65" t="n"/>
-      <c r="F160" s="64" t="n"/>
-      <c r="G160" s="64" t="n"/>
+      <c r="D160" s="40" t="n"/>
+      <c r="E160" s="40" t="n"/>
+      <c r="F160" s="40" t="n"/>
+      <c r="G160" s="40" t="n"/>
       <c r="H160" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="56">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="E43:E44"/>
     <mergeCell ref="C103:C104"/>
     <mergeCell ref="E123:E124"/>
-    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="G43:G44"/>
     <mergeCell ref="G23:G24"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="F103:F104"/>
     <mergeCell ref="F83:F84"/>
-    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="B42:G42"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E23:E24"/>
@@ -4222,7 +4242,6 @@
     <mergeCell ref="E83:E84"/>
     <mergeCell ref="F63:F64"/>
     <mergeCell ref="F143:F144"/>
-    <mergeCell ref="H63:H64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4234,11 +4253,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="B1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="9" customWidth="1" style="24" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="25"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
+    <col width="13" customWidth="1" style="24" min="4" max="4"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="13" customWidth="1" style="24" min="6" max="6"/>
     <col width="9" customWidth="1" style="24" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -4266,17 +4289,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F3" s="72" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -4290,9 +4313,9 @@
     <row r="4" ht="15" customHeight="1" s="24">
       <c r="B4" s="69" t="n"/>
       <c r="C4" s="71" t="n"/>
-      <c r="D4" s="70" t="n"/>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="70" t="n"/>
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
       <c r="G4" s="35" t="n"/>
       <c r="H4" s="35" t="n"/>
       <c r="I4" s="30" t="n"/>
@@ -4321,10 +4344,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="40" t="n"/>
       <c r="G6" s="57" t="n"/>
       <c r="H6" s="57" t="n"/>
       <c r="I6" s="30" t="n"/>
@@ -4402,9 +4425,9 @@
         </is>
       </c>
       <c r="C11" s="40" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="49" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
       <c r="G11" s="57" t="n"/>
       <c r="H11" s="57" t="n"/>
       <c r="I11" s="30" t="n"/>
@@ -4417,10 +4440,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="53" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
       <c r="G12" s="57" t="n"/>
       <c r="H12" s="57" t="n"/>
       <c r="I12" s="30" t="n"/>
@@ -4465,7 +4488,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F15" s="72" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -4481,7 +4504,7 @@
       <c r="C16" s="71" t="n"/>
       <c r="D16" s="71" t="n"/>
       <c r="E16" s="71" t="n"/>
-      <c r="F16" s="70" t="n"/>
+      <c r="F16" s="71" t="n"/>
       <c r="G16" s="35" t="n"/>
       <c r="H16" s="35" t="n"/>
       <c r="I16" s="30" t="n"/>
@@ -4497,7 +4520,7 @@
       <c r="C17" s="40" t="n"/>
       <c r="D17" s="40" t="n"/>
       <c r="E17" s="40" t="n"/>
-      <c r="F17" s="45" t="n"/>
+      <c r="F17" s="40" t="n"/>
       <c r="G17" s="35" t="n"/>
       <c r="H17" s="35" t="n"/>
       <c r="I17" s="30" t="n"/>
@@ -4510,10 +4533,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="45" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
       <c r="G18" s="35" t="n"/>
       <c r="H18" s="35" t="n"/>
       <c r="I18" s="30" t="n"/>
@@ -4590,10 +4613,10 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="49" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
       <c r="G23" s="35" t="n"/>
       <c r="H23" s="35" t="n"/>
       <c r="I23" s="30" t="n"/>
@@ -4606,10 +4629,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="40" t="n"/>
       <c r="G24" s="35" t="n"/>
       <c r="H24" s="35" t="n"/>
       <c r="I24" s="30" t="n"/>
@@ -4644,17 +4667,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D27" s="72" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E27" s="72" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F27" s="72" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -4668,9 +4691,9 @@
     <row r="28" ht="15" customHeight="1" s="24">
       <c r="B28" s="69" t="n"/>
       <c r="C28" s="71" t="n"/>
-      <c r="D28" s="70" t="n"/>
-      <c r="E28" s="70" t="n"/>
-      <c r="F28" s="70" t="n"/>
+      <c r="D28" s="71" t="n"/>
+      <c r="E28" s="71" t="n"/>
+      <c r="F28" s="71" t="n"/>
       <c r="G28" s="35" t="n"/>
       <c r="H28" s="35" t="n"/>
       <c r="I28" s="30" t="n"/>
@@ -4699,10 +4722,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
+      <c r="C30" s="40" t="n"/>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="40" t="n"/>
       <c r="G30" s="57" t="n"/>
       <c r="H30" s="57" t="n"/>
       <c r="I30" s="30" t="n"/>
@@ -4780,9 +4803,9 @@
         </is>
       </c>
       <c r="C35" s="40" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="40" t="n"/>
+      <c r="F35" s="40" t="n"/>
       <c r="G35" s="57" t="n"/>
       <c r="H35" s="57" t="n"/>
       <c r="I35" s="30" t="n"/>
@@ -4795,10 +4818,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
-      <c r="E36" s="53" t="n"/>
-      <c r="F36" s="53" t="n"/>
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
       <c r="G36" s="57" t="n"/>
       <c r="H36" s="57" t="n"/>
       <c r="I36" s="30" t="n"/>
@@ -4843,7 +4866,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F39" s="72" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -4859,7 +4882,7 @@
       <c r="C40" s="71" t="n"/>
       <c r="D40" s="71" t="n"/>
       <c r="E40" s="71" t="n"/>
-      <c r="F40" s="70" t="n"/>
+      <c r="F40" s="71" t="n"/>
       <c r="G40" s="35" t="n"/>
       <c r="H40" s="35" t="n"/>
       <c r="I40" s="30" t="n"/>
@@ -4875,7 +4898,7 @@
       <c r="C41" s="40" t="n"/>
       <c r="D41" s="40" t="n"/>
       <c r="E41" s="40" t="n"/>
-      <c r="F41" s="45" t="n"/>
+      <c r="F41" s="40" t="n"/>
       <c r="G41" s="35" t="n"/>
       <c r="H41" s="35" t="n"/>
       <c r="I41" s="30" t="n"/>
@@ -4888,10 +4911,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="45" t="n"/>
-      <c r="D42" s="45" t="n"/>
-      <c r="E42" s="45" t="n"/>
-      <c r="F42" s="45" t="n"/>
+      <c r="C42" s="40" t="n"/>
+      <c r="D42" s="40" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
       <c r="G42" s="35" t="n"/>
       <c r="H42" s="35" t="n"/>
       <c r="I42" s="30" t="n"/>
@@ -4968,10 +4991,10 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="49" t="n"/>
-      <c r="D47" s="49" t="n"/>
-      <c r="E47" s="49" t="n"/>
-      <c r="F47" s="49" t="n"/>
+      <c r="C47" s="40" t="n"/>
+      <c r="D47" s="40" t="n"/>
+      <c r="E47" s="40" t="n"/>
+      <c r="F47" s="40" t="n"/>
       <c r="G47" s="35" t="n"/>
       <c r="H47" s="35" t="n"/>
       <c r="I47" s="30" t="n"/>
@@ -4984,10 +5007,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
-      <c r="E48" s="53" t="n"/>
-      <c r="F48" s="53" t="n"/>
+      <c r="C48" s="40" t="n"/>
+      <c r="D48" s="40" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
       <c r="G48" s="35" t="n"/>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="30" t="n"/>
@@ -5022,17 +5045,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D51" s="72" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E51" s="72" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F51" s="72" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -5046,9 +5069,9 @@
     <row r="52" ht="15" customHeight="1" s="24">
       <c r="B52" s="69" t="n"/>
       <c r="C52" s="71" t="n"/>
-      <c r="D52" s="70" t="n"/>
-      <c r="E52" s="70" t="n"/>
-      <c r="F52" s="70" t="n"/>
+      <c r="D52" s="71" t="n"/>
+      <c r="E52" s="71" t="n"/>
+      <c r="F52" s="71" t="n"/>
       <c r="G52" s="35" t="n"/>
       <c r="H52" s="35" t="n"/>
       <c r="I52" s="30" t="n"/>
@@ -5077,10 +5100,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="45" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="45" t="n"/>
-      <c r="F54" s="45" t="n"/>
+      <c r="C54" s="40" t="n"/>
+      <c r="D54" s="40" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
       <c r="G54" s="57" t="n"/>
       <c r="H54" s="57" t="n"/>
       <c r="I54" s="30" t="n"/>
@@ -5136,15 +5159,15 @@
       <c r="K57" s="30" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="40" t="n"/>
-      <c r="D58" s="40" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
+      <c r="C58" s="74" t="n"/>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="74" t="n"/>
       <c r="G58" s="57" t="n"/>
       <c r="H58" s="57" t="n"/>
       <c r="I58" s="30" t="n"/>
@@ -5158,9 +5181,9 @@
         </is>
       </c>
       <c r="C59" s="40" t="n"/>
-      <c r="D59" s="49" t="n"/>
-      <c r="E59" s="49" t="n"/>
-      <c r="F59" s="49" t="n"/>
+      <c r="D59" s="40" t="n"/>
+      <c r="E59" s="40" t="n"/>
+      <c r="F59" s="40" t="n"/>
       <c r="G59" s="57" t="n"/>
       <c r="H59" s="57" t="n"/>
       <c r="I59" s="30" t="n"/>
@@ -5173,10 +5196,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
+      <c r="C60" s="40" t="n"/>
+      <c r="D60" s="40" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
       <c r="G60" s="57" t="n"/>
       <c r="H60" s="57" t="n"/>
       <c r="I60" s="30" t="n"/>
@@ -5221,7 +5244,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F63" s="72" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -5237,7 +5260,7 @@
       <c r="C64" s="71" t="n"/>
       <c r="D64" s="71" t="n"/>
       <c r="E64" s="71" t="n"/>
-      <c r="F64" s="70" t="n"/>
+      <c r="F64" s="71" t="n"/>
       <c r="G64" s="35" t="n"/>
       <c r="H64" s="35" t="n"/>
       <c r="I64" s="30" t="n"/>
@@ -5253,7 +5276,7 @@
       <c r="C65" s="40" t="n"/>
       <c r="D65" s="40" t="n"/>
       <c r="E65" s="40" t="n"/>
-      <c r="F65" s="45" t="n"/>
+      <c r="F65" s="40" t="n"/>
       <c r="G65" s="35" t="n"/>
       <c r="H65" s="35" t="n"/>
       <c r="I65" s="30" t="n"/>
@@ -5266,10 +5289,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="45" t="n"/>
-      <c r="D66" s="45" t="n"/>
-      <c r="E66" s="45" t="n"/>
-      <c r="F66" s="45" t="n"/>
+      <c r="C66" s="40" t="n"/>
+      <c r="D66" s="40" t="n"/>
+      <c r="E66" s="40" t="n"/>
+      <c r="F66" s="40" t="n"/>
       <c r="G66" s="35" t="n"/>
       <c r="H66" s="35" t="n"/>
       <c r="I66" s="30" t="n"/>
@@ -5325,15 +5348,15 @@
       <c r="K69" s="30" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="40" t="n"/>
-      <c r="D70" s="40" t="n"/>
-      <c r="E70" s="40" t="n"/>
-      <c r="F70" s="40" t="n"/>
+      <c r="C70" s="74" t="n"/>
+      <c r="D70" s="74" t="n"/>
+      <c r="E70" s="74" t="n"/>
+      <c r="F70" s="74" t="n"/>
       <c r="G70" s="35" t="n"/>
       <c r="H70" s="35" t="n"/>
       <c r="I70" s="30" t="n"/>
@@ -5346,10 +5369,10 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="49" t="n"/>
-      <c r="D71" s="49" t="n"/>
-      <c r="E71" s="49" t="n"/>
-      <c r="F71" s="49" t="n"/>
+      <c r="C71" s="40" t="n"/>
+      <c r="D71" s="40" t="n"/>
+      <c r="E71" s="40" t="n"/>
+      <c r="F71" s="40" t="n"/>
       <c r="G71" s="35" t="n"/>
       <c r="H71" s="35" t="n"/>
       <c r="I71" s="30" t="n"/>
@@ -5362,10 +5385,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="53" t="n"/>
-      <c r="D72" s="53" t="n"/>
-      <c r="E72" s="53" t="n"/>
-      <c r="F72" s="53" t="n"/>
+      <c r="C72" s="40" t="n"/>
+      <c r="D72" s="40" t="n"/>
+      <c r="E72" s="40" t="n"/>
+      <c r="F72" s="40" t="n"/>
       <c r="G72" s="35" t="n"/>
       <c r="H72" s="35" t="n"/>
       <c r="I72" s="30" t="n"/>
@@ -5400,17 +5423,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D75" s="72" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E75" s="72" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F75" s="72" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -5424,9 +5447,9 @@
     <row r="76" ht="15" customHeight="1" s="24">
       <c r="B76" s="69" t="n"/>
       <c r="C76" s="71" t="n"/>
-      <c r="D76" s="70" t="n"/>
-      <c r="E76" s="70" t="n"/>
-      <c r="F76" s="70" t="n"/>
+      <c r="D76" s="71" t="n"/>
+      <c r="E76" s="71" t="n"/>
+      <c r="F76" s="71" t="n"/>
       <c r="G76" s="35" t="n"/>
       <c r="H76" s="35" t="n"/>
       <c r="I76" s="30" t="n"/>
@@ -5455,10 +5478,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="45" t="n"/>
-      <c r="D78" s="45" t="n"/>
-      <c r="E78" s="45" t="n"/>
-      <c r="F78" s="45" t="n"/>
+      <c r="C78" s="40" t="n"/>
+      <c r="D78" s="40" t="n"/>
+      <c r="E78" s="40" t="n"/>
+      <c r="F78" s="40" t="n"/>
       <c r="G78" s="57" t="n"/>
       <c r="H78" s="57" t="n"/>
       <c r="I78" s="30" t="n"/>
@@ -5536,9 +5559,9 @@
         </is>
       </c>
       <c r="C83" s="40" t="n"/>
-      <c r="D83" s="49" t="n"/>
-      <c r="E83" s="49" t="n"/>
-      <c r="F83" s="49" t="n"/>
+      <c r="D83" s="40" t="n"/>
+      <c r="E83" s="40" t="n"/>
+      <c r="F83" s="40" t="n"/>
       <c r="G83" s="57" t="n"/>
       <c r="H83" s="57" t="n"/>
       <c r="I83" s="30" t="n"/>
@@ -5551,10 +5574,10 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="53" t="n"/>
-      <c r="D84" s="53" t="n"/>
-      <c r="E84" s="53" t="n"/>
-      <c r="F84" s="53" t="n"/>
+      <c r="C84" s="40" t="n"/>
+      <c r="D84" s="40" t="n"/>
+      <c r="E84" s="40" t="n"/>
+      <c r="F84" s="40" t="n"/>
       <c r="G84" s="57" t="n"/>
       <c r="H84" s="57" t="n"/>
       <c r="I84" s="30" t="n"/>
@@ -5599,7 +5622,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F87" s="72" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -5615,7 +5638,7 @@
       <c r="C88" s="71" t="n"/>
       <c r="D88" s="71" t="n"/>
       <c r="E88" s="71" t="n"/>
-      <c r="F88" s="70" t="n"/>
+      <c r="F88" s="71" t="n"/>
       <c r="G88" s="35" t="n"/>
       <c r="H88" s="35" t="n"/>
       <c r="I88" s="30" t="n"/>
@@ -5631,7 +5654,7 @@
       <c r="C89" s="40" t="n"/>
       <c r="D89" s="40" t="n"/>
       <c r="E89" s="40" t="n"/>
-      <c r="F89" s="45" t="n"/>
+      <c r="F89" s="40" t="n"/>
       <c r="G89" s="35" t="n"/>
       <c r="H89" s="35" t="n"/>
       <c r="I89" s="30" t="n"/>
@@ -5644,10 +5667,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="45" t="n"/>
-      <c r="D90" s="45" t="n"/>
-      <c r="E90" s="45" t="n"/>
-      <c r="F90" s="45" t="n"/>
+      <c r="C90" s="40" t="n"/>
+      <c r="D90" s="40" t="n"/>
+      <c r="E90" s="40" t="n"/>
+      <c r="F90" s="40" t="n"/>
       <c r="G90" s="35" t="n"/>
       <c r="H90" s="35" t="n"/>
       <c r="I90" s="30" t="n"/>
@@ -5724,10 +5747,10 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="49" t="n"/>
-      <c r="D95" s="49" t="n"/>
-      <c r="E95" s="49" t="n"/>
-      <c r="F95" s="49" t="n"/>
+      <c r="C95" s="40" t="n"/>
+      <c r="D95" s="40" t="n"/>
+      <c r="E95" s="40" t="n"/>
+      <c r="F95" s="40" t="n"/>
       <c r="G95" s="35" t="n"/>
       <c r="H95" s="35" t="n"/>
       <c r="I95" s="30" t="n"/>
@@ -5740,17 +5763,16 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="53" t="n"/>
-      <c r="D96" s="53" t="n"/>
-      <c r="E96" s="53" t="n"/>
-      <c r="F96" s="53" t="n"/>
+      <c r="C96" s="40" t="n"/>
+      <c r="D96" s="40" t="n"/>
+      <c r="E96" s="40" t="n"/>
+      <c r="F96" s="40" t="n"/>
       <c r="G96" s="35" t="n"/>
       <c r="H96" s="35" t="n"/>
       <c r="I96" s="30" t="n"/>
       <c r="J96" s="30" t="n"/>
       <c r="K96" s="30" t="n"/>
     </row>
-    <row r="97"/>
   </sheetData>
   <mergeCells count="48">
     <mergeCell ref="F15:F16"/>
@@ -5768,9 +5790,9 @@
     <mergeCell ref="E87:E88"/>
     <mergeCell ref="D75:D76"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="F75:F76"/>
+    <mergeCell ref="B86:F86"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="D87:D88"/>
@@ -5812,11 +5834,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K138"/>
+  <dimension ref="B1:K138"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="9" customWidth="1" style="24" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="24"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
+    <col width="13" customWidth="1" style="24" min="4" max="4"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="13" customWidth="1" style="24" min="6" max="6"/>
     <col width="9" customWidth="1" style="24" min="25" max="16384"/>
   </cols>
   <sheetData>
@@ -5844,17 +5870,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F3" s="72" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -5868,9 +5894,9 @@
     <row r="4" ht="15" customHeight="1" s="24">
       <c r="B4" s="69" t="n"/>
       <c r="C4" s="71" t="n"/>
-      <c r="D4" s="70" t="n"/>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="70" t="n"/>
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
       <c r="G4" s="35" t="n"/>
       <c r="H4" s="35" t="n"/>
       <c r="I4" s="30" t="n"/>
@@ -5899,10 +5925,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="40" t="n"/>
       <c r="G6" s="57" t="n"/>
       <c r="H6" s="57" t="n"/>
       <c r="I6" s="30" t="n"/>
@@ -5980,9 +6006,9 @@
         </is>
       </c>
       <c r="C11" s="40" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="49" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
       <c r="G11" s="57" t="n"/>
       <c r="H11" s="57" t="n"/>
       <c r="I11" s="30" t="n"/>
@@ -5995,10 +6021,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="53" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
       <c r="G12" s="57" t="n"/>
       <c r="H12" s="57" t="n"/>
       <c r="I12" s="30" t="n"/>
@@ -6043,7 +6069,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F15" s="72" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -6059,7 +6085,7 @@
       <c r="C16" s="71" t="n"/>
       <c r="D16" s="71" t="n"/>
       <c r="E16" s="71" t="n"/>
-      <c r="F16" s="70" t="n"/>
+      <c r="F16" s="71" t="n"/>
       <c r="G16" s="35" t="n"/>
       <c r="H16" s="35" t="n"/>
       <c r="I16" s="30" t="n"/>
@@ -6075,7 +6101,7 @@
       <c r="C17" s="40" t="n"/>
       <c r="D17" s="40" t="n"/>
       <c r="E17" s="40" t="n"/>
-      <c r="F17" s="45" t="n"/>
+      <c r="F17" s="40" t="n"/>
       <c r="G17" s="35" t="n"/>
       <c r="H17" s="35" t="n"/>
       <c r="I17" s="30" t="n"/>
@@ -6088,10 +6114,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="45" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
       <c r="G18" s="35" t="n"/>
       <c r="H18" s="35" t="n"/>
       <c r="I18" s="30" t="n"/>
@@ -6168,10 +6194,10 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="49" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
       <c r="G23" s="35" t="n"/>
       <c r="H23" s="35" t="n"/>
       <c r="I23" s="30" t="n"/>
@@ -6184,10 +6210,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="40" t="n"/>
       <c r="G24" s="35" t="n"/>
       <c r="H24" s="35" t="n"/>
       <c r="I24" s="30" t="n"/>
@@ -6222,17 +6248,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D27" s="72" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E27" s="72" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F27" s="72" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -6246,9 +6272,9 @@
     <row r="28" ht="15" customHeight="1" s="24">
       <c r="B28" s="69" t="n"/>
       <c r="C28" s="71" t="n"/>
-      <c r="D28" s="70" t="n"/>
-      <c r="E28" s="70" t="n"/>
-      <c r="F28" s="70" t="n"/>
+      <c r="D28" s="71" t="n"/>
+      <c r="E28" s="71" t="n"/>
+      <c r="F28" s="71" t="n"/>
       <c r="G28" s="35" t="n"/>
       <c r="H28" s="35" t="n"/>
       <c r="I28" s="30" t="n"/>
@@ -6277,10 +6303,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
+      <c r="C30" s="40" t="n"/>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="40" t="n"/>
       <c r="G30" s="57" t="n"/>
       <c r="H30" s="57" t="n"/>
       <c r="I30" s="30" t="n"/>
@@ -6358,9 +6384,9 @@
         </is>
       </c>
       <c r="C35" s="40" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="40" t="n"/>
+      <c r="F35" s="40" t="n"/>
       <c r="G35" s="57" t="n"/>
       <c r="H35" s="57" t="n"/>
       <c r="I35" s="30" t="n"/>
@@ -6373,10 +6399,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
-      <c r="E36" s="53" t="n"/>
-      <c r="F36" s="53" t="n"/>
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
       <c r="G36" s="57" t="n"/>
       <c r="H36" s="57" t="n"/>
       <c r="I36" s="30" t="n"/>
@@ -6421,7 +6447,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F39" s="72" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -6437,7 +6463,7 @@
       <c r="C40" s="71" t="n"/>
       <c r="D40" s="71" t="n"/>
       <c r="E40" s="71" t="n"/>
-      <c r="F40" s="70" t="n"/>
+      <c r="F40" s="71" t="n"/>
       <c r="G40" s="35" t="n"/>
       <c r="H40" s="35" t="n"/>
       <c r="I40" s="30" t="n"/>
@@ -6453,7 +6479,7 @@
       <c r="C41" s="40" t="n"/>
       <c r="D41" s="40" t="n"/>
       <c r="E41" s="40" t="n"/>
-      <c r="F41" s="45" t="n"/>
+      <c r="F41" s="40" t="n"/>
       <c r="G41" s="35" t="n"/>
       <c r="H41" s="35" t="n"/>
       <c r="I41" s="30" t="n"/>
@@ -6466,10 +6492,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="45" t="n"/>
-      <c r="D42" s="45" t="n"/>
-      <c r="E42" s="45" t="n"/>
-      <c r="F42" s="45" t="n"/>
+      <c r="C42" s="40" t="n"/>
+      <c r="D42" s="40" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
       <c r="G42" s="35" t="n"/>
       <c r="H42" s="35" t="n"/>
       <c r="I42" s="30" t="n"/>
@@ -6546,10 +6572,10 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="49" t="n"/>
-      <c r="D47" s="49" t="n"/>
-      <c r="E47" s="49" t="n"/>
-      <c r="F47" s="49" t="n"/>
+      <c r="C47" s="40" t="n"/>
+      <c r="D47" s="40" t="n"/>
+      <c r="E47" s="40" t="n"/>
+      <c r="F47" s="40" t="n"/>
       <c r="G47" s="35" t="n"/>
       <c r="H47" s="35" t="n"/>
       <c r="I47" s="30" t="n"/>
@@ -6562,10 +6588,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
-      <c r="E48" s="53" t="n"/>
-      <c r="F48" s="53" t="n"/>
+      <c r="C48" s="40" t="n"/>
+      <c r="D48" s="40" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
       <c r="G48" s="35" t="n"/>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="30" t="n"/>
@@ -6600,17 +6626,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D51" s="72" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E51" s="72" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F51" s="72" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -6624,9 +6650,9 @@
     <row r="52" ht="15" customHeight="1" s="24">
       <c r="B52" s="69" t="n"/>
       <c r="C52" s="71" t="n"/>
-      <c r="D52" s="70" t="n"/>
-      <c r="E52" s="70" t="n"/>
-      <c r="F52" s="70" t="n"/>
+      <c r="D52" s="71" t="n"/>
+      <c r="E52" s="71" t="n"/>
+      <c r="F52" s="71" t="n"/>
       <c r="G52" s="35" t="n"/>
       <c r="H52" s="35" t="n"/>
       <c r="I52" s="30" t="n"/>
@@ -6655,10 +6681,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="45" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="45" t="n"/>
-      <c r="F54" s="45" t="n"/>
+      <c r="C54" s="40" t="n"/>
+      <c r="D54" s="40" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
       <c r="G54" s="57" t="n"/>
       <c r="H54" s="57" t="n"/>
       <c r="I54" s="30" t="n"/>
@@ -6714,15 +6740,15 @@
       <c r="K57" s="30" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="40" t="n"/>
-      <c r="D58" s="40" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
+      <c r="C58" s="74" t="n"/>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="74" t="n"/>
       <c r="G58" s="57" t="n"/>
       <c r="H58" s="57" t="n"/>
       <c r="I58" s="30" t="n"/>
@@ -6736,9 +6762,9 @@
         </is>
       </c>
       <c r="C59" s="40" t="n"/>
-      <c r="D59" s="49" t="n"/>
-      <c r="E59" s="49" t="n"/>
-      <c r="F59" s="49" t="n"/>
+      <c r="D59" s="40" t="n"/>
+      <c r="E59" s="40" t="n"/>
+      <c r="F59" s="40" t="n"/>
       <c r="G59" s="57" t="n"/>
       <c r="H59" s="57" t="n"/>
       <c r="I59" s="30" t="n"/>
@@ -6751,10 +6777,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
+      <c r="C60" s="40" t="n"/>
+      <c r="D60" s="40" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
       <c r="G60" s="57" t="n"/>
       <c r="H60" s="57" t="n"/>
       <c r="I60" s="30" t="n"/>
@@ -6799,7 +6825,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F63" s="72" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -6815,7 +6841,7 @@
       <c r="C64" s="71" t="n"/>
       <c r="D64" s="71" t="n"/>
       <c r="E64" s="71" t="n"/>
-      <c r="F64" s="70" t="n"/>
+      <c r="F64" s="71" t="n"/>
       <c r="G64" s="35" t="n"/>
       <c r="H64" s="35" t="n"/>
       <c r="I64" s="30" t="n"/>
@@ -6831,7 +6857,7 @@
       <c r="C65" s="40" t="n"/>
       <c r="D65" s="40" t="n"/>
       <c r="E65" s="40" t="n"/>
-      <c r="F65" s="45" t="n"/>
+      <c r="F65" s="40" t="n"/>
       <c r="G65" s="35" t="n"/>
       <c r="H65" s="35" t="n"/>
       <c r="I65" s="30" t="n"/>
@@ -6844,10 +6870,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="45" t="n"/>
-      <c r="D66" s="45" t="n"/>
-      <c r="E66" s="45" t="n"/>
-      <c r="F66" s="45" t="n"/>
+      <c r="C66" s="40" t="n"/>
+      <c r="D66" s="40" t="n"/>
+      <c r="E66" s="40" t="n"/>
+      <c r="F66" s="40" t="n"/>
       <c r="G66" s="35" t="n"/>
       <c r="H66" s="35" t="n"/>
       <c r="I66" s="30" t="n"/>
@@ -6903,15 +6929,15 @@
       <c r="K69" s="30" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="40" t="n"/>
-      <c r="D70" s="40" t="n"/>
-      <c r="E70" s="40" t="n"/>
-      <c r="F70" s="40" t="n"/>
+      <c r="C70" s="74" t="n"/>
+      <c r="D70" s="74" t="n"/>
+      <c r="E70" s="74" t="n"/>
+      <c r="F70" s="74" t="n"/>
       <c r="G70" s="35" t="n"/>
       <c r="H70" s="35" t="n"/>
       <c r="I70" s="30" t="n"/>
@@ -6924,10 +6950,10 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="49" t="n"/>
-      <c r="D71" s="49" t="n"/>
-      <c r="E71" s="49" t="n"/>
-      <c r="F71" s="49" t="n"/>
+      <c r="C71" s="40" t="n"/>
+      <c r="D71" s="40" t="n"/>
+      <c r="E71" s="40" t="n"/>
+      <c r="F71" s="40" t="n"/>
       <c r="G71" s="35" t="n"/>
       <c r="H71" s="35" t="n"/>
       <c r="I71" s="30" t="n"/>
@@ -6940,10 +6966,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="53" t="n"/>
-      <c r="D72" s="53" t="n"/>
-      <c r="E72" s="53" t="n"/>
-      <c r="F72" s="53" t="n"/>
+      <c r="C72" s="40" t="n"/>
+      <c r="D72" s="40" t="n"/>
+      <c r="E72" s="40" t="n"/>
+      <c r="F72" s="40" t="n"/>
       <c r="G72" s="35" t="n"/>
       <c r="H72" s="35" t="n"/>
       <c r="I72" s="30" t="n"/>
@@ -6978,17 +7004,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D75" s="72" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E75" s="72" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F75" s="72" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -7002,9 +7028,9 @@
     <row r="76" ht="15" customHeight="1" s="24">
       <c r="B76" s="69" t="n"/>
       <c r="C76" s="71" t="n"/>
-      <c r="D76" s="70" t="n"/>
-      <c r="E76" s="70" t="n"/>
-      <c r="F76" s="70" t="n"/>
+      <c r="D76" s="71" t="n"/>
+      <c r="E76" s="71" t="n"/>
+      <c r="F76" s="71" t="n"/>
       <c r="G76" s="35" t="n"/>
       <c r="H76" s="35" t="n"/>
       <c r="I76" s="30" t="n"/>
@@ -7033,10 +7059,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="45" t="n"/>
-      <c r="D78" s="45" t="n"/>
-      <c r="E78" s="45" t="n"/>
-      <c r="F78" s="45" t="n"/>
+      <c r="C78" s="40" t="n"/>
+      <c r="D78" s="40" t="n"/>
+      <c r="E78" s="40" t="n"/>
+      <c r="F78" s="40" t="n"/>
       <c r="G78" s="57" t="n"/>
       <c r="H78" s="57" t="n"/>
       <c r="I78" s="30" t="n"/>
@@ -7114,9 +7140,9 @@
         </is>
       </c>
       <c r="C83" s="40" t="n"/>
-      <c r="D83" s="49" t="n"/>
-      <c r="E83" s="49" t="n"/>
-      <c r="F83" s="49" t="n"/>
+      <c r="D83" s="40" t="n"/>
+      <c r="E83" s="40" t="n"/>
+      <c r="F83" s="40" t="n"/>
       <c r="G83" s="57" t="n"/>
       <c r="H83" s="57" t="n"/>
       <c r="I83" s="30" t="n"/>
@@ -7129,10 +7155,10 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="53" t="n"/>
-      <c r="D84" s="53" t="n"/>
-      <c r="E84" s="53" t="n"/>
-      <c r="F84" s="53" t="n"/>
+      <c r="C84" s="40" t="n"/>
+      <c r="D84" s="40" t="n"/>
+      <c r="E84" s="40" t="n"/>
+      <c r="F84" s="40" t="n"/>
       <c r="G84" s="57" t="n"/>
       <c r="H84" s="57" t="n"/>
       <c r="I84" s="30" t="n"/>
@@ -7177,7 +7203,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F87" s="72" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -7193,7 +7219,7 @@
       <c r="C88" s="71" t="n"/>
       <c r="D88" s="71" t="n"/>
       <c r="E88" s="71" t="n"/>
-      <c r="F88" s="70" t="n"/>
+      <c r="F88" s="71" t="n"/>
       <c r="G88" s="35" t="n"/>
       <c r="H88" s="35" t="n"/>
       <c r="I88" s="30" t="n"/>
@@ -7209,7 +7235,7 @@
       <c r="C89" s="40" t="n"/>
       <c r="D89" s="40" t="n"/>
       <c r="E89" s="40" t="n"/>
-      <c r="F89" s="45" t="n"/>
+      <c r="F89" s="40" t="n"/>
       <c r="G89" s="35" t="n"/>
       <c r="H89" s="35" t="n"/>
       <c r="I89" s="30" t="n"/>
@@ -7222,10 +7248,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="45" t="n"/>
-      <c r="D90" s="45" t="n"/>
-      <c r="E90" s="45" t="n"/>
-      <c r="F90" s="45" t="n"/>
+      <c r="C90" s="40" t="n"/>
+      <c r="D90" s="40" t="n"/>
+      <c r="E90" s="40" t="n"/>
+      <c r="F90" s="40" t="n"/>
       <c r="G90" s="35" t="n"/>
       <c r="H90" s="35" t="n"/>
       <c r="I90" s="30" t="n"/>
@@ -7302,10 +7328,10 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="49" t="n"/>
-      <c r="D95" s="49" t="n"/>
-      <c r="E95" s="49" t="n"/>
-      <c r="F95" s="49" t="n"/>
+      <c r="C95" s="40" t="n"/>
+      <c r="D95" s="40" t="n"/>
+      <c r="E95" s="40" t="n"/>
+      <c r="F95" s="40" t="n"/>
       <c r="G95" s="35" t="n"/>
       <c r="H95" s="35" t="n"/>
       <c r="I95" s="30" t="n"/>
@@ -7318,10 +7344,10 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="53" t="n"/>
-      <c r="D96" s="53" t="n"/>
-      <c r="E96" s="53" t="n"/>
-      <c r="F96" s="53" t="n"/>
+      <c r="C96" s="40" t="n"/>
+      <c r="D96" s="40" t="n"/>
+      <c r="E96" s="40" t="n"/>
+      <c r="F96" s="40" t="n"/>
       <c r="G96" s="35" t="n"/>
       <c r="H96" s="35" t="n"/>
       <c r="I96" s="30" t="n"/>
@@ -7842,9 +7868,9 @@
     <mergeCell ref="E87:E88"/>
     <mergeCell ref="D75:D76"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="F75:F76"/>
+    <mergeCell ref="B86:F86"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="D87:D88"/>
@@ -7886,7 +7912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="B1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="23"/>
@@ -8023,12 +8049,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="B1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="15.1284403669725" customWidth="1" style="24" min="2" max="2"/>
     <col width="16.8715596330275" customWidth="1" style="24" min="3" max="3"/>
     <col width="16.7522935779816" customWidth="1" style="24" min="4" max="16"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="13" customWidth="1" style="24" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="24"/>
@@ -8052,17 +8080,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F3" s="72" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -8073,113 +8101,113 @@
     <row r="4" ht="15" customHeight="1" s="24">
       <c r="B4" s="69" t="n"/>
       <c r="C4" s="71" t="n"/>
-      <c r="D4" s="70" t="n"/>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="70" t="n"/>
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
       <c r="G4" s="35" t="n"/>
       <c r="H4" s="35" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="73" t="inlineStr">
         <is>
           <t>Nov_2015</t>
         </is>
       </c>
-      <c r="C5" s="40" t="n"/>
-      <c r="D5" s="40" t="n"/>
-      <c r="E5" s="40" t="n"/>
-      <c r="F5" s="40" t="n"/>
+      <c r="C5" s="74" t="n"/>
+      <c r="D5" s="74" t="n"/>
+      <c r="E5" s="74" t="n"/>
+      <c r="F5" s="74" t="n"/>
       <c r="G5" s="57" t="n"/>
       <c r="H5" s="57" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="75" t="inlineStr">
         <is>
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
+      <c r="C6" s="74" t="n"/>
+      <c r="D6" s="74" t="n"/>
+      <c r="E6" s="74" t="n"/>
+      <c r="F6" s="74" t="n"/>
       <c r="G6" s="57" t="n"/>
       <c r="H6" s="57" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="73" t="inlineStr">
         <is>
           <t>Nov_2017</t>
         </is>
       </c>
-      <c r="C7" s="40" t="n"/>
-      <c r="D7" s="40" t="n"/>
-      <c r="E7" s="40" t="n"/>
-      <c r="F7" s="40" t="n"/>
+      <c r="C7" s="74" t="n"/>
+      <c r="D7" s="74" t="n"/>
+      <c r="E7" s="74" t="n"/>
+      <c r="F7" s="74" t="n"/>
       <c r="G7" s="57" t="n"/>
       <c r="H7" s="57" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="73" t="inlineStr">
         <is>
           <t>Nov_2018</t>
         </is>
       </c>
-      <c r="C8" s="40" t="n"/>
-      <c r="D8" s="40" t="n"/>
-      <c r="E8" s="40" t="n"/>
-      <c r="F8" s="40" t="n"/>
+      <c r="C8" s="74" t="n"/>
+      <c r="D8" s="74" t="n"/>
+      <c r="E8" s="74" t="n"/>
+      <c r="F8" s="74" t="n"/>
       <c r="G8" s="57" t="n"/>
       <c r="H8" s="57" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="73" t="inlineStr">
         <is>
           <t>Nov_2019</t>
         </is>
       </c>
-      <c r="C9" s="40" t="n"/>
-      <c r="D9" s="40" t="n"/>
-      <c r="E9" s="40" t="n"/>
-      <c r="F9" s="40" t="n"/>
+      <c r="C9" s="74" t="n"/>
+      <c r="D9" s="74" t="n"/>
+      <c r="E9" s="74" t="n"/>
+      <c r="F9" s="74" t="n"/>
       <c r="G9" s="57" t="n"/>
       <c r="H9" s="57" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="73" t="inlineStr">
         <is>
           <t>Nov_2020</t>
         </is>
       </c>
-      <c r="C10" s="40" t="n"/>
-      <c r="D10" s="40" t="n"/>
-      <c r="E10" s="40" t="n"/>
-      <c r="F10" s="40" t="n"/>
+      <c r="C10" s="74" t="n"/>
+      <c r="D10" s="74" t="n"/>
+      <c r="E10" s="74" t="n"/>
+      <c r="F10" s="74" t="n"/>
       <c r="G10" s="57" t="n"/>
       <c r="H10" s="57" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="73" t="inlineStr">
         <is>
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C11" s="40" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="49" t="n"/>
+      <c r="C11" s="74" t="n"/>
+      <c r="D11" s="74" t="n"/>
+      <c r="E11" s="74" t="n"/>
+      <c r="F11" s="74" t="n"/>
       <c r="G11" s="57" t="n"/>
       <c r="H11" s="57" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="24">
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="76" t="inlineStr">
         <is>
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="53" t="n"/>
+      <c r="C12" s="74" t="n"/>
+      <c r="D12" s="74" t="n"/>
+      <c r="E12" s="74" t="n"/>
+      <c r="F12" s="74" t="n"/>
       <c r="G12" s="57" t="n"/>
       <c r="H12" s="57" t="n"/>
     </row>
@@ -8214,7 +8242,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F15" s="72" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -8227,115 +8255,114 @@
       <c r="C16" s="71" t="n"/>
       <c r="D16" s="71" t="n"/>
       <c r="E16" s="71" t="n"/>
-      <c r="F16" s="70" t="n"/>
+      <c r="F16" s="71" t="n"/>
       <c r="G16" s="35" t="n"/>
       <c r="H16" s="35" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="73" t="inlineStr">
         <is>
           <t>Nov_2015</t>
         </is>
       </c>
-      <c r="C17" s="40" t="n"/>
-      <c r="D17" s="40" t="n"/>
-      <c r="E17" s="40" t="n"/>
-      <c r="F17" s="45" t="n"/>
+      <c r="C17" s="74" t="n"/>
+      <c r="D17" s="74" t="n"/>
+      <c r="E17" s="74" t="n"/>
+      <c r="F17" s="74" t="n"/>
       <c r="G17" s="35" t="n"/>
       <c r="H17" s="35" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="75" t="inlineStr">
         <is>
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="45" t="n"/>
+      <c r="C18" s="74" t="n"/>
+      <c r="D18" s="74" t="n"/>
+      <c r="E18" s="74" t="n"/>
+      <c r="F18" s="74" t="n"/>
       <c r="G18" s="35" t="n"/>
       <c r="H18" s="35" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="73" t="inlineStr">
         <is>
           <t>Nov_2017</t>
         </is>
       </c>
-      <c r="C19" s="40" t="n"/>
-      <c r="D19" s="40" t="n"/>
-      <c r="E19" s="40" t="n"/>
-      <c r="F19" s="40" t="n"/>
+      <c r="C19" s="74" t="n"/>
+      <c r="D19" s="74" t="n"/>
+      <c r="E19" s="74" t="n"/>
+      <c r="F19" s="74" t="n"/>
       <c r="G19" s="35" t="n"/>
       <c r="H19" s="35" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="73" t="inlineStr">
         <is>
           <t>Nov_2018</t>
         </is>
       </c>
-      <c r="C20" s="40" t="n"/>
-      <c r="D20" s="40" t="n"/>
-      <c r="E20" s="40" t="n"/>
-      <c r="F20" s="40" t="n"/>
+      <c r="C20" s="74" t="n"/>
+      <c r="D20" s="74" t="n"/>
+      <c r="E20" s="74" t="n"/>
+      <c r="F20" s="74" t="n"/>
       <c r="G20" s="35" t="n"/>
       <c r="H20" s="35" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="73" t="inlineStr">
         <is>
           <t>Nov_2019</t>
         </is>
       </c>
-      <c r="C21" s="40" t="n"/>
-      <c r="D21" s="40" t="n"/>
-      <c r="E21" s="40" t="n"/>
-      <c r="F21" s="40" t="n"/>
+      <c r="C21" s="74" t="n"/>
+      <c r="D21" s="74" t="n"/>
+      <c r="E21" s="74" t="n"/>
+      <c r="F21" s="74" t="n"/>
       <c r="G21" s="35" t="n"/>
       <c r="H21" s="35" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="73" t="inlineStr">
         <is>
           <t>Nov_2020</t>
         </is>
       </c>
-      <c r="C22" s="40" t="n"/>
-      <c r="D22" s="40" t="n"/>
-      <c r="E22" s="40" t="n"/>
-      <c r="F22" s="40" t="n"/>
+      <c r="C22" s="74" t="n"/>
+      <c r="D22" s="74" t="n"/>
+      <c r="E22" s="74" t="n"/>
+      <c r="F22" s="74" t="n"/>
       <c r="G22" s="35" t="n"/>
       <c r="H22" s="35" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="73" t="inlineStr">
         <is>
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="49" t="n"/>
+      <c r="C23" s="74" t="n"/>
+      <c r="D23" s="74" t="n"/>
+      <c r="E23" s="74" t="n"/>
+      <c r="F23" s="74" t="n"/>
       <c r="G23" s="35" t="n"/>
       <c r="H23" s="35" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="24">
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="76" t="inlineStr">
         <is>
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
+      <c r="C24" s="74" t="n"/>
+      <c r="D24" s="74" t="n"/>
+      <c r="E24" s="74" t="n"/>
+      <c r="F24" s="74" t="n"/>
       <c r="G24" s="35" t="n"/>
       <c r="H24" s="35" t="n"/>
     </row>
-    <row r="25"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="F15:F16"/>
@@ -8346,8 +8373,8 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E15:E16"/>
     <mergeCell ref="C15:C16"/>
-    <mergeCell ref="E15:E16"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:B16"/>
   </mergeCells>
@@ -8392,17 +8419,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F3" s="72" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -8411,9 +8438,9 @@
     <row r="4" ht="15" customHeight="1" s="24">
       <c r="B4" s="69" t="n"/>
       <c r="C4" s="71" t="n"/>
-      <c r="D4" s="70" t="n"/>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="70" t="n"/>
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
     </row>
     <row r="5" ht="14.95" customHeight="1" s="24">
       <c r="B5" s="16" t="inlineStr">
@@ -8432,10 +8459,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="40" t="n"/>
     </row>
     <row r="7" ht="14.95" customHeight="1" s="24">
       <c r="B7" s="16" t="inlineStr">
@@ -8488,9 +8515,9 @@
         </is>
       </c>
       <c r="C11" s="40" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="49" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
     </row>
     <row r="12" ht="14.95" customHeight="1" s="24">
       <c r="B12" s="22" t="inlineStr">
@@ -8498,10 +8525,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="53" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="24"/>
     <row r="14" ht="15" customHeight="1" s="24">
@@ -8532,7 +8559,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F15" s="72" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -8543,7 +8570,7 @@
       <c r="C16" s="71" t="n"/>
       <c r="D16" s="71" t="n"/>
       <c r="E16" s="71" t="n"/>
-      <c r="F16" s="70" t="n"/>
+      <c r="F16" s="71" t="n"/>
     </row>
     <row r="17" ht="14.95" customHeight="1" s="24">
       <c r="B17" s="16" t="inlineStr">
@@ -8554,7 +8581,7 @@
       <c r="C17" s="40" t="n"/>
       <c r="D17" s="40" t="n"/>
       <c r="E17" s="40" t="n"/>
-      <c r="F17" s="45" t="n"/>
+      <c r="F17" s="40" t="n"/>
     </row>
     <row r="18" ht="14.95" customHeight="1" s="24">
       <c r="B18" s="19" t="inlineStr">
@@ -8562,10 +8589,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="45" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
     </row>
     <row r="19" ht="14.95" customHeight="1" s="24">
       <c r="B19" s="16" t="inlineStr">
@@ -8617,10 +8644,10 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="49" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
     </row>
     <row r="24" ht="14.95" customHeight="1" s="24">
       <c r="B24" s="22" t="inlineStr">
@@ -8628,10 +8655,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="40" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="24"/>
     <row r="26" ht="15" customHeight="1" s="24">
@@ -8652,17 +8679,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D27" s="72" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E27" s="72" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F27" s="72" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -8671,97 +8698,97 @@
     <row r="28" ht="15" customHeight="1" s="24">
       <c r="B28" s="69" t="n"/>
       <c r="C28" s="71" t="n"/>
-      <c r="D28" s="70" t="n"/>
-      <c r="E28" s="70" t="n"/>
-      <c r="F28" s="70" t="n"/>
+      <c r="D28" s="71" t="n"/>
+      <c r="E28" s="71" t="n"/>
+      <c r="F28" s="71" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="73" t="inlineStr">
         <is>
           <t>Sept_2015</t>
         </is>
       </c>
-      <c r="C29" s="40" t="n"/>
-      <c r="D29" s="40" t="n"/>
-      <c r="E29" s="40" t="n"/>
-      <c r="F29" s="40" t="n"/>
+      <c r="C29" s="74" t="n"/>
+      <c r="D29" s="74" t="n"/>
+      <c r="E29" s="74" t="n"/>
+      <c r="F29" s="74" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="73" t="inlineStr">
         <is>
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
+      <c r="C30" s="74" t="n"/>
+      <c r="D30" s="74" t="n"/>
+      <c r="E30" s="74" t="n"/>
+      <c r="F30" s="74" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="73" t="inlineStr">
         <is>
           <t>Sept_2017</t>
         </is>
       </c>
-      <c r="C31" s="40" t="n"/>
-      <c r="D31" s="40" t="n"/>
-      <c r="E31" s="40" t="n"/>
-      <c r="F31" s="40" t="n"/>
+      <c r="C31" s="74" t="n"/>
+      <c r="D31" s="74" t="n"/>
+      <c r="E31" s="74" t="n"/>
+      <c r="F31" s="74" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="73" t="inlineStr">
         <is>
           <t>Sept_2018</t>
         </is>
       </c>
-      <c r="C32" s="40" t="n"/>
-      <c r="D32" s="40" t="n"/>
-      <c r="E32" s="40" t="n"/>
-      <c r="F32" s="40" t="n"/>
+      <c r="C32" s="74" t="n"/>
+      <c r="D32" s="74" t="n"/>
+      <c r="E32" s="74" t="n"/>
+      <c r="F32" s="74" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="73" t="inlineStr">
         <is>
           <t>Sept_2019</t>
         </is>
       </c>
-      <c r="C33" s="40" t="n"/>
-      <c r="D33" s="40" t="n"/>
-      <c r="E33" s="40" t="n"/>
-      <c r="F33" s="40" t="n"/>
+      <c r="C33" s="74" t="n"/>
+      <c r="D33" s="74" t="n"/>
+      <c r="E33" s="74" t="n"/>
+      <c r="F33" s="74" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="73" t="inlineStr">
         <is>
           <t>Sept_2020</t>
         </is>
       </c>
-      <c r="C34" s="40" t="n"/>
-      <c r="D34" s="40" t="n"/>
-      <c r="E34" s="40" t="n"/>
-      <c r="F34" s="40" t="n"/>
+      <c r="C34" s="74" t="n"/>
+      <c r="D34" s="74" t="n"/>
+      <c r="E34" s="74" t="n"/>
+      <c r="F34" s="74" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="73" t="inlineStr">
         <is>
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C35" s="40" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
+      <c r="C35" s="74" t="n"/>
+      <c r="D35" s="74" t="n"/>
+      <c r="E35" s="74" t="n"/>
+      <c r="F35" s="74" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="24">
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="76" t="inlineStr">
         <is>
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
-      <c r="E36" s="53" t="n"/>
-      <c r="F36" s="53" t="n"/>
+      <c r="C36" s="74" t="n"/>
+      <c r="D36" s="74" t="n"/>
+      <c r="E36" s="74" t="n"/>
+      <c r="F36" s="74" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="24"/>
     <row r="38" ht="15" customHeight="1" s="24">
@@ -8792,7 +8819,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F39" s="72" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -8803,95 +8830,95 @@
       <c r="C40" s="71" t="n"/>
       <c r="D40" s="71" t="n"/>
       <c r="E40" s="71" t="n"/>
-      <c r="F40" s="70" t="n"/>
+      <c r="F40" s="71" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="73" t="inlineStr">
         <is>
           <t>Sept_2015</t>
         </is>
       </c>
-      <c r="C41" s="40" t="n"/>
-      <c r="D41" s="40" t="n"/>
-      <c r="E41" s="40" t="n"/>
-      <c r="F41" s="45" t="n"/>
+      <c r="C41" s="74" t="n"/>
+      <c r="D41" s="74" t="n"/>
+      <c r="E41" s="74" t="n"/>
+      <c r="F41" s="74" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B42" s="73" t="inlineStr">
         <is>
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="45" t="n"/>
-      <c r="D42" s="45" t="n"/>
-      <c r="E42" s="45" t="n"/>
-      <c r="F42" s="45" t="n"/>
+      <c r="C42" s="74" t="n"/>
+      <c r="D42" s="74" t="n"/>
+      <c r="E42" s="74" t="n"/>
+      <c r="F42" s="74" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B43" s="73" t="inlineStr">
         <is>
           <t>Sept_2017</t>
         </is>
       </c>
-      <c r="C43" s="40" t="n"/>
-      <c r="D43" s="40" t="n"/>
-      <c r="E43" s="40" t="n"/>
-      <c r="F43" s="40" t="n"/>
+      <c r="C43" s="74" t="n"/>
+      <c r="D43" s="74" t="n"/>
+      <c r="E43" s="74" t="n"/>
+      <c r="F43" s="74" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B44" s="73" t="inlineStr">
         <is>
           <t>Sept_2018</t>
         </is>
       </c>
-      <c r="C44" s="40" t="n"/>
-      <c r="D44" s="40" t="n"/>
-      <c r="E44" s="40" t="n"/>
-      <c r="F44" s="40" t="n"/>
+      <c r="C44" s="74" t="n"/>
+      <c r="D44" s="74" t="n"/>
+      <c r="E44" s="74" t="n"/>
+      <c r="F44" s="74" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B45" s="73" t="inlineStr">
         <is>
           <t>Sept_2019</t>
         </is>
       </c>
-      <c r="C45" s="40" t="n"/>
-      <c r="D45" s="40" t="n"/>
-      <c r="E45" s="40" t="n"/>
-      <c r="F45" s="40" t="n"/>
+      <c r="C45" s="74" t="n"/>
+      <c r="D45" s="74" t="n"/>
+      <c r="E45" s="74" t="n"/>
+      <c r="F45" s="74" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="73" t="inlineStr">
         <is>
           <t>Sept_2020</t>
         </is>
       </c>
-      <c r="C46" s="40" t="n"/>
-      <c r="D46" s="40" t="n"/>
-      <c r="E46" s="40" t="n"/>
-      <c r="F46" s="40" t="n"/>
+      <c r="C46" s="74" t="n"/>
+      <c r="D46" s="74" t="n"/>
+      <c r="E46" s="74" t="n"/>
+      <c r="F46" s="74" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="73" t="inlineStr">
         <is>
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="49" t="n"/>
-      <c r="D47" s="49" t="n"/>
-      <c r="E47" s="49" t="n"/>
-      <c r="F47" s="49" t="n"/>
+      <c r="C47" s="74" t="n"/>
+      <c r="D47" s="74" t="n"/>
+      <c r="E47" s="74" t="n"/>
+      <c r="F47" s="74" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="24">
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="76" t="inlineStr">
         <is>
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
-      <c r="E48" s="53" t="n"/>
-      <c r="F48" s="53" t="n"/>
+      <c r="C48" s="74" t="n"/>
+      <c r="D48" s="74" t="n"/>
+      <c r="E48" s="74" t="n"/>
+      <c r="F48" s="74" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="24"/>
     <row r="50" ht="15" customHeight="1" s="24">
@@ -8912,17 +8939,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D51" s="72" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E51" s="72" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F51" s="72" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -8931,97 +8958,97 @@
     <row r="52" ht="15" customHeight="1" s="24">
       <c r="B52" s="69" t="n"/>
       <c r="C52" s="71" t="n"/>
-      <c r="D52" s="70" t="n"/>
-      <c r="E52" s="70" t="n"/>
-      <c r="F52" s="70" t="n"/>
+      <c r="D52" s="71" t="n"/>
+      <c r="E52" s="71" t="n"/>
+      <c r="F52" s="71" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B53" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2015</t>
         </is>
       </c>
-      <c r="C53" s="40" t="n"/>
-      <c r="D53" s="40" t="n"/>
-      <c r="E53" s="40" t="n"/>
-      <c r="F53" s="40" t="n"/>
+      <c r="C53" s="74" t="n"/>
+      <c r="D53" s="74" t="n"/>
+      <c r="E53" s="74" t="n"/>
+      <c r="F53" s="74" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B54" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="45" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="45" t="n"/>
-      <c r="F54" s="45" t="n"/>
+      <c r="C54" s="74" t="n"/>
+      <c r="D54" s="74" t="n"/>
+      <c r="E54" s="74" t="n"/>
+      <c r="F54" s="74" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="16" t="inlineStr">
+      <c r="B55" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2017</t>
         </is>
       </c>
-      <c r="C55" s="40" t="n"/>
-      <c r="D55" s="40" t="n"/>
-      <c r="E55" s="40" t="n"/>
-      <c r="F55" s="40" t="n"/>
+      <c r="C55" s="74" t="n"/>
+      <c r="D55" s="74" t="n"/>
+      <c r="E55" s="74" t="n"/>
+      <c r="F55" s="74" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="16" t="inlineStr">
+      <c r="B56" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2018</t>
         </is>
       </c>
-      <c r="C56" s="40" t="n"/>
-      <c r="D56" s="40" t="n"/>
-      <c r="E56" s="40" t="n"/>
-      <c r="F56" s="40" t="n"/>
+      <c r="C56" s="74" t="n"/>
+      <c r="D56" s="74" t="n"/>
+      <c r="E56" s="74" t="n"/>
+      <c r="F56" s="74" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="16" t="inlineStr">
+      <c r="B57" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2019</t>
         </is>
       </c>
-      <c r="C57" s="40" t="n"/>
-      <c r="D57" s="40" t="n"/>
-      <c r="E57" s="40" t="n"/>
-      <c r="F57" s="40" t="n"/>
+      <c r="C57" s="74" t="n"/>
+      <c r="D57" s="74" t="n"/>
+      <c r="E57" s="74" t="n"/>
+      <c r="F57" s="74" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="40" t="n"/>
-      <c r="D58" s="40" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
+      <c r="C58" s="74" t="n"/>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="74" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="16" t="inlineStr">
+      <c r="B59" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C59" s="40" t="n"/>
-      <c r="D59" s="49" t="n"/>
-      <c r="E59" s="49" t="n"/>
-      <c r="F59" s="49" t="n"/>
+      <c r="C59" s="74" t="n"/>
+      <c r="D59" s="74" t="n"/>
+      <c r="E59" s="74" t="n"/>
+      <c r="F59" s="74" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="24">
-      <c r="B60" s="22" t="inlineStr">
+      <c r="B60" s="76" t="inlineStr">
         <is>
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
+      <c r="C60" s="74" t="n"/>
+      <c r="D60" s="74" t="n"/>
+      <c r="E60" s="74" t="n"/>
+      <c r="F60" s="74" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1" s="24"/>
     <row r="62" ht="15" customHeight="1" s="24">
@@ -9052,7 +9079,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F63" s="72" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -9063,95 +9090,95 @@
       <c r="C64" s="71" t="n"/>
       <c r="D64" s="71" t="n"/>
       <c r="E64" s="71" t="n"/>
-      <c r="F64" s="70" t="n"/>
+      <c r="F64" s="71" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" s="16" t="inlineStr">
+      <c r="B65" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2015</t>
         </is>
       </c>
-      <c r="C65" s="40" t="n"/>
-      <c r="D65" s="40" t="n"/>
-      <c r="E65" s="40" t="n"/>
-      <c r="F65" s="45" t="n"/>
+      <c r="C65" s="74" t="n"/>
+      <c r="D65" s="74" t="n"/>
+      <c r="E65" s="74" t="n"/>
+      <c r="F65" s="74" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="16" t="inlineStr">
+      <c r="B66" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="45" t="n"/>
-      <c r="D66" s="45" t="n"/>
-      <c r="E66" s="45" t="n"/>
-      <c r="F66" s="45" t="n"/>
+      <c r="C66" s="74" t="n"/>
+      <c r="D66" s="74" t="n"/>
+      <c r="E66" s="74" t="n"/>
+      <c r="F66" s="74" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="16" t="inlineStr">
+      <c r="B67" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2017</t>
         </is>
       </c>
-      <c r="C67" s="40" t="n"/>
-      <c r="D67" s="40" t="n"/>
-      <c r="E67" s="40" t="n"/>
-      <c r="F67" s="40" t="n"/>
+      <c r="C67" s="74" t="n"/>
+      <c r="D67" s="74" t="n"/>
+      <c r="E67" s="74" t="n"/>
+      <c r="F67" s="74" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="16" t="inlineStr">
+      <c r="B68" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2018</t>
         </is>
       </c>
-      <c r="C68" s="40" t="n"/>
-      <c r="D68" s="40" t="n"/>
-      <c r="E68" s="40" t="n"/>
-      <c r="F68" s="40" t="n"/>
+      <c r="C68" s="74" t="n"/>
+      <c r="D68" s="74" t="n"/>
+      <c r="E68" s="74" t="n"/>
+      <c r="F68" s="74" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="16" t="inlineStr">
+      <c r="B69" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2019</t>
         </is>
       </c>
-      <c r="C69" s="40" t="n"/>
-      <c r="D69" s="40" t="n"/>
-      <c r="E69" s="40" t="n"/>
-      <c r="F69" s="40" t="n"/>
+      <c r="C69" s="74" t="n"/>
+      <c r="D69" s="74" t="n"/>
+      <c r="E69" s="74" t="n"/>
+      <c r="F69" s="74" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="40" t="n"/>
-      <c r="D70" s="40" t="n"/>
-      <c r="E70" s="40" t="n"/>
-      <c r="F70" s="40" t="n"/>
+      <c r="C70" s="74" t="n"/>
+      <c r="D70" s="74" t="n"/>
+      <c r="E70" s="74" t="n"/>
+      <c r="F70" s="74" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="16" t="inlineStr">
+      <c r="B71" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="49" t="n"/>
-      <c r="D71" s="49" t="n"/>
-      <c r="E71" s="49" t="n"/>
-      <c r="F71" s="49" t="n"/>
+      <c r="C71" s="74" t="n"/>
+      <c r="D71" s="74" t="n"/>
+      <c r="E71" s="74" t="n"/>
+      <c r="F71" s="74" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" s="24">
-      <c r="B72" s="22" t="inlineStr">
+      <c r="B72" s="76" t="inlineStr">
         <is>
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="53" t="n"/>
-      <c r="D72" s="53" t="n"/>
-      <c r="E72" s="53" t="n"/>
-      <c r="F72" s="53" t="n"/>
+      <c r="C72" s="74" t="n"/>
+      <c r="D72" s="74" t="n"/>
+      <c r="E72" s="74" t="n"/>
+      <c r="F72" s="74" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="24"/>
     <row r="74" ht="15" customHeight="1" s="24">
@@ -9172,17 +9199,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D75" s="72" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E75" s="72" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F75" s="72" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -9191,97 +9218,97 @@
     <row r="76" ht="15" customHeight="1" s="24">
       <c r="B76" s="69" t="n"/>
       <c r="C76" s="71" t="n"/>
-      <c r="D76" s="70" t="n"/>
-      <c r="E76" s="70" t="n"/>
-      <c r="F76" s="70" t="n"/>
+      <c r="D76" s="71" t="n"/>
+      <c r="E76" s="71" t="n"/>
+      <c r="F76" s="71" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="16" t="inlineStr">
+      <c r="B77" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2015</t>
         </is>
       </c>
-      <c r="C77" s="40" t="n"/>
-      <c r="D77" s="40" t="n"/>
-      <c r="E77" s="40" t="n"/>
-      <c r="F77" s="40" t="n"/>
+      <c r="C77" s="74" t="n"/>
+      <c r="D77" s="74" t="n"/>
+      <c r="E77" s="74" t="n"/>
+      <c r="F77" s="74" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="16" t="inlineStr">
+      <c r="B78" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="45" t="n"/>
-      <c r="D78" s="45" t="n"/>
-      <c r="E78" s="45" t="n"/>
-      <c r="F78" s="45" t="n"/>
+      <c r="C78" s="74" t="n"/>
+      <c r="D78" s="74" t="n"/>
+      <c r="E78" s="74" t="n"/>
+      <c r="F78" s="74" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="16" t="inlineStr">
+      <c r="B79" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2017</t>
         </is>
       </c>
-      <c r="C79" s="40" t="n"/>
-      <c r="D79" s="40" t="n"/>
-      <c r="E79" s="40" t="n"/>
-      <c r="F79" s="40" t="n"/>
+      <c r="C79" s="74" t="n"/>
+      <c r="D79" s="74" t="n"/>
+      <c r="E79" s="74" t="n"/>
+      <c r="F79" s="74" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" s="16" t="inlineStr">
+      <c r="B80" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2018</t>
         </is>
       </c>
-      <c r="C80" s="40" t="n"/>
-      <c r="D80" s="40" t="n"/>
-      <c r="E80" s="40" t="n"/>
-      <c r="F80" s="40" t="n"/>
+      <c r="C80" s="74" t="n"/>
+      <c r="D80" s="74" t="n"/>
+      <c r="E80" s="74" t="n"/>
+      <c r="F80" s="74" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" s="16" t="inlineStr">
+      <c r="B81" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2019</t>
         </is>
       </c>
-      <c r="C81" s="40" t="n"/>
-      <c r="D81" s="40" t="n"/>
-      <c r="E81" s="40" t="n"/>
-      <c r="F81" s="40" t="n"/>
+      <c r="C81" s="74" t="n"/>
+      <c r="D81" s="74" t="n"/>
+      <c r="E81" s="74" t="n"/>
+      <c r="F81" s="74" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="16" t="inlineStr">
+      <c r="B82" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2020</t>
         </is>
       </c>
-      <c r="C82" s="40" t="n"/>
-      <c r="D82" s="40" t="n"/>
-      <c r="E82" s="40" t="n"/>
-      <c r="F82" s="40" t="n"/>
+      <c r="C82" s="74" t="n"/>
+      <c r="D82" s="74" t="n"/>
+      <c r="E82" s="74" t="n"/>
+      <c r="F82" s="74" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" s="16" t="inlineStr">
+      <c r="B83" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C83" s="40" t="n"/>
-      <c r="D83" s="49" t="n"/>
-      <c r="E83" s="49" t="n"/>
-      <c r="F83" s="49" t="n"/>
+      <c r="C83" s="74" t="n"/>
+      <c r="D83" s="74" t="n"/>
+      <c r="E83" s="74" t="n"/>
+      <c r="F83" s="74" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1" s="24">
-      <c r="B84" s="22" t="inlineStr">
+      <c r="B84" s="76" t="inlineStr">
         <is>
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="53" t="n"/>
-      <c r="D84" s="53" t="n"/>
-      <c r="E84" s="53" t="n"/>
-      <c r="F84" s="53" t="n"/>
+      <c r="C84" s="74" t="n"/>
+      <c r="D84" s="74" t="n"/>
+      <c r="E84" s="74" t="n"/>
+      <c r="F84" s="74" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1" s="24"/>
     <row r="86" ht="15" customHeight="1" s="24">
@@ -9312,7 +9339,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F87" s="72" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -9323,95 +9350,95 @@
       <c r="C88" s="71" t="n"/>
       <c r="D88" s="71" t="n"/>
       <c r="E88" s="71" t="n"/>
-      <c r="F88" s="70" t="n"/>
+      <c r="F88" s="71" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="16" t="inlineStr">
+      <c r="B89" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2015</t>
         </is>
       </c>
-      <c r="C89" s="40" t="n"/>
-      <c r="D89" s="40" t="n"/>
-      <c r="E89" s="40" t="n"/>
-      <c r="F89" s="45" t="n"/>
+      <c r="C89" s="74" t="n"/>
+      <c r="D89" s="74" t="n"/>
+      <c r="E89" s="74" t="n"/>
+      <c r="F89" s="74" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="16" t="inlineStr">
+      <c r="B90" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="45" t="n"/>
-      <c r="D90" s="45" t="n"/>
-      <c r="E90" s="45" t="n"/>
-      <c r="F90" s="45" t="n"/>
+      <c r="C90" s="74" t="n"/>
+      <c r="D90" s="74" t="n"/>
+      <c r="E90" s="74" t="n"/>
+      <c r="F90" s="74" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="16" t="inlineStr">
+      <c r="B91" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2017</t>
         </is>
       </c>
-      <c r="C91" s="40" t="n"/>
-      <c r="D91" s="40" t="n"/>
-      <c r="E91" s="40" t="n"/>
-      <c r="F91" s="40" t="n"/>
+      <c r="C91" s="74" t="n"/>
+      <c r="D91" s="74" t="n"/>
+      <c r="E91" s="74" t="n"/>
+      <c r="F91" s="74" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="16" t="inlineStr">
+      <c r="B92" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2018</t>
         </is>
       </c>
-      <c r="C92" s="40" t="n"/>
-      <c r="D92" s="40" t="n"/>
-      <c r="E92" s="40" t="n"/>
-      <c r="F92" s="40" t="n"/>
+      <c r="C92" s="74" t="n"/>
+      <c r="D92" s="74" t="n"/>
+      <c r="E92" s="74" t="n"/>
+      <c r="F92" s="74" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="16" t="inlineStr">
+      <c r="B93" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2019</t>
         </is>
       </c>
-      <c r="C93" s="40" t="n"/>
-      <c r="D93" s="40" t="n"/>
-      <c r="E93" s="40" t="n"/>
-      <c r="F93" s="40" t="n"/>
+      <c r="C93" s="74" t="n"/>
+      <c r="D93" s="74" t="n"/>
+      <c r="E93" s="74" t="n"/>
+      <c r="F93" s="74" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="16" t="inlineStr">
+      <c r="B94" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2020</t>
         </is>
       </c>
-      <c r="C94" s="40" t="n"/>
-      <c r="D94" s="40" t="n"/>
-      <c r="E94" s="40" t="n"/>
-      <c r="F94" s="40" t="n"/>
+      <c r="C94" s="74" t="n"/>
+      <c r="D94" s="74" t="n"/>
+      <c r="E94" s="74" t="n"/>
+      <c r="F94" s="74" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="16" t="inlineStr">
+      <c r="B95" s="73" t="inlineStr">
         <is>
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="49" t="n"/>
-      <c r="D95" s="49" t="n"/>
-      <c r="E95" s="49" t="n"/>
-      <c r="F95" s="49" t="n"/>
+      <c r="C95" s="74" t="n"/>
+      <c r="D95" s="74" t="n"/>
+      <c r="E95" s="74" t="n"/>
+      <c r="F95" s="74" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1" s="24">
-      <c r="B96" s="22" t="inlineStr">
+      <c r="B96" s="76" t="inlineStr">
         <is>
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="53" t="n"/>
-      <c r="D96" s="53" t="n"/>
-      <c r="E96" s="53" t="n"/>
-      <c r="F96" s="53" t="n"/>
+      <c r="C96" s="74" t="n"/>
+      <c r="D96" s="74" t="n"/>
+      <c r="E96" s="74" t="n"/>
+      <c r="F96" s="74" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="48">
@@ -9430,9 +9457,9 @@
     <mergeCell ref="E87:E88"/>
     <mergeCell ref="D75:D76"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="F75:F76"/>
+    <mergeCell ref="B86:F86"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="D87:D88"/>
@@ -9474,11 +9501,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="B1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.12844036697248" customWidth="1" style="24" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="24" min="2" max="25"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
+    <col width="13" customWidth="1" style="24" min="4" max="4"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="13" customWidth="1" style="24" min="6" max="6"/>
     <col width="9.12844036697248" customWidth="1" style="24" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -9501,17 +9532,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F3" s="72" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -9520,9 +9551,9 @@
     <row r="4" ht="15" customHeight="1" s="24">
       <c r="B4" s="69" t="n"/>
       <c r="C4" s="71" t="n"/>
-      <c r="D4" s="70" t="n"/>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="70" t="n"/>
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="16" t="inlineStr">
@@ -9541,10 +9572,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="40" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="16" t="inlineStr">
@@ -9597,9 +9628,9 @@
         </is>
       </c>
       <c r="C11" s="40" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="49" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="24">
       <c r="B12" s="22" t="inlineStr">
@@ -9607,10 +9638,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="53" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="24"/>
     <row r="14" ht="15" customHeight="1" s="24">
@@ -9641,7 +9672,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F15" s="72" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -9652,7 +9683,7 @@
       <c r="C16" s="71" t="n"/>
       <c r="D16" s="71" t="n"/>
       <c r="E16" s="71" t="n"/>
-      <c r="F16" s="70" t="n"/>
+      <c r="F16" s="71" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="16" t="inlineStr">
@@ -9663,7 +9694,7 @@
       <c r="C17" s="40" t="n"/>
       <c r="D17" s="40" t="n"/>
       <c r="E17" s="40" t="n"/>
-      <c r="F17" s="45" t="n"/>
+      <c r="F17" s="40" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="19" t="inlineStr">
@@ -9671,10 +9702,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="45" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="16" t="inlineStr">
@@ -9726,10 +9757,10 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="49" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="24">
       <c r="B24" s="22" t="inlineStr">
@@ -9737,10 +9768,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="40" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="24"/>
     <row r="26" ht="15" customHeight="1" s="24">
@@ -9761,17 +9792,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D27" s="72" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E27" s="72" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F27" s="72" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -9780,9 +9811,9 @@
     <row r="28" ht="15" customHeight="1" s="24">
       <c r="B28" s="69" t="n"/>
       <c r="C28" s="71" t="n"/>
-      <c r="D28" s="70" t="n"/>
-      <c r="E28" s="70" t="n"/>
-      <c r="F28" s="70" t="n"/>
+      <c r="D28" s="71" t="n"/>
+      <c r="E28" s="71" t="n"/>
+      <c r="F28" s="71" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="16" t="inlineStr">
@@ -9801,10 +9832,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
+      <c r="C30" s="40" t="n"/>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="40" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="16" t="inlineStr">
@@ -9857,9 +9888,9 @@
         </is>
       </c>
       <c r="C35" s="40" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="40" t="n"/>
+      <c r="F35" s="40" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="24">
       <c r="B36" s="22" t="inlineStr">
@@ -9867,10 +9898,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
-      <c r="E36" s="53" t="n"/>
-      <c r="F36" s="53" t="n"/>
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="24"/>
     <row r="38" ht="15" customHeight="1" s="24">
@@ -9901,7 +9932,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F39" s="72" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -9912,7 +9943,7 @@
       <c r="C40" s="71" t="n"/>
       <c r="D40" s="71" t="n"/>
       <c r="E40" s="71" t="n"/>
-      <c r="F40" s="70" t="n"/>
+      <c r="F40" s="71" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="16" t="inlineStr">
@@ -9923,7 +9954,7 @@
       <c r="C41" s="40" t="n"/>
       <c r="D41" s="40" t="n"/>
       <c r="E41" s="40" t="n"/>
-      <c r="F41" s="45" t="n"/>
+      <c r="F41" s="40" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="16" t="inlineStr">
@@ -9931,10 +9962,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="45" t="n"/>
-      <c r="D42" s="45" t="n"/>
-      <c r="E42" s="45" t="n"/>
-      <c r="F42" s="45" t="n"/>
+      <c r="C42" s="40" t="n"/>
+      <c r="D42" s="40" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="16" t="inlineStr">
@@ -9986,10 +10017,10 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="49" t="n"/>
-      <c r="D47" s="49" t="n"/>
-      <c r="E47" s="49" t="n"/>
-      <c r="F47" s="49" t="n"/>
+      <c r="C47" s="40" t="n"/>
+      <c r="D47" s="40" t="n"/>
+      <c r="E47" s="40" t="n"/>
+      <c r="F47" s="40" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="24">
       <c r="B48" s="22" t="inlineStr">
@@ -9997,10 +10028,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
-      <c r="E48" s="53" t="n"/>
-      <c r="F48" s="53" t="n"/>
+      <c r="C48" s="40" t="n"/>
+      <c r="D48" s="40" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="24"/>
     <row r="50" ht="15" customHeight="1" s="24">
@@ -10021,17 +10052,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D51" s="72" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E51" s="72" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F51" s="72" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -10040,9 +10071,9 @@
     <row r="52" ht="15" customHeight="1" s="24">
       <c r="B52" s="69" t="n"/>
       <c r="C52" s="71" t="n"/>
-      <c r="D52" s="70" t="n"/>
-      <c r="E52" s="70" t="n"/>
-      <c r="F52" s="70" t="n"/>
+      <c r="D52" s="71" t="n"/>
+      <c r="E52" s="71" t="n"/>
+      <c r="F52" s="71" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="16" t="inlineStr">
@@ -10061,10 +10092,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="45" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="45" t="n"/>
-      <c r="F54" s="45" t="n"/>
+      <c r="C54" s="40" t="n"/>
+      <c r="D54" s="40" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="16" t="inlineStr">
@@ -10100,15 +10131,15 @@
       <c r="F57" s="40" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="40" t="n"/>
-      <c r="D58" s="40" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
+      <c r="C58" s="74" t="n"/>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="74" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="16" t="inlineStr">
@@ -10117,9 +10148,9 @@
         </is>
       </c>
       <c r="C59" s="40" t="n"/>
-      <c r="D59" s="49" t="n"/>
-      <c r="E59" s="49" t="n"/>
-      <c r="F59" s="49" t="n"/>
+      <c r="D59" s="40" t="n"/>
+      <c r="E59" s="40" t="n"/>
+      <c r="F59" s="40" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="24">
       <c r="B60" s="22" t="inlineStr">
@@ -10127,10 +10158,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
+      <c r="C60" s="40" t="n"/>
+      <c r="D60" s="40" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1" s="24"/>
     <row r="62" ht="15" customHeight="1" s="24">
@@ -10161,7 +10192,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F63" s="72" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -10172,7 +10203,7 @@
       <c r="C64" s="71" t="n"/>
       <c r="D64" s="71" t="n"/>
       <c r="E64" s="71" t="n"/>
-      <c r="F64" s="70" t="n"/>
+      <c r="F64" s="71" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="16" t="inlineStr">
@@ -10183,7 +10214,7 @@
       <c r="C65" s="40" t="n"/>
       <c r="D65" s="40" t="n"/>
       <c r="E65" s="40" t="n"/>
-      <c r="F65" s="45" t="n"/>
+      <c r="F65" s="40" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="16" t="inlineStr">
@@ -10191,10 +10222,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="45" t="n"/>
-      <c r="D66" s="45" t="n"/>
-      <c r="E66" s="45" t="n"/>
-      <c r="F66" s="45" t="n"/>
+      <c r="C66" s="40" t="n"/>
+      <c r="D66" s="40" t="n"/>
+      <c r="E66" s="40" t="n"/>
+      <c r="F66" s="40" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="16" t="inlineStr">
@@ -10230,15 +10261,15 @@
       <c r="F69" s="40" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="40" t="n"/>
-      <c r="D70" s="40" t="n"/>
-      <c r="E70" s="40" t="n"/>
-      <c r="F70" s="40" t="n"/>
+      <c r="C70" s="74" t="n"/>
+      <c r="D70" s="74" t="n"/>
+      <c r="E70" s="74" t="n"/>
+      <c r="F70" s="74" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="16" t="inlineStr">
@@ -10246,10 +10277,10 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="49" t="n"/>
-      <c r="D71" s="49" t="n"/>
-      <c r="E71" s="49" t="n"/>
-      <c r="F71" s="49" t="n"/>
+      <c r="C71" s="40" t="n"/>
+      <c r="D71" s="40" t="n"/>
+      <c r="E71" s="40" t="n"/>
+      <c r="F71" s="40" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" s="24">
       <c r="B72" s="22" t="inlineStr">
@@ -10257,10 +10288,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="53" t="n"/>
-      <c r="D72" s="53" t="n"/>
-      <c r="E72" s="53" t="n"/>
-      <c r="F72" s="53" t="n"/>
+      <c r="C72" s="40" t="n"/>
+      <c r="D72" s="40" t="n"/>
+      <c r="E72" s="40" t="n"/>
+      <c r="F72" s="40" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="24"/>
     <row r="74" ht="15" customHeight="1" s="24">
@@ -10281,17 +10312,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D75" s="72" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E75" s="72" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F75" s="72" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -10300,9 +10331,9 @@
     <row r="76" ht="15" customHeight="1" s="24">
       <c r="B76" s="69" t="n"/>
       <c r="C76" s="71" t="n"/>
-      <c r="D76" s="70" t="n"/>
-      <c r="E76" s="70" t="n"/>
-      <c r="F76" s="70" t="n"/>
+      <c r="D76" s="71" t="n"/>
+      <c r="E76" s="71" t="n"/>
+      <c r="F76" s="71" t="n"/>
     </row>
     <row r="77">
       <c r="B77" s="16" t="inlineStr">
@@ -10321,10 +10352,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="45" t="n"/>
-      <c r="D78" s="45" t="n"/>
-      <c r="E78" s="45" t="n"/>
-      <c r="F78" s="45" t="n"/>
+      <c r="C78" s="40" t="n"/>
+      <c r="D78" s="40" t="n"/>
+      <c r="E78" s="40" t="n"/>
+      <c r="F78" s="40" t="n"/>
     </row>
     <row r="79">
       <c r="B79" s="16" t="inlineStr">
@@ -10377,9 +10408,9 @@
         </is>
       </c>
       <c r="C83" s="40" t="n"/>
-      <c r="D83" s="49" t="n"/>
-      <c r="E83" s="49" t="n"/>
-      <c r="F83" s="49" t="n"/>
+      <c r="D83" s="40" t="n"/>
+      <c r="E83" s="40" t="n"/>
+      <c r="F83" s="40" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1" s="24">
       <c r="B84" s="22" t="inlineStr">
@@ -10387,10 +10418,10 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="53" t="n"/>
-      <c r="D84" s="53" t="n"/>
-      <c r="E84" s="53" t="n"/>
-      <c r="F84" s="53" t="n"/>
+      <c r="C84" s="40" t="n"/>
+      <c r="D84" s="40" t="n"/>
+      <c r="E84" s="40" t="n"/>
+      <c r="F84" s="40" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1" s="24"/>
     <row r="86" ht="15" customHeight="1" s="24">
@@ -10421,7 +10452,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F87" s="72" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -10432,7 +10463,7 @@
       <c r="C88" s="71" t="n"/>
       <c r="D88" s="71" t="n"/>
       <c r="E88" s="71" t="n"/>
-      <c r="F88" s="70" t="n"/>
+      <c r="F88" s="71" t="n"/>
     </row>
     <row r="89">
       <c r="B89" s="16" t="inlineStr">
@@ -10443,7 +10474,7 @@
       <c r="C89" s="40" t="n"/>
       <c r="D89" s="40" t="n"/>
       <c r="E89" s="40" t="n"/>
-      <c r="F89" s="45" t="n"/>
+      <c r="F89" s="40" t="n"/>
     </row>
     <row r="90">
       <c r="B90" s="16" t="inlineStr">
@@ -10451,10 +10482,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="45" t="n"/>
-      <c r="D90" s="45" t="n"/>
-      <c r="E90" s="45" t="n"/>
-      <c r="F90" s="45" t="n"/>
+      <c r="C90" s="40" t="n"/>
+      <c r="D90" s="40" t="n"/>
+      <c r="E90" s="40" t="n"/>
+      <c r="F90" s="40" t="n"/>
     </row>
     <row r="91">
       <c r="B91" s="16" t="inlineStr">
@@ -10506,10 +10537,10 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="49" t="n"/>
-      <c r="D95" s="49" t="n"/>
-      <c r="E95" s="49" t="n"/>
-      <c r="F95" s="49" t="n"/>
+      <c r="C95" s="40" t="n"/>
+      <c r="D95" s="40" t="n"/>
+      <c r="E95" s="40" t="n"/>
+      <c r="F95" s="40" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1" s="24">
       <c r="B96" s="22" t="inlineStr">
@@ -10517,12 +10548,11 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="53" t="n"/>
-      <c r="D96" s="53" t="n"/>
-      <c r="E96" s="53" t="n"/>
-      <c r="F96" s="53" t="n"/>
-    </row>
-    <row r="97"/>
+      <c r="C96" s="40" t="n"/>
+      <c r="D96" s="40" t="n"/>
+      <c r="E96" s="40" t="n"/>
+      <c r="F96" s="40" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="48">
     <mergeCell ref="F15:F16"/>
@@ -10540,9 +10570,9 @@
     <mergeCell ref="E87:E88"/>
     <mergeCell ref="D75:D76"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="F75:F76"/>
+    <mergeCell ref="B86:F86"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="D87:D88"/>
@@ -10584,11 +10614,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="B1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.12844036697248" customWidth="1" style="24" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="24" min="2" max="25"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
+    <col width="13" customWidth="1" style="24" min="4" max="4"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="13" customWidth="1" style="24" min="6" max="6"/>
     <col width="9.12844036697248" customWidth="1" style="24" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -10611,17 +10645,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F3" s="72" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -10630,9 +10664,9 @@
     <row r="4" ht="15" customHeight="1" s="24">
       <c r="B4" s="69" t="n"/>
       <c r="C4" s="71" t="n"/>
-      <c r="D4" s="70" t="n"/>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="70" t="n"/>
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="16" t="inlineStr">
@@ -10651,10 +10685,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="40" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="16" t="inlineStr">
@@ -10707,9 +10741,9 @@
         </is>
       </c>
       <c r="C11" s="40" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="49" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="24">
       <c r="B12" s="22" t="inlineStr">
@@ -10717,10 +10751,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="53" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="24"/>
     <row r="14" ht="15" customHeight="1" s="24">
@@ -10751,7 +10785,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F15" s="72" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -10762,7 +10796,7 @@
       <c r="C16" s="71" t="n"/>
       <c r="D16" s="71" t="n"/>
       <c r="E16" s="71" t="n"/>
-      <c r="F16" s="70" t="n"/>
+      <c r="F16" s="71" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="16" t="inlineStr">
@@ -10773,7 +10807,7 @@
       <c r="C17" s="40" t="n"/>
       <c r="D17" s="40" t="n"/>
       <c r="E17" s="40" t="n"/>
-      <c r="F17" s="45" t="n"/>
+      <c r="F17" s="40" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="19" t="inlineStr">
@@ -10781,10 +10815,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="45" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="16" t="inlineStr">
@@ -10836,10 +10870,10 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="49" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="24">
       <c r="B24" s="22" t="inlineStr">
@@ -10847,10 +10881,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="40" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="24"/>
     <row r="26" ht="15" customHeight="1" s="24">
@@ -10871,17 +10905,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D27" s="72" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E27" s="72" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F27" s="72" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -10890,9 +10924,9 @@
     <row r="28" ht="15" customHeight="1" s="24">
       <c r="B28" s="69" t="n"/>
       <c r="C28" s="71" t="n"/>
-      <c r="D28" s="70" t="n"/>
-      <c r="E28" s="70" t="n"/>
-      <c r="F28" s="70" t="n"/>
+      <c r="D28" s="71" t="n"/>
+      <c r="E28" s="71" t="n"/>
+      <c r="F28" s="71" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="16" t="inlineStr">
@@ -10911,10 +10945,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
+      <c r="C30" s="40" t="n"/>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="40" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="16" t="inlineStr">
@@ -10967,9 +11001,9 @@
         </is>
       </c>
       <c r="C35" s="40" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="40" t="n"/>
+      <c r="F35" s="40" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="24">
       <c r="B36" s="22" t="inlineStr">
@@ -10977,10 +11011,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
-      <c r="E36" s="53" t="n"/>
-      <c r="F36" s="53" t="n"/>
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="24"/>
     <row r="38" ht="15" customHeight="1" s="24">
@@ -11011,7 +11045,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F39" s="72" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -11022,7 +11056,7 @@
       <c r="C40" s="71" t="n"/>
       <c r="D40" s="71" t="n"/>
       <c r="E40" s="71" t="n"/>
-      <c r="F40" s="70" t="n"/>
+      <c r="F40" s="71" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="16" t="inlineStr">
@@ -11033,7 +11067,7 @@
       <c r="C41" s="40" t="n"/>
       <c r="D41" s="40" t="n"/>
       <c r="E41" s="40" t="n"/>
-      <c r="F41" s="45" t="n"/>
+      <c r="F41" s="40" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="16" t="inlineStr">
@@ -11041,10 +11075,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="45" t="n"/>
-      <c r="D42" s="45" t="n"/>
-      <c r="E42" s="45" t="n"/>
-      <c r="F42" s="45" t="n"/>
+      <c r="C42" s="40" t="n"/>
+      <c r="D42" s="40" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="16" t="inlineStr">
@@ -11096,10 +11130,10 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="49" t="n"/>
-      <c r="D47" s="49" t="n"/>
-      <c r="E47" s="49" t="n"/>
-      <c r="F47" s="49" t="n"/>
+      <c r="C47" s="40" t="n"/>
+      <c r="D47" s="40" t="n"/>
+      <c r="E47" s="40" t="n"/>
+      <c r="F47" s="40" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="24">
       <c r="B48" s="22" t="inlineStr">
@@ -11107,10 +11141,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
-      <c r="E48" s="53" t="n"/>
-      <c r="F48" s="53" t="n"/>
+      <c r="C48" s="40" t="n"/>
+      <c r="D48" s="40" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="24"/>
     <row r="50" ht="15" customHeight="1" s="24">
@@ -11131,17 +11165,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D51" s="72" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E51" s="72" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F51" s="72" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -11150,9 +11184,9 @@
     <row r="52" ht="15" customHeight="1" s="24">
       <c r="B52" s="69" t="n"/>
       <c r="C52" s="71" t="n"/>
-      <c r="D52" s="70" t="n"/>
-      <c r="E52" s="70" t="n"/>
-      <c r="F52" s="70" t="n"/>
+      <c r="D52" s="71" t="n"/>
+      <c r="E52" s="71" t="n"/>
+      <c r="F52" s="71" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="16" t="inlineStr">
@@ -11171,10 +11205,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="45" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="45" t="n"/>
-      <c r="F54" s="45" t="n"/>
+      <c r="C54" s="40" t="n"/>
+      <c r="D54" s="40" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="16" t="inlineStr">
@@ -11210,15 +11244,15 @@
       <c r="F57" s="40" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="40" t="n"/>
-      <c r="D58" s="40" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
+      <c r="C58" s="74" t="n"/>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="74" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="16" t="inlineStr">
@@ -11227,9 +11261,9 @@
         </is>
       </c>
       <c r="C59" s="40" t="n"/>
-      <c r="D59" s="49" t="n"/>
-      <c r="E59" s="49" t="n"/>
-      <c r="F59" s="49" t="n"/>
+      <c r="D59" s="40" t="n"/>
+      <c r="E59" s="40" t="n"/>
+      <c r="F59" s="40" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="24">
       <c r="B60" s="22" t="inlineStr">
@@ -11237,10 +11271,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
+      <c r="C60" s="40" t="n"/>
+      <c r="D60" s="40" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1" s="24"/>
     <row r="62" ht="15" customHeight="1" s="24">
@@ -11271,7 +11305,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F63" s="72" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -11282,7 +11316,7 @@
       <c r="C64" s="71" t="n"/>
       <c r="D64" s="71" t="n"/>
       <c r="E64" s="71" t="n"/>
-      <c r="F64" s="70" t="n"/>
+      <c r="F64" s="71" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="16" t="inlineStr">
@@ -11293,7 +11327,7 @@
       <c r="C65" s="40" t="n"/>
       <c r="D65" s="40" t="n"/>
       <c r="E65" s="40" t="n"/>
-      <c r="F65" s="45" t="n"/>
+      <c r="F65" s="40" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="16" t="inlineStr">
@@ -11301,10 +11335,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="45" t="n"/>
-      <c r="D66" s="45" t="n"/>
-      <c r="E66" s="45" t="n"/>
-      <c r="F66" s="45" t="n"/>
+      <c r="C66" s="40" t="n"/>
+      <c r="D66" s="40" t="n"/>
+      <c r="E66" s="40" t="n"/>
+      <c r="F66" s="40" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="16" t="inlineStr">
@@ -11340,15 +11374,15 @@
       <c r="F69" s="40" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="40" t="n"/>
-      <c r="D70" s="40" t="n"/>
-      <c r="E70" s="40" t="n"/>
-      <c r="F70" s="40" t="n"/>
+      <c r="C70" s="74" t="n"/>
+      <c r="D70" s="74" t="n"/>
+      <c r="E70" s="74" t="n"/>
+      <c r="F70" s="74" t="n"/>
     </row>
     <row r="71">
       <c r="B71" s="16" t="inlineStr">
@@ -11356,10 +11390,10 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="49" t="n"/>
-      <c r="D71" s="49" t="n"/>
-      <c r="E71" s="49" t="n"/>
-      <c r="F71" s="49" t="n"/>
+      <c r="C71" s="40" t="n"/>
+      <c r="D71" s="40" t="n"/>
+      <c r="E71" s="40" t="n"/>
+      <c r="F71" s="40" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" s="24">
       <c r="B72" s="22" t="inlineStr">
@@ -11367,10 +11401,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="53" t="n"/>
-      <c r="D72" s="53" t="n"/>
-      <c r="E72" s="53" t="n"/>
-      <c r="F72" s="53" t="n"/>
+      <c r="C72" s="40" t="n"/>
+      <c r="D72" s="40" t="n"/>
+      <c r="E72" s="40" t="n"/>
+      <c r="F72" s="40" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1" s="24"/>
     <row r="74" ht="15" customHeight="1" s="24">
@@ -11391,17 +11425,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D75" s="72" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E75" s="72" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F75" s="72" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -11410,9 +11444,9 @@
     <row r="76" ht="15" customHeight="1" s="24">
       <c r="B76" s="69" t="n"/>
       <c r="C76" s="71" t="n"/>
-      <c r="D76" s="70" t="n"/>
-      <c r="E76" s="70" t="n"/>
-      <c r="F76" s="70" t="n"/>
+      <c r="D76" s="71" t="n"/>
+      <c r="E76" s="71" t="n"/>
+      <c r="F76" s="71" t="n"/>
     </row>
     <row r="77">
       <c r="B77" s="16" t="inlineStr">
@@ -11431,10 +11465,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="45" t="n"/>
-      <c r="D78" s="45" t="n"/>
-      <c r="E78" s="45" t="n"/>
-      <c r="F78" s="45" t="n"/>
+      <c r="C78" s="40" t="n"/>
+      <c r="D78" s="40" t="n"/>
+      <c r="E78" s="40" t="n"/>
+      <c r="F78" s="40" t="n"/>
     </row>
     <row r="79">
       <c r="B79" s="16" t="inlineStr">
@@ -11487,9 +11521,9 @@
         </is>
       </c>
       <c r="C83" s="40" t="n"/>
-      <c r="D83" s="49" t="n"/>
-      <c r="E83" s="49" t="n"/>
-      <c r="F83" s="49" t="n"/>
+      <c r="D83" s="40" t="n"/>
+      <c r="E83" s="40" t="n"/>
+      <c r="F83" s="40" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1" s="24">
       <c r="B84" s="22" t="inlineStr">
@@ -11497,10 +11531,10 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="53" t="n"/>
-      <c r="D84" s="53" t="n"/>
-      <c r="E84" s="53" t="n"/>
-      <c r="F84" s="53" t="n"/>
+      <c r="C84" s="40" t="n"/>
+      <c r="D84" s="40" t="n"/>
+      <c r="E84" s="40" t="n"/>
+      <c r="F84" s="40" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1" s="24"/>
     <row r="86" ht="15" customHeight="1" s="24">
@@ -11531,7 +11565,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F87" s="72" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -11542,7 +11576,7 @@
       <c r="C88" s="71" t="n"/>
       <c r="D88" s="71" t="n"/>
       <c r="E88" s="71" t="n"/>
-      <c r="F88" s="70" t="n"/>
+      <c r="F88" s="71" t="n"/>
     </row>
     <row r="89">
       <c r="B89" s="16" t="inlineStr">
@@ -11553,7 +11587,7 @@
       <c r="C89" s="40" t="n"/>
       <c r="D89" s="40" t="n"/>
       <c r="E89" s="40" t="n"/>
-      <c r="F89" s="45" t="n"/>
+      <c r="F89" s="40" t="n"/>
     </row>
     <row r="90">
       <c r="B90" s="16" t="inlineStr">
@@ -11561,10 +11595,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="45" t="n"/>
-      <c r="D90" s="45" t="n"/>
-      <c r="E90" s="45" t="n"/>
-      <c r="F90" s="45" t="n"/>
+      <c r="C90" s="40" t="n"/>
+      <c r="D90" s="40" t="n"/>
+      <c r="E90" s="40" t="n"/>
+      <c r="F90" s="40" t="n"/>
     </row>
     <row r="91">
       <c r="B91" s="16" t="inlineStr">
@@ -11616,10 +11650,10 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="49" t="n"/>
-      <c r="D95" s="49" t="n"/>
-      <c r="E95" s="49" t="n"/>
-      <c r="F95" s="49" t="n"/>
+      <c r="C95" s="40" t="n"/>
+      <c r="D95" s="40" t="n"/>
+      <c r="E95" s="40" t="n"/>
+      <c r="F95" s="40" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1" s="24">
       <c r="B96" s="22" t="inlineStr">
@@ -11627,12 +11661,11 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="53" t="n"/>
-      <c r="D96" s="53" t="n"/>
-      <c r="E96" s="53" t="n"/>
-      <c r="F96" s="53" t="n"/>
-    </row>
-    <row r="97"/>
+      <c r="C96" s="40" t="n"/>
+      <c r="D96" s="40" t="n"/>
+      <c r="E96" s="40" t="n"/>
+      <c r="F96" s="40" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="48">
     <mergeCell ref="F15:F16"/>
@@ -11650,9 +11683,9 @@
     <mergeCell ref="E87:E88"/>
     <mergeCell ref="D75:D76"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="F75:F76"/>
+    <mergeCell ref="B86:F86"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="D87:D88"/>
@@ -11694,11 +11727,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="B1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.12844036697248" customWidth="1" style="24" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="25"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
+    <col width="13" customWidth="1" style="24" min="4" max="4"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="13" customWidth="1" style="24" min="6" max="6"/>
     <col width="9.12844036697248" customWidth="1" style="24" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -11726,17 +11763,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F3" s="72" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -11750,9 +11787,9 @@
     <row r="4" ht="15" customHeight="1" s="24">
       <c r="B4" s="69" t="n"/>
       <c r="C4" s="71" t="n"/>
-      <c r="D4" s="70" t="n"/>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="70" t="n"/>
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
       <c r="G4" s="35" t="n"/>
       <c r="H4" s="35" t="n"/>
       <c r="I4" s="30" t="n"/>
@@ -11781,10 +11818,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="40" t="n"/>
       <c r="G6" s="57" t="n"/>
       <c r="H6" s="57" t="n"/>
       <c r="I6" s="30" t="n"/>
@@ -11862,9 +11899,9 @@
         </is>
       </c>
       <c r="C11" s="40" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="49" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
       <c r="G11" s="57" t="n"/>
       <c r="H11" s="57" t="n"/>
       <c r="I11" s="30" t="n"/>
@@ -11877,10 +11914,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="53" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
       <c r="G12" s="57" t="n"/>
       <c r="H12" s="57" t="n"/>
       <c r="I12" s="30" t="n"/>
@@ -11925,7 +11962,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F15" s="72" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -11941,7 +11978,7 @@
       <c r="C16" s="71" t="n"/>
       <c r="D16" s="71" t="n"/>
       <c r="E16" s="71" t="n"/>
-      <c r="F16" s="70" t="n"/>
+      <c r="F16" s="71" t="n"/>
       <c r="G16" s="35" t="n"/>
       <c r="H16" s="35" t="n"/>
       <c r="I16" s="30" t="n"/>
@@ -11957,7 +11994,7 @@
       <c r="C17" s="40" t="n"/>
       <c r="D17" s="40" t="n"/>
       <c r="E17" s="40" t="n"/>
-      <c r="F17" s="45" t="n"/>
+      <c r="F17" s="40" t="n"/>
       <c r="G17" s="35" t="n"/>
       <c r="H17" s="35" t="n"/>
       <c r="I17" s="30" t="n"/>
@@ -11970,10 +12007,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="45" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
       <c r="G18" s="35" t="n"/>
       <c r="H18" s="35" t="n"/>
       <c r="I18" s="30" t="n"/>
@@ -12050,10 +12087,10 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="49" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
       <c r="G23" s="35" t="n"/>
       <c r="H23" s="35" t="n"/>
       <c r="I23" s="30" t="n"/>
@@ -12066,10 +12103,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="40" t="n"/>
       <c r="G24" s="35" t="n"/>
       <c r="H24" s="35" t="n"/>
       <c r="I24" s="30" t="n"/>
@@ -12104,17 +12141,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D27" s="72" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E27" s="72" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F27" s="72" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -12128,9 +12165,9 @@
     <row r="28" ht="15" customHeight="1" s="24">
       <c r="B28" s="69" t="n"/>
       <c r="C28" s="71" t="n"/>
-      <c r="D28" s="70" t="n"/>
-      <c r="E28" s="70" t="n"/>
-      <c r="F28" s="70" t="n"/>
+      <c r="D28" s="71" t="n"/>
+      <c r="E28" s="71" t="n"/>
+      <c r="F28" s="71" t="n"/>
       <c r="G28" s="35" t="n"/>
       <c r="H28" s="35" t="n"/>
       <c r="I28" s="30" t="n"/>
@@ -12159,10 +12196,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
+      <c r="C30" s="40" t="n"/>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="40" t="n"/>
       <c r="G30" s="57" t="n"/>
       <c r="H30" s="57" t="n"/>
       <c r="I30" s="30" t="n"/>
@@ -12240,9 +12277,9 @@
         </is>
       </c>
       <c r="C35" s="40" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="40" t="n"/>
+      <c r="F35" s="40" t="n"/>
       <c r="G35" s="57" t="n"/>
       <c r="H35" s="57" t="n"/>
       <c r="I35" s="30" t="n"/>
@@ -12255,10 +12292,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
-      <c r="E36" s="53" t="n"/>
-      <c r="F36" s="53" t="n"/>
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
       <c r="G36" s="57" t="n"/>
       <c r="H36" s="57" t="n"/>
       <c r="I36" s="30" t="n"/>
@@ -12303,7 +12340,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F39" s="72" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -12319,7 +12356,7 @@
       <c r="C40" s="71" t="n"/>
       <c r="D40" s="71" t="n"/>
       <c r="E40" s="71" t="n"/>
-      <c r="F40" s="70" t="n"/>
+      <c r="F40" s="71" t="n"/>
       <c r="G40" s="35" t="n"/>
       <c r="H40" s="35" t="n"/>
       <c r="I40" s="30" t="n"/>
@@ -12335,7 +12372,7 @@
       <c r="C41" s="40" t="n"/>
       <c r="D41" s="40" t="n"/>
       <c r="E41" s="40" t="n"/>
-      <c r="F41" s="45" t="n"/>
+      <c r="F41" s="40" t="n"/>
       <c r="G41" s="35" t="n"/>
       <c r="H41" s="35" t="n"/>
       <c r="I41" s="30" t="n"/>
@@ -12348,10 +12385,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="45" t="n"/>
-      <c r="D42" s="45" t="n"/>
-      <c r="E42" s="45" t="n"/>
-      <c r="F42" s="45" t="n"/>
+      <c r="C42" s="40" t="n"/>
+      <c r="D42" s="40" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
       <c r="G42" s="35" t="n"/>
       <c r="H42" s="35" t="n"/>
       <c r="I42" s="30" t="n"/>
@@ -12428,10 +12465,10 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="49" t="n"/>
-      <c r="D47" s="49" t="n"/>
-      <c r="E47" s="49" t="n"/>
-      <c r="F47" s="49" t="n"/>
+      <c r="C47" s="40" t="n"/>
+      <c r="D47" s="40" t="n"/>
+      <c r="E47" s="40" t="n"/>
+      <c r="F47" s="40" t="n"/>
       <c r="G47" s="35" t="n"/>
       <c r="H47" s="35" t="n"/>
       <c r="I47" s="30" t="n"/>
@@ -12444,10 +12481,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
-      <c r="E48" s="53" t="n"/>
-      <c r="F48" s="53" t="n"/>
+      <c r="C48" s="40" t="n"/>
+      <c r="D48" s="40" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
       <c r="G48" s="35" t="n"/>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="30" t="n"/>
@@ -12482,17 +12519,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D51" s="72" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E51" s="72" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F51" s="72" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -12506,9 +12543,9 @@
     <row r="52" ht="15" customHeight="1" s="24">
       <c r="B52" s="69" t="n"/>
       <c r="C52" s="71" t="n"/>
-      <c r="D52" s="70" t="n"/>
-      <c r="E52" s="70" t="n"/>
-      <c r="F52" s="70" t="n"/>
+      <c r="D52" s="71" t="n"/>
+      <c r="E52" s="71" t="n"/>
+      <c r="F52" s="71" t="n"/>
       <c r="G52" s="35" t="n"/>
       <c r="H52" s="35" t="n"/>
       <c r="I52" s="30" t="n"/>
@@ -12537,10 +12574,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="45" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="45" t="n"/>
-      <c r="F54" s="45" t="n"/>
+      <c r="C54" s="40" t="n"/>
+      <c r="D54" s="40" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
       <c r="G54" s="57" t="n"/>
       <c r="H54" s="57" t="n"/>
       <c r="I54" s="30" t="n"/>
@@ -12596,15 +12633,15 @@
       <c r="K57" s="30" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="40" t="n"/>
-      <c r="D58" s="40" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
+      <c r="C58" s="74" t="n"/>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="74" t="n"/>
       <c r="G58" s="57" t="n"/>
       <c r="H58" s="57" t="n"/>
       <c r="I58" s="30" t="n"/>
@@ -12618,9 +12655,9 @@
         </is>
       </c>
       <c r="C59" s="40" t="n"/>
-      <c r="D59" s="49" t="n"/>
-      <c r="E59" s="49" t="n"/>
-      <c r="F59" s="49" t="n"/>
+      <c r="D59" s="40" t="n"/>
+      <c r="E59" s="40" t="n"/>
+      <c r="F59" s="40" t="n"/>
       <c r="G59" s="57" t="n"/>
       <c r="H59" s="57" t="n"/>
       <c r="I59" s="30" t="n"/>
@@ -12633,10 +12670,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
+      <c r="C60" s="40" t="n"/>
+      <c r="D60" s="40" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
       <c r="G60" s="57" t="n"/>
       <c r="H60" s="57" t="n"/>
       <c r="I60" s="30" t="n"/>
@@ -12681,7 +12718,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F63" s="72" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -12697,7 +12734,7 @@
       <c r="C64" s="71" t="n"/>
       <c r="D64" s="71" t="n"/>
       <c r="E64" s="71" t="n"/>
-      <c r="F64" s="70" t="n"/>
+      <c r="F64" s="71" t="n"/>
       <c r="G64" s="35" t="n"/>
       <c r="H64" s="35" t="n"/>
       <c r="I64" s="30" t="n"/>
@@ -12713,7 +12750,7 @@
       <c r="C65" s="40" t="n"/>
       <c r="D65" s="40" t="n"/>
       <c r="E65" s="40" t="n"/>
-      <c r="F65" s="45" t="n"/>
+      <c r="F65" s="40" t="n"/>
       <c r="G65" s="35" t="n"/>
       <c r="H65" s="35" t="n"/>
       <c r="I65" s="30" t="n"/>
@@ -12726,10 +12763,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="45" t="n"/>
-      <c r="D66" s="45" t="n"/>
-      <c r="E66" s="45" t="n"/>
-      <c r="F66" s="45" t="n"/>
+      <c r="C66" s="40" t="n"/>
+      <c r="D66" s="40" t="n"/>
+      <c r="E66" s="40" t="n"/>
+      <c r="F66" s="40" t="n"/>
       <c r="G66" s="35" t="n"/>
       <c r="H66" s="35" t="n"/>
       <c r="I66" s="30" t="n"/>
@@ -12785,15 +12822,15 @@
       <c r="K69" s="30" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="40" t="n"/>
-      <c r="D70" s="40" t="n"/>
-      <c r="E70" s="40" t="n"/>
-      <c r="F70" s="40" t="n"/>
+      <c r="C70" s="74" t="n"/>
+      <c r="D70" s="74" t="n"/>
+      <c r="E70" s="74" t="n"/>
+      <c r="F70" s="74" t="n"/>
       <c r="G70" s="35" t="n"/>
       <c r="H70" s="35" t="n"/>
       <c r="I70" s="30" t="n"/>
@@ -12806,10 +12843,10 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="49" t="n"/>
-      <c r="D71" s="49" t="n"/>
-      <c r="E71" s="49" t="n"/>
-      <c r="F71" s="49" t="n"/>
+      <c r="C71" s="40" t="n"/>
+      <c r="D71" s="40" t="n"/>
+      <c r="E71" s="40" t="n"/>
+      <c r="F71" s="40" t="n"/>
       <c r="G71" s="35" t="n"/>
       <c r="H71" s="35" t="n"/>
       <c r="I71" s="30" t="n"/>
@@ -12822,10 +12859,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="53" t="n"/>
-      <c r="D72" s="53" t="n"/>
-      <c r="E72" s="53" t="n"/>
-      <c r="F72" s="53" t="n"/>
+      <c r="C72" s="40" t="n"/>
+      <c r="D72" s="40" t="n"/>
+      <c r="E72" s="40" t="n"/>
+      <c r="F72" s="40" t="n"/>
       <c r="G72" s="35" t="n"/>
       <c r="H72" s="35" t="n"/>
       <c r="I72" s="30" t="n"/>
@@ -12860,17 +12897,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D75" s="72" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E75" s="72" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F75" s="72" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -12884,9 +12921,9 @@
     <row r="76" ht="15" customHeight="1" s="24">
       <c r="B76" s="69" t="n"/>
       <c r="C76" s="71" t="n"/>
-      <c r="D76" s="70" t="n"/>
-      <c r="E76" s="70" t="n"/>
-      <c r="F76" s="70" t="n"/>
+      <c r="D76" s="71" t="n"/>
+      <c r="E76" s="71" t="n"/>
+      <c r="F76" s="71" t="n"/>
       <c r="G76" s="35" t="n"/>
       <c r="H76" s="35" t="n"/>
       <c r="I76" s="30" t="n"/>
@@ -12915,10 +12952,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="45" t="n"/>
-      <c r="D78" s="45" t="n"/>
-      <c r="E78" s="45" t="n"/>
-      <c r="F78" s="45" t="n"/>
+      <c r="C78" s="40" t="n"/>
+      <c r="D78" s="40" t="n"/>
+      <c r="E78" s="40" t="n"/>
+      <c r="F78" s="40" t="n"/>
       <c r="G78" s="57" t="n"/>
       <c r="H78" s="57" t="n"/>
       <c r="I78" s="30" t="n"/>
@@ -12996,9 +13033,9 @@
         </is>
       </c>
       <c r="C83" s="40" t="n"/>
-      <c r="D83" s="49" t="n"/>
-      <c r="E83" s="49" t="n"/>
-      <c r="F83" s="49" t="n"/>
+      <c r="D83" s="40" t="n"/>
+      <c r="E83" s="40" t="n"/>
+      <c r="F83" s="40" t="n"/>
       <c r="G83" s="57" t="n"/>
       <c r="H83" s="57" t="n"/>
       <c r="I83" s="30" t="n"/>
@@ -13011,10 +13048,10 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="53" t="n"/>
-      <c r="D84" s="53" t="n"/>
-      <c r="E84" s="53" t="n"/>
-      <c r="F84" s="53" t="n"/>
+      <c r="C84" s="40" t="n"/>
+      <c r="D84" s="40" t="n"/>
+      <c r="E84" s="40" t="n"/>
+      <c r="F84" s="40" t="n"/>
       <c r="G84" s="57" t="n"/>
       <c r="H84" s="57" t="n"/>
       <c r="I84" s="30" t="n"/>
@@ -13059,7 +13096,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F87" s="72" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -13075,7 +13112,7 @@
       <c r="C88" s="71" t="n"/>
       <c r="D88" s="71" t="n"/>
       <c r="E88" s="71" t="n"/>
-      <c r="F88" s="70" t="n"/>
+      <c r="F88" s="71" t="n"/>
       <c r="G88" s="35" t="n"/>
       <c r="H88" s="35" t="n"/>
       <c r="I88" s="30" t="n"/>
@@ -13091,7 +13128,7 @@
       <c r="C89" s="40" t="n"/>
       <c r="D89" s="40" t="n"/>
       <c r="E89" s="40" t="n"/>
-      <c r="F89" s="45" t="n"/>
+      <c r="F89" s="40" t="n"/>
       <c r="G89" s="35" t="n"/>
       <c r="H89" s="35" t="n"/>
       <c r="I89" s="30" t="n"/>
@@ -13104,10 +13141,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="45" t="n"/>
-      <c r="D90" s="45" t="n"/>
-      <c r="E90" s="45" t="n"/>
-      <c r="F90" s="45" t="n"/>
+      <c r="C90" s="40" t="n"/>
+      <c r="D90" s="40" t="n"/>
+      <c r="E90" s="40" t="n"/>
+      <c r="F90" s="40" t="n"/>
       <c r="G90" s="35" t="n"/>
       <c r="H90" s="35" t="n"/>
       <c r="I90" s="30" t="n"/>
@@ -13184,10 +13221,10 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="49" t="n"/>
-      <c r="D95" s="49" t="n"/>
-      <c r="E95" s="49" t="n"/>
-      <c r="F95" s="49" t="n"/>
+      <c r="C95" s="40" t="n"/>
+      <c r="D95" s="40" t="n"/>
+      <c r="E95" s="40" t="n"/>
+      <c r="F95" s="40" t="n"/>
       <c r="G95" s="35" t="n"/>
       <c r="H95" s="35" t="n"/>
       <c r="I95" s="30" t="n"/>
@@ -13200,10 +13237,10 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="53" t="n"/>
-      <c r="D96" s="53" t="n"/>
-      <c r="E96" s="53" t="n"/>
-      <c r="F96" s="53" t="n"/>
+      <c r="C96" s="40" t="n"/>
+      <c r="D96" s="40" t="n"/>
+      <c r="E96" s="40" t="n"/>
+      <c r="F96" s="40" t="n"/>
       <c r="G96" s="35" t="n"/>
       <c r="H96" s="35" t="n"/>
       <c r="I96" s="30" t="n"/>
@@ -13232,9 +13269,9 @@
     <mergeCell ref="E87:E88"/>
     <mergeCell ref="D75:D76"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="F75:F76"/>
+    <mergeCell ref="B86:F86"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="D87:D88"/>
@@ -13276,11 +13313,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="B1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.12844036697248" customWidth="1" style="24" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="25"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
+    <col width="13" customWidth="1" style="24" min="4" max="4"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="13" customWidth="1" style="24" min="6" max="6"/>
     <col width="9.12844036697248" customWidth="1" style="24" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -13308,17 +13349,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F3" s="72" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -13332,9 +13373,9 @@
     <row r="4" ht="15" customHeight="1" s="24">
       <c r="B4" s="69" t="n"/>
       <c r="C4" s="71" t="n"/>
-      <c r="D4" s="70" t="n"/>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="70" t="n"/>
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
       <c r="G4" s="35" t="n"/>
       <c r="H4" s="35" t="n"/>
       <c r="I4" s="30" t="n"/>
@@ -13363,10 +13404,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="40" t="n"/>
       <c r="G6" s="57" t="n"/>
       <c r="H6" s="57" t="n"/>
       <c r="I6" s="30" t="n"/>
@@ -13444,9 +13485,9 @@
         </is>
       </c>
       <c r="C11" s="40" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="49" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
       <c r="G11" s="57" t="n"/>
       <c r="H11" s="57" t="n"/>
       <c r="I11" s="30" t="n"/>
@@ -13459,10 +13500,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="53" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
       <c r="G12" s="57" t="n"/>
       <c r="H12" s="57" t="n"/>
       <c r="I12" s="30" t="n"/>
@@ -13507,7 +13548,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F15" s="72" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -13523,7 +13564,7 @@
       <c r="C16" s="71" t="n"/>
       <c r="D16" s="71" t="n"/>
       <c r="E16" s="71" t="n"/>
-      <c r="F16" s="70" t="n"/>
+      <c r="F16" s="71" t="n"/>
       <c r="G16" s="35" t="n"/>
       <c r="H16" s="35" t="n"/>
       <c r="I16" s="30" t="n"/>
@@ -13539,7 +13580,7 @@
       <c r="C17" s="40" t="n"/>
       <c r="D17" s="40" t="n"/>
       <c r="E17" s="40" t="n"/>
-      <c r="F17" s="45" t="n"/>
+      <c r="F17" s="40" t="n"/>
       <c r="G17" s="35" t="n"/>
       <c r="H17" s="35" t="n"/>
       <c r="I17" s="30" t="n"/>
@@ -13552,10 +13593,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="45" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
       <c r="G18" s="35" t="n"/>
       <c r="H18" s="35" t="n"/>
       <c r="I18" s="30" t="n"/>
@@ -13632,10 +13673,10 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="49" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
       <c r="G23" s="35" t="n"/>
       <c r="H23" s="35" t="n"/>
       <c r="I23" s="30" t="n"/>
@@ -13648,10 +13689,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="40" t="n"/>
       <c r="G24" s="35" t="n"/>
       <c r="H24" s="35" t="n"/>
       <c r="I24" s="30" t="n"/>
@@ -13686,17 +13727,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D27" s="72" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E27" s="72" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F27" s="72" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -13710,9 +13751,9 @@
     <row r="28" ht="15" customHeight="1" s="24">
       <c r="B28" s="69" t="n"/>
       <c r="C28" s="71" t="n"/>
-      <c r="D28" s="70" t="n"/>
-      <c r="E28" s="70" t="n"/>
-      <c r="F28" s="70" t="n"/>
+      <c r="D28" s="71" t="n"/>
+      <c r="E28" s="71" t="n"/>
+      <c r="F28" s="71" t="n"/>
       <c r="G28" s="35" t="n"/>
       <c r="H28" s="35" t="n"/>
       <c r="I28" s="30" t="n"/>
@@ -13741,10 +13782,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
+      <c r="C30" s="40" t="n"/>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="40" t="n"/>
       <c r="G30" s="57" t="n"/>
       <c r="H30" s="57" t="n"/>
       <c r="I30" s="30" t="n"/>
@@ -13822,9 +13863,9 @@
         </is>
       </c>
       <c r="C35" s="40" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="40" t="n"/>
+      <c r="F35" s="40" t="n"/>
       <c r="G35" s="57" t="n"/>
       <c r="H35" s="57" t="n"/>
       <c r="I35" s="30" t="n"/>
@@ -13837,10 +13878,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
-      <c r="E36" s="53" t="n"/>
-      <c r="F36" s="53" t="n"/>
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
       <c r="G36" s="57" t="n"/>
       <c r="H36" s="57" t="n"/>
       <c r="I36" s="30" t="n"/>
@@ -13885,7 +13926,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F39" s="72" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -13901,7 +13942,7 @@
       <c r="C40" s="71" t="n"/>
       <c r="D40" s="71" t="n"/>
       <c r="E40" s="71" t="n"/>
-      <c r="F40" s="70" t="n"/>
+      <c r="F40" s="71" t="n"/>
       <c r="G40" s="35" t="n"/>
       <c r="H40" s="35" t="n"/>
       <c r="I40" s="30" t="n"/>
@@ -13917,7 +13958,7 @@
       <c r="C41" s="40" t="n"/>
       <c r="D41" s="40" t="n"/>
       <c r="E41" s="40" t="n"/>
-      <c r="F41" s="45" t="n"/>
+      <c r="F41" s="40" t="n"/>
       <c r="G41" s="35" t="n"/>
       <c r="H41" s="35" t="n"/>
       <c r="I41" s="30" t="n"/>
@@ -13930,10 +13971,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="45" t="n"/>
-      <c r="D42" s="45" t="n"/>
-      <c r="E42" s="45" t="n"/>
-      <c r="F42" s="45" t="n"/>
+      <c r="C42" s="40" t="n"/>
+      <c r="D42" s="40" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
       <c r="G42" s="35" t="n"/>
       <c r="H42" s="35" t="n"/>
       <c r="I42" s="30" t="n"/>
@@ -14010,10 +14051,10 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="49" t="n"/>
-      <c r="D47" s="49" t="n"/>
-      <c r="E47" s="49" t="n"/>
-      <c r="F47" s="49" t="n"/>
+      <c r="C47" s="40" t="n"/>
+      <c r="D47" s="40" t="n"/>
+      <c r="E47" s="40" t="n"/>
+      <c r="F47" s="40" t="n"/>
       <c r="G47" s="35" t="n"/>
       <c r="H47" s="35" t="n"/>
       <c r="I47" s="30" t="n"/>
@@ -14026,10 +14067,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
-      <c r="E48" s="53" t="n"/>
-      <c r="F48" s="53" t="n"/>
+      <c r="C48" s="40" t="n"/>
+      <c r="D48" s="40" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
       <c r="G48" s="35" t="n"/>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="30" t="n"/>
@@ -14064,17 +14105,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D51" s="72" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E51" s="72" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F51" s="72" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -14088,9 +14129,9 @@
     <row r="52" ht="15" customHeight="1" s="24">
       <c r="B52" s="69" t="n"/>
       <c r="C52" s="71" t="n"/>
-      <c r="D52" s="70" t="n"/>
-      <c r="E52" s="70" t="n"/>
-      <c r="F52" s="70" t="n"/>
+      <c r="D52" s="71" t="n"/>
+      <c r="E52" s="71" t="n"/>
+      <c r="F52" s="71" t="n"/>
       <c r="G52" s="35" t="n"/>
       <c r="H52" s="35" t="n"/>
       <c r="I52" s="30" t="n"/>
@@ -14119,10 +14160,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="45" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="45" t="n"/>
-      <c r="F54" s="45" t="n"/>
+      <c r="C54" s="40" t="n"/>
+      <c r="D54" s="40" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
       <c r="G54" s="57" t="n"/>
       <c r="H54" s="57" t="n"/>
       <c r="I54" s="30" t="n"/>
@@ -14178,15 +14219,15 @@
       <c r="K57" s="30" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="40" t="n"/>
-      <c r="D58" s="40" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
+      <c r="C58" s="74" t="n"/>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="74" t="n"/>
       <c r="G58" s="57" t="n"/>
       <c r="H58" s="57" t="n"/>
       <c r="I58" s="30" t="n"/>
@@ -14200,9 +14241,9 @@
         </is>
       </c>
       <c r="C59" s="40" t="n"/>
-      <c r="D59" s="49" t="n"/>
-      <c r="E59" s="49" t="n"/>
-      <c r="F59" s="49" t="n"/>
+      <c r="D59" s="40" t="n"/>
+      <c r="E59" s="40" t="n"/>
+      <c r="F59" s="40" t="n"/>
       <c r="G59" s="57" t="n"/>
       <c r="H59" s="57" t="n"/>
       <c r="I59" s="30" t="n"/>
@@ -14215,10 +14256,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
+      <c r="C60" s="40" t="n"/>
+      <c r="D60" s="40" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
       <c r="G60" s="57" t="n"/>
       <c r="H60" s="57" t="n"/>
       <c r="I60" s="30" t="n"/>
@@ -14263,7 +14304,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F63" s="72" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -14279,7 +14320,7 @@
       <c r="C64" s="71" t="n"/>
       <c r="D64" s="71" t="n"/>
       <c r="E64" s="71" t="n"/>
-      <c r="F64" s="70" t="n"/>
+      <c r="F64" s="71" t="n"/>
       <c r="G64" s="35" t="n"/>
       <c r="H64" s="35" t="n"/>
       <c r="I64" s="30" t="n"/>
@@ -14295,7 +14336,7 @@
       <c r="C65" s="40" t="n"/>
       <c r="D65" s="40" t="n"/>
       <c r="E65" s="40" t="n"/>
-      <c r="F65" s="45" t="n"/>
+      <c r="F65" s="40" t="n"/>
       <c r="G65" s="35" t="n"/>
       <c r="H65" s="35" t="n"/>
       <c r="I65" s="30" t="n"/>
@@ -14308,10 +14349,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="45" t="n"/>
-      <c r="D66" s="45" t="n"/>
-      <c r="E66" s="45" t="n"/>
-      <c r="F66" s="45" t="n"/>
+      <c r="C66" s="40" t="n"/>
+      <c r="D66" s="40" t="n"/>
+      <c r="E66" s="40" t="n"/>
+      <c r="F66" s="40" t="n"/>
       <c r="G66" s="35" t="n"/>
       <c r="H66" s="35" t="n"/>
       <c r="I66" s="30" t="n"/>
@@ -14367,15 +14408,15 @@
       <c r="K69" s="30" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="40" t="n"/>
-      <c r="D70" s="40" t="n"/>
-      <c r="E70" s="40" t="n"/>
-      <c r="F70" s="40" t="n"/>
+      <c r="C70" s="74" t="n"/>
+      <c r="D70" s="74" t="n"/>
+      <c r="E70" s="74" t="n"/>
+      <c r="F70" s="74" t="n"/>
       <c r="G70" s="35" t="n"/>
       <c r="H70" s="35" t="n"/>
       <c r="I70" s="30" t="n"/>
@@ -14388,10 +14429,10 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="49" t="n"/>
-      <c r="D71" s="49" t="n"/>
-      <c r="E71" s="49" t="n"/>
-      <c r="F71" s="49" t="n"/>
+      <c r="C71" s="40" t="n"/>
+      <c r="D71" s="40" t="n"/>
+      <c r="E71" s="40" t="n"/>
+      <c r="F71" s="40" t="n"/>
       <c r="G71" s="35" t="n"/>
       <c r="H71" s="35" t="n"/>
       <c r="I71" s="30" t="n"/>
@@ -14404,10 +14445,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="53" t="n"/>
-      <c r="D72" s="53" t="n"/>
-      <c r="E72" s="53" t="n"/>
-      <c r="F72" s="53" t="n"/>
+      <c r="C72" s="40" t="n"/>
+      <c r="D72" s="40" t="n"/>
+      <c r="E72" s="40" t="n"/>
+      <c r="F72" s="40" t="n"/>
       <c r="G72" s="35" t="n"/>
       <c r="H72" s="35" t="n"/>
       <c r="I72" s="30" t="n"/>
@@ -14442,17 +14483,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D75" s="72" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E75" s="72" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F75" s="72" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -14466,9 +14507,9 @@
     <row r="76" ht="15" customHeight="1" s="24">
       <c r="B76" s="69" t="n"/>
       <c r="C76" s="71" t="n"/>
-      <c r="D76" s="70" t="n"/>
-      <c r="E76" s="70" t="n"/>
-      <c r="F76" s="70" t="n"/>
+      <c r="D76" s="71" t="n"/>
+      <c r="E76" s="71" t="n"/>
+      <c r="F76" s="71" t="n"/>
       <c r="G76" s="35" t="n"/>
       <c r="H76" s="35" t="n"/>
       <c r="I76" s="30" t="n"/>
@@ -14497,10 +14538,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="45" t="n"/>
-      <c r="D78" s="45" t="n"/>
-      <c r="E78" s="45" t="n"/>
-      <c r="F78" s="45" t="n"/>
+      <c r="C78" s="40" t="n"/>
+      <c r="D78" s="40" t="n"/>
+      <c r="E78" s="40" t="n"/>
+      <c r="F78" s="40" t="n"/>
       <c r="G78" s="57" t="n"/>
       <c r="H78" s="57" t="n"/>
       <c r="I78" s="30" t="n"/>
@@ -14578,9 +14619,9 @@
         </is>
       </c>
       <c r="C83" s="40" t="n"/>
-      <c r="D83" s="49" t="n"/>
-      <c r="E83" s="49" t="n"/>
-      <c r="F83" s="49" t="n"/>
+      <c r="D83" s="40" t="n"/>
+      <c r="E83" s="40" t="n"/>
+      <c r="F83" s="40" t="n"/>
       <c r="G83" s="57" t="n"/>
       <c r="H83" s="57" t="n"/>
       <c r="I83" s="30" t="n"/>
@@ -14593,10 +14634,10 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="53" t="n"/>
-      <c r="D84" s="53" t="n"/>
-      <c r="E84" s="53" t="n"/>
-      <c r="F84" s="53" t="n"/>
+      <c r="C84" s="40" t="n"/>
+      <c r="D84" s="40" t="n"/>
+      <c r="E84" s="40" t="n"/>
+      <c r="F84" s="40" t="n"/>
       <c r="G84" s="57" t="n"/>
       <c r="H84" s="57" t="n"/>
       <c r="I84" s="30" t="n"/>
@@ -14641,7 +14682,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F87" s="72" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -14657,7 +14698,7 @@
       <c r="C88" s="71" t="n"/>
       <c r="D88" s="71" t="n"/>
       <c r="E88" s="71" t="n"/>
-      <c r="F88" s="70" t="n"/>
+      <c r="F88" s="71" t="n"/>
       <c r="G88" s="35" t="n"/>
       <c r="H88" s="35" t="n"/>
       <c r="I88" s="30" t="n"/>
@@ -14673,7 +14714,7 @@
       <c r="C89" s="40" t="n"/>
       <c r="D89" s="40" t="n"/>
       <c r="E89" s="40" t="n"/>
-      <c r="F89" s="45" t="n"/>
+      <c r="F89" s="40" t="n"/>
       <c r="G89" s="35" t="n"/>
       <c r="H89" s="35" t="n"/>
       <c r="I89" s="30" t="n"/>
@@ -14686,10 +14727,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="45" t="n"/>
-      <c r="D90" s="45" t="n"/>
-      <c r="E90" s="45" t="n"/>
-      <c r="F90" s="45" t="n"/>
+      <c r="C90" s="40" t="n"/>
+      <c r="D90" s="40" t="n"/>
+      <c r="E90" s="40" t="n"/>
+      <c r="F90" s="40" t="n"/>
       <c r="G90" s="35" t="n"/>
       <c r="H90" s="35" t="n"/>
       <c r="I90" s="30" t="n"/>
@@ -14766,10 +14807,10 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="49" t="n"/>
-      <c r="D95" s="49" t="n"/>
-      <c r="E95" s="49" t="n"/>
-      <c r="F95" s="49" t="n"/>
+      <c r="C95" s="40" t="n"/>
+      <c r="D95" s="40" t="n"/>
+      <c r="E95" s="40" t="n"/>
+      <c r="F95" s="40" t="n"/>
       <c r="G95" s="35" t="n"/>
       <c r="H95" s="35" t="n"/>
       <c r="I95" s="30" t="n"/>
@@ -14782,10 +14823,10 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="53" t="n"/>
-      <c r="D96" s="53" t="n"/>
-      <c r="E96" s="53" t="n"/>
-      <c r="F96" s="53" t="n"/>
+      <c r="C96" s="40" t="n"/>
+      <c r="D96" s="40" t="n"/>
+      <c r="E96" s="40" t="n"/>
+      <c r="F96" s="40" t="n"/>
       <c r="G96" s="35" t="n"/>
       <c r="H96" s="35" t="n"/>
       <c r="I96" s="30" t="n"/>
@@ -14814,9 +14855,9 @@
     <mergeCell ref="E87:E88"/>
     <mergeCell ref="D75:D76"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="F75:F76"/>
+    <mergeCell ref="B86:F86"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="D87:D88"/>
@@ -14858,11 +14899,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="B1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.12844036697248" customWidth="1" style="24" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="25"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
+    <col width="13" customWidth="1" style="24" min="4" max="4"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="13" customWidth="1" style="24" min="6" max="6"/>
     <col width="9.12844036697248" customWidth="1" style="24" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -14890,17 +14935,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F3" s="72" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -14914,9 +14959,9 @@
     <row r="4" ht="15" customHeight="1" s="24">
       <c r="B4" s="69" t="n"/>
       <c r="C4" s="71" t="n"/>
-      <c r="D4" s="70" t="n"/>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="70" t="n"/>
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
       <c r="G4" s="35" t="n"/>
       <c r="H4" s="35" t="n"/>
       <c r="I4" s="30" t="n"/>
@@ -14945,10 +14990,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="40" t="n"/>
       <c r="G6" s="57" t="n"/>
       <c r="H6" s="57" t="n"/>
       <c r="I6" s="30" t="n"/>
@@ -15026,9 +15071,9 @@
         </is>
       </c>
       <c r="C11" s="40" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="49" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
       <c r="G11" s="57" t="n"/>
       <c r="H11" s="57" t="n"/>
       <c r="I11" s="30" t="n"/>
@@ -15041,10 +15086,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="53" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
       <c r="G12" s="57" t="n"/>
       <c r="H12" s="57" t="n"/>
       <c r="I12" s="30" t="n"/>
@@ -15089,7 +15134,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F15" s="72" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -15105,7 +15150,7 @@
       <c r="C16" s="71" t="n"/>
       <c r="D16" s="71" t="n"/>
       <c r="E16" s="71" t="n"/>
-      <c r="F16" s="70" t="n"/>
+      <c r="F16" s="71" t="n"/>
       <c r="G16" s="35" t="n"/>
       <c r="H16" s="35" t="n"/>
       <c r="I16" s="30" t="n"/>
@@ -15121,7 +15166,7 @@
       <c r="C17" s="40" t="n"/>
       <c r="D17" s="40" t="n"/>
       <c r="E17" s="40" t="n"/>
-      <c r="F17" s="45" t="n"/>
+      <c r="F17" s="40" t="n"/>
       <c r="G17" s="35" t="n"/>
       <c r="H17" s="35" t="n"/>
       <c r="I17" s="30" t="n"/>
@@ -15134,10 +15179,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="45" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
       <c r="G18" s="35" t="n"/>
       <c r="H18" s="35" t="n"/>
       <c r="I18" s="30" t="n"/>
@@ -15214,10 +15259,10 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="49" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
       <c r="G23" s="35" t="n"/>
       <c r="H23" s="35" t="n"/>
       <c r="I23" s="30" t="n"/>
@@ -15230,10 +15275,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="40" t="n"/>
       <c r="G24" s="35" t="n"/>
       <c r="H24" s="35" t="n"/>
       <c r="I24" s="30" t="n"/>
@@ -15268,17 +15313,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D27" s="72" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E27" s="72" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F27" s="72" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -15292,9 +15337,9 @@
     <row r="28" ht="15" customHeight="1" s="24">
       <c r="B28" s="69" t="n"/>
       <c r="C28" s="71" t="n"/>
-      <c r="D28" s="70" t="n"/>
-      <c r="E28" s="70" t="n"/>
-      <c r="F28" s="70" t="n"/>
+      <c r="D28" s="71" t="n"/>
+      <c r="E28" s="71" t="n"/>
+      <c r="F28" s="71" t="n"/>
       <c r="G28" s="35" t="n"/>
       <c r="H28" s="35" t="n"/>
       <c r="I28" s="30" t="n"/>
@@ -15323,10 +15368,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
+      <c r="C30" s="40" t="n"/>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="40" t="n"/>
       <c r="G30" s="57" t="n"/>
       <c r="H30" s="57" t="n"/>
       <c r="I30" s="30" t="n"/>
@@ -15404,9 +15449,9 @@
         </is>
       </c>
       <c r="C35" s="40" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="40" t="n"/>
+      <c r="F35" s="40" t="n"/>
       <c r="G35" s="57" t="n"/>
       <c r="H35" s="57" t="n"/>
       <c r="I35" s="30" t="n"/>
@@ -15419,10 +15464,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
-      <c r="E36" s="53" t="n"/>
-      <c r="F36" s="53" t="n"/>
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
       <c r="G36" s="57" t="n"/>
       <c r="H36" s="57" t="n"/>
       <c r="I36" s="30" t="n"/>
@@ -15467,7 +15512,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F39" s="72" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -15483,7 +15528,7 @@
       <c r="C40" s="71" t="n"/>
       <c r="D40" s="71" t="n"/>
       <c r="E40" s="71" t="n"/>
-      <c r="F40" s="70" t="n"/>
+      <c r="F40" s="71" t="n"/>
       <c r="G40" s="35" t="n"/>
       <c r="H40" s="35" t="n"/>
       <c r="I40" s="30" t="n"/>
@@ -15499,7 +15544,7 @@
       <c r="C41" s="40" t="n"/>
       <c r="D41" s="40" t="n"/>
       <c r="E41" s="40" t="n"/>
-      <c r="F41" s="45" t="n"/>
+      <c r="F41" s="40" t="n"/>
       <c r="G41" s="35" t="n"/>
       <c r="H41" s="35" t="n"/>
       <c r="I41" s="30" t="n"/>
@@ -15512,10 +15557,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="45" t="n"/>
-      <c r="D42" s="45" t="n"/>
-      <c r="E42" s="45" t="n"/>
-      <c r="F42" s="45" t="n"/>
+      <c r="C42" s="40" t="n"/>
+      <c r="D42" s="40" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
       <c r="G42" s="35" t="n"/>
       <c r="H42" s="35" t="n"/>
       <c r="I42" s="30" t="n"/>
@@ -15592,10 +15637,10 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="49" t="n"/>
-      <c r="D47" s="49" t="n"/>
-      <c r="E47" s="49" t="n"/>
-      <c r="F47" s="49" t="n"/>
+      <c r="C47" s="40" t="n"/>
+      <c r="D47" s="40" t="n"/>
+      <c r="E47" s="40" t="n"/>
+      <c r="F47" s="40" t="n"/>
       <c r="G47" s="35" t="n"/>
       <c r="H47" s="35" t="n"/>
       <c r="I47" s="30" t="n"/>
@@ -15608,10 +15653,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
-      <c r="E48" s="53" t="n"/>
-      <c r="F48" s="53" t="n"/>
+      <c r="C48" s="40" t="n"/>
+      <c r="D48" s="40" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
       <c r="G48" s="35" t="n"/>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="30" t="n"/>
@@ -15646,17 +15691,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D51" s="72" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E51" s="72" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F51" s="72" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -15670,9 +15715,9 @@
     <row r="52" ht="15" customHeight="1" s="24">
       <c r="B52" s="69" t="n"/>
       <c r="C52" s="71" t="n"/>
-      <c r="D52" s="70" t="n"/>
-      <c r="E52" s="70" t="n"/>
-      <c r="F52" s="70" t="n"/>
+      <c r="D52" s="71" t="n"/>
+      <c r="E52" s="71" t="n"/>
+      <c r="F52" s="71" t="n"/>
       <c r="G52" s="35" t="n"/>
       <c r="H52" s="35" t="n"/>
       <c r="I52" s="30" t="n"/>
@@ -15701,10 +15746,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="45" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="45" t="n"/>
-      <c r="F54" s="45" t="n"/>
+      <c r="C54" s="40" t="n"/>
+      <c r="D54" s="40" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
       <c r="G54" s="57" t="n"/>
       <c r="H54" s="57" t="n"/>
       <c r="I54" s="30" t="n"/>
@@ -15760,15 +15805,15 @@
       <c r="K57" s="30" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="40" t="n"/>
-      <c r="D58" s="40" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
+      <c r="C58" s="74" t="n"/>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="74" t="n"/>
       <c r="G58" s="57" t="n"/>
       <c r="H58" s="57" t="n"/>
       <c r="I58" s="30" t="n"/>
@@ -15782,9 +15827,9 @@
         </is>
       </c>
       <c r="C59" s="40" t="n"/>
-      <c r="D59" s="49" t="n"/>
-      <c r="E59" s="49" t="n"/>
-      <c r="F59" s="49" t="n"/>
+      <c r="D59" s="40" t="n"/>
+      <c r="E59" s="40" t="n"/>
+      <c r="F59" s="40" t="n"/>
       <c r="G59" s="57" t="n"/>
       <c r="H59" s="57" t="n"/>
       <c r="I59" s="30" t="n"/>
@@ -15797,10 +15842,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
+      <c r="C60" s="40" t="n"/>
+      <c r="D60" s="40" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
       <c r="G60" s="57" t="n"/>
       <c r="H60" s="57" t="n"/>
       <c r="I60" s="30" t="n"/>
@@ -15845,7 +15890,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F63" s="72" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -15861,7 +15906,7 @@
       <c r="C64" s="71" t="n"/>
       <c r="D64" s="71" t="n"/>
       <c r="E64" s="71" t="n"/>
-      <c r="F64" s="70" t="n"/>
+      <c r="F64" s="71" t="n"/>
       <c r="G64" s="35" t="n"/>
       <c r="H64" s="35" t="n"/>
       <c r="I64" s="30" t="n"/>
@@ -15877,7 +15922,7 @@
       <c r="C65" s="40" t="n"/>
       <c r="D65" s="40" t="n"/>
       <c r="E65" s="40" t="n"/>
-      <c r="F65" s="45" t="n"/>
+      <c r="F65" s="40" t="n"/>
       <c r="G65" s="35" t="n"/>
       <c r="H65" s="35" t="n"/>
       <c r="I65" s="30" t="n"/>
@@ -15890,10 +15935,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="45" t="n"/>
-      <c r="D66" s="45" t="n"/>
-      <c r="E66" s="45" t="n"/>
-      <c r="F66" s="45" t="n"/>
+      <c r="C66" s="40" t="n"/>
+      <c r="D66" s="40" t="n"/>
+      <c r="E66" s="40" t="n"/>
+      <c r="F66" s="40" t="n"/>
       <c r="G66" s="35" t="n"/>
       <c r="H66" s="35" t="n"/>
       <c r="I66" s="30" t="n"/>
@@ -15949,15 +15994,15 @@
       <c r="K69" s="30" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="40" t="n"/>
-      <c r="D70" s="40" t="n"/>
-      <c r="E70" s="40" t="n"/>
-      <c r="F70" s="40" t="n"/>
+      <c r="C70" s="74" t="n"/>
+      <c r="D70" s="74" t="n"/>
+      <c r="E70" s="74" t="n"/>
+      <c r="F70" s="74" t="n"/>
       <c r="G70" s="35" t="n"/>
       <c r="H70" s="35" t="n"/>
       <c r="I70" s="30" t="n"/>
@@ -15970,10 +16015,10 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="49" t="n"/>
-      <c r="D71" s="49" t="n"/>
-      <c r="E71" s="49" t="n"/>
-      <c r="F71" s="49" t="n"/>
+      <c r="C71" s="40" t="n"/>
+      <c r="D71" s="40" t="n"/>
+      <c r="E71" s="40" t="n"/>
+      <c r="F71" s="40" t="n"/>
       <c r="G71" s="35" t="n"/>
       <c r="H71" s="35" t="n"/>
       <c r="I71" s="30" t="n"/>
@@ -15986,10 +16031,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="53" t="n"/>
-      <c r="D72" s="53" t="n"/>
-      <c r="E72" s="53" t="n"/>
-      <c r="F72" s="53" t="n"/>
+      <c r="C72" s="40" t="n"/>
+      <c r="D72" s="40" t="n"/>
+      <c r="E72" s="40" t="n"/>
+      <c r="F72" s="40" t="n"/>
       <c r="G72" s="35" t="n"/>
       <c r="H72" s="35" t="n"/>
       <c r="I72" s="30" t="n"/>
@@ -16024,17 +16069,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D75" s="72" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E75" s="72" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F75" s="72" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -16048,9 +16093,9 @@
     <row r="76" ht="15" customHeight="1" s="24">
       <c r="B76" s="69" t="n"/>
       <c r="C76" s="71" t="n"/>
-      <c r="D76" s="70" t="n"/>
-      <c r="E76" s="70" t="n"/>
-      <c r="F76" s="70" t="n"/>
+      <c r="D76" s="71" t="n"/>
+      <c r="E76" s="71" t="n"/>
+      <c r="F76" s="71" t="n"/>
       <c r="G76" s="35" t="n"/>
       <c r="H76" s="35" t="n"/>
       <c r="I76" s="30" t="n"/>
@@ -16079,10 +16124,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="45" t="n"/>
-      <c r="D78" s="45" t="n"/>
-      <c r="E78" s="45" t="n"/>
-      <c r="F78" s="45" t="n"/>
+      <c r="C78" s="40" t="n"/>
+      <c r="D78" s="40" t="n"/>
+      <c r="E78" s="40" t="n"/>
+      <c r="F78" s="40" t="n"/>
       <c r="G78" s="57" t="n"/>
       <c r="H78" s="57" t="n"/>
       <c r="I78" s="30" t="n"/>
@@ -16160,9 +16205,9 @@
         </is>
       </c>
       <c r="C83" s="40" t="n"/>
-      <c r="D83" s="49" t="n"/>
-      <c r="E83" s="49" t="n"/>
-      <c r="F83" s="49" t="n"/>
+      <c r="D83" s="40" t="n"/>
+      <c r="E83" s="40" t="n"/>
+      <c r="F83" s="40" t="n"/>
       <c r="G83" s="57" t="n"/>
       <c r="H83" s="57" t="n"/>
       <c r="I83" s="30" t="n"/>
@@ -16175,10 +16220,10 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="53" t="n"/>
-      <c r="D84" s="53" t="n"/>
-      <c r="E84" s="53" t="n"/>
-      <c r="F84" s="53" t="n"/>
+      <c r="C84" s="40" t="n"/>
+      <c r="D84" s="40" t="n"/>
+      <c r="E84" s="40" t="n"/>
+      <c r="F84" s="40" t="n"/>
       <c r="G84" s="57" t="n"/>
       <c r="H84" s="57" t="n"/>
       <c r="I84" s="30" t="n"/>
@@ -16223,7 +16268,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F87" s="72" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -16239,7 +16284,7 @@
       <c r="C88" s="71" t="n"/>
       <c r="D88" s="71" t="n"/>
       <c r="E88" s="71" t="n"/>
-      <c r="F88" s="70" t="n"/>
+      <c r="F88" s="71" t="n"/>
       <c r="G88" s="35" t="n"/>
       <c r="H88" s="35" t="n"/>
       <c r="I88" s="30" t="n"/>
@@ -16255,7 +16300,7 @@
       <c r="C89" s="40" t="n"/>
       <c r="D89" s="40" t="n"/>
       <c r="E89" s="40" t="n"/>
-      <c r="F89" s="45" t="n"/>
+      <c r="F89" s="40" t="n"/>
       <c r="G89" s="35" t="n"/>
       <c r="H89" s="35" t="n"/>
       <c r="I89" s="30" t="n"/>
@@ -16268,10 +16313,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="45" t="n"/>
-      <c r="D90" s="45" t="n"/>
-      <c r="E90" s="45" t="n"/>
-      <c r="F90" s="45" t="n"/>
+      <c r="C90" s="40" t="n"/>
+      <c r="D90" s="40" t="n"/>
+      <c r="E90" s="40" t="n"/>
+      <c r="F90" s="40" t="n"/>
       <c r="G90" s="35" t="n"/>
       <c r="H90" s="35" t="n"/>
       <c r="I90" s="30" t="n"/>
@@ -16348,10 +16393,10 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="49" t="n"/>
-      <c r="D95" s="49" t="n"/>
-      <c r="E95" s="49" t="n"/>
-      <c r="F95" s="49" t="n"/>
+      <c r="C95" s="40" t="n"/>
+      <c r="D95" s="40" t="n"/>
+      <c r="E95" s="40" t="n"/>
+      <c r="F95" s="40" t="n"/>
       <c r="G95" s="35" t="n"/>
       <c r="H95" s="35" t="n"/>
       <c r="I95" s="30" t="n"/>
@@ -16364,10 +16409,10 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="53" t="n"/>
-      <c r="D96" s="53" t="n"/>
-      <c r="E96" s="53" t="n"/>
-      <c r="F96" s="53" t="n"/>
+      <c r="C96" s="40" t="n"/>
+      <c r="D96" s="40" t="n"/>
+      <c r="E96" s="40" t="n"/>
+      <c r="F96" s="40" t="n"/>
       <c r="G96" s="35" t="n"/>
       <c r="H96" s="35" t="n"/>
       <c r="I96" s="30" t="n"/>
@@ -16396,9 +16441,9 @@
     <mergeCell ref="E87:E88"/>
     <mergeCell ref="D75:D76"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="F75:F76"/>
+    <mergeCell ref="B86:F86"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="D87:D88"/>
@@ -16440,11 +16485,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="B1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12844036697248" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.12844036697248" customWidth="1" style="24" min="1" max="1"/>
     <col width="16.6238532110092" customWidth="1" style="3" min="2" max="25"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
+    <col width="13" customWidth="1" style="24" min="4" max="4"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="13" customWidth="1" style="24" min="6" max="6"/>
     <col width="9.12844036697248" customWidth="1" style="24" min="26" max="16384"/>
   </cols>
   <sheetData>
@@ -16472,17 +16521,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D3" s="72" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E3" s="72" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F3" s="72" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -16496,9 +16545,9 @@
     <row r="4" ht="15" customHeight="1" s="24">
       <c r="B4" s="69" t="n"/>
       <c r="C4" s="71" t="n"/>
-      <c r="D4" s="70" t="n"/>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="70" t="n"/>
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
       <c r="G4" s="35" t="n"/>
       <c r="H4" s="35" t="n"/>
       <c r="I4" s="30" t="n"/>
@@ -16527,10 +16576,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
-      <c r="D6" s="45" t="n"/>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="40" t="n"/>
       <c r="G6" s="57" t="n"/>
       <c r="H6" s="57" t="n"/>
       <c r="I6" s="30" t="n"/>
@@ -16608,9 +16657,9 @@
         </is>
       </c>
       <c r="C11" s="40" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="49" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
       <c r="G11" s="57" t="n"/>
       <c r="H11" s="57" t="n"/>
       <c r="I11" s="30" t="n"/>
@@ -16623,10 +16672,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="53" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
       <c r="G12" s="57" t="n"/>
       <c r="H12" s="57" t="n"/>
       <c r="I12" s="30" t="n"/>
@@ -16671,7 +16720,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F15" s="72" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -16687,7 +16736,7 @@
       <c r="C16" s="71" t="n"/>
       <c r="D16" s="71" t="n"/>
       <c r="E16" s="71" t="n"/>
-      <c r="F16" s="70" t="n"/>
+      <c r="F16" s="71" t="n"/>
       <c r="G16" s="35" t="n"/>
       <c r="H16" s="35" t="n"/>
       <c r="I16" s="30" t="n"/>
@@ -16703,7 +16752,7 @@
       <c r="C17" s="40" t="n"/>
       <c r="D17" s="40" t="n"/>
       <c r="E17" s="40" t="n"/>
-      <c r="F17" s="45" t="n"/>
+      <c r="F17" s="40" t="n"/>
       <c r="G17" s="35" t="n"/>
       <c r="H17" s="35" t="n"/>
       <c r="I17" s="30" t="n"/>
@@ -16716,10 +16765,10 @@
           <t>Nov_2016</t>
         </is>
       </c>
-      <c r="C18" s="45" t="n"/>
-      <c r="D18" s="45" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="45" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
       <c r="G18" s="35" t="n"/>
       <c r="H18" s="35" t="n"/>
       <c r="I18" s="30" t="n"/>
@@ -16796,10 +16845,10 @@
           <t>Nov_2021</t>
         </is>
       </c>
-      <c r="C23" s="49" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="49" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
       <c r="G23" s="35" t="n"/>
       <c r="H23" s="35" t="n"/>
       <c r="I23" s="30" t="n"/>
@@ -16812,10 +16861,10 @@
           <t>Nov_2022</t>
         </is>
       </c>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
-      <c r="E24" s="53" t="n"/>
-      <c r="F24" s="53" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="40" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="F24" s="40" t="n"/>
       <c r="G24" s="35" t="n"/>
       <c r="H24" s="35" t="n"/>
       <c r="I24" s="30" t="n"/>
@@ -16850,17 +16899,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D27" s="72" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E27" s="72" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F27" s="72" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -16874,9 +16923,9 @@
     <row r="28" ht="15" customHeight="1" s="24">
       <c r="B28" s="69" t="n"/>
       <c r="C28" s="71" t="n"/>
-      <c r="D28" s="70" t="n"/>
-      <c r="E28" s="70" t="n"/>
-      <c r="F28" s="70" t="n"/>
+      <c r="D28" s="71" t="n"/>
+      <c r="E28" s="71" t="n"/>
+      <c r="F28" s="71" t="n"/>
       <c r="G28" s="35" t="n"/>
       <c r="H28" s="35" t="n"/>
       <c r="I28" s="30" t="n"/>
@@ -16905,10 +16954,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C30" s="45" t="n"/>
-      <c r="D30" s="45" t="n"/>
-      <c r="E30" s="45" t="n"/>
-      <c r="F30" s="45" t="n"/>
+      <c r="C30" s="40" t="n"/>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="40" t="n"/>
       <c r="G30" s="57" t="n"/>
       <c r="H30" s="57" t="n"/>
       <c r="I30" s="30" t="n"/>
@@ -16986,9 +17035,9 @@
         </is>
       </c>
       <c r="C35" s="40" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="40" t="n"/>
+      <c r="F35" s="40" t="n"/>
       <c r="G35" s="57" t="n"/>
       <c r="H35" s="57" t="n"/>
       <c r="I35" s="30" t="n"/>
@@ -17001,10 +17050,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
-      <c r="E36" s="53" t="n"/>
-      <c r="F36" s="53" t="n"/>
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
       <c r="G36" s="57" t="n"/>
       <c r="H36" s="57" t="n"/>
       <c r="I36" s="30" t="n"/>
@@ -17049,7 +17098,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F39" s="72" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -17065,7 +17114,7 @@
       <c r="C40" s="71" t="n"/>
       <c r="D40" s="71" t="n"/>
       <c r="E40" s="71" t="n"/>
-      <c r="F40" s="70" t="n"/>
+      <c r="F40" s="71" t="n"/>
       <c r="G40" s="35" t="n"/>
       <c r="H40" s="35" t="n"/>
       <c r="I40" s="30" t="n"/>
@@ -17081,7 +17130,7 @@
       <c r="C41" s="40" t="n"/>
       <c r="D41" s="40" t="n"/>
       <c r="E41" s="40" t="n"/>
-      <c r="F41" s="45" t="n"/>
+      <c r="F41" s="40" t="n"/>
       <c r="G41" s="35" t="n"/>
       <c r="H41" s="35" t="n"/>
       <c r="I41" s="30" t="n"/>
@@ -17094,10 +17143,10 @@
           <t>Sept_2016</t>
         </is>
       </c>
-      <c r="C42" s="45" t="n"/>
-      <c r="D42" s="45" t="n"/>
-      <c r="E42" s="45" t="n"/>
-      <c r="F42" s="45" t="n"/>
+      <c r="C42" s="40" t="n"/>
+      <c r="D42" s="40" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
       <c r="G42" s="35" t="n"/>
       <c r="H42" s="35" t="n"/>
       <c r="I42" s="30" t="n"/>
@@ -17174,10 +17223,10 @@
           <t>Sept_2021</t>
         </is>
       </c>
-      <c r="C47" s="49" t="n"/>
-      <c r="D47" s="49" t="n"/>
-      <c r="E47" s="49" t="n"/>
-      <c r="F47" s="49" t="n"/>
+      <c r="C47" s="40" t="n"/>
+      <c r="D47" s="40" t="n"/>
+      <c r="E47" s="40" t="n"/>
+      <c r="F47" s="40" t="n"/>
       <c r="G47" s="35" t="n"/>
       <c r="H47" s="35" t="n"/>
       <c r="I47" s="30" t="n"/>
@@ -17190,10 +17239,10 @@
           <t>Sept_2022</t>
         </is>
       </c>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
-      <c r="E48" s="53" t="n"/>
-      <c r="F48" s="53" t="n"/>
+      <c r="C48" s="40" t="n"/>
+      <c r="D48" s="40" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
       <c r="G48" s="35" t="n"/>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="30" t="n"/>
@@ -17228,17 +17277,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D51" s="72" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E51" s="72" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F51" s="72" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -17252,9 +17301,9 @@
     <row r="52" ht="15" customHeight="1" s="24">
       <c r="B52" s="69" t="n"/>
       <c r="C52" s="71" t="n"/>
-      <c r="D52" s="70" t="n"/>
-      <c r="E52" s="70" t="n"/>
-      <c r="F52" s="70" t="n"/>
+      <c r="D52" s="71" t="n"/>
+      <c r="E52" s="71" t="n"/>
+      <c r="F52" s="71" t="n"/>
       <c r="G52" s="35" t="n"/>
       <c r="H52" s="35" t="n"/>
       <c r="I52" s="30" t="n"/>
@@ -17283,10 +17332,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C54" s="45" t="n"/>
-      <c r="D54" s="45" t="n"/>
-      <c r="E54" s="45" t="n"/>
-      <c r="F54" s="45" t="n"/>
+      <c r="C54" s="40" t="n"/>
+      <c r="D54" s="40" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
       <c r="G54" s="57" t="n"/>
       <c r="H54" s="57" t="n"/>
       <c r="I54" s="30" t="n"/>
@@ -17342,15 +17391,15 @@
       <c r="K57" s="30" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C58" s="40" t="n"/>
-      <c r="D58" s="40" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
+      <c r="C58" s="74" t="n"/>
+      <c r="D58" s="74" t="n"/>
+      <c r="E58" s="74" t="n"/>
+      <c r="F58" s="74" t="n"/>
       <c r="G58" s="57" t="n"/>
       <c r="H58" s="57" t="n"/>
       <c r="I58" s="30" t="n"/>
@@ -17364,9 +17413,9 @@
         </is>
       </c>
       <c r="C59" s="40" t="n"/>
-      <c r="D59" s="49" t="n"/>
-      <c r="E59" s="49" t="n"/>
-      <c r="F59" s="49" t="n"/>
+      <c r="D59" s="40" t="n"/>
+      <c r="E59" s="40" t="n"/>
+      <c r="F59" s="40" t="n"/>
       <c r="G59" s="57" t="n"/>
       <c r="H59" s="57" t="n"/>
       <c r="I59" s="30" t="n"/>
@@ -17379,10 +17428,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
+      <c r="C60" s="40" t="n"/>
+      <c r="D60" s="40" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
       <c r="G60" s="57" t="n"/>
       <c r="H60" s="57" t="n"/>
       <c r="I60" s="30" t="n"/>
@@ -17427,7 +17476,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F63" s="72" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -17443,7 +17492,7 @@
       <c r="C64" s="71" t="n"/>
       <c r="D64" s="71" t="n"/>
       <c r="E64" s="71" t="n"/>
-      <c r="F64" s="70" t="n"/>
+      <c r="F64" s="71" t="n"/>
       <c r="G64" s="35" t="n"/>
       <c r="H64" s="35" t="n"/>
       <c r="I64" s="30" t="n"/>
@@ -17459,7 +17508,7 @@
       <c r="C65" s="40" t="n"/>
       <c r="D65" s="40" t="n"/>
       <c r="E65" s="40" t="n"/>
-      <c r="F65" s="45" t="n"/>
+      <c r="F65" s="40" t="n"/>
       <c r="G65" s="35" t="n"/>
       <c r="H65" s="35" t="n"/>
       <c r="I65" s="30" t="n"/>
@@ -17472,10 +17521,10 @@
           <t>May/Jun_2016</t>
         </is>
       </c>
-      <c r="C66" s="45" t="n"/>
-      <c r="D66" s="45" t="n"/>
-      <c r="E66" s="45" t="n"/>
-      <c r="F66" s="45" t="n"/>
+      <c r="C66" s="40" t="n"/>
+      <c r="D66" s="40" t="n"/>
+      <c r="E66" s="40" t="n"/>
+      <c r="F66" s="40" t="n"/>
       <c r="G66" s="35" t="n"/>
       <c r="H66" s="35" t="n"/>
       <c r="I66" s="30" t="n"/>
@@ -17531,15 +17580,15 @@
       <c r="K69" s="30" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="73" t="inlineStr">
         <is>
           <t>May/Jun_2020</t>
         </is>
       </c>
-      <c r="C70" s="40" t="n"/>
-      <c r="D70" s="40" t="n"/>
-      <c r="E70" s="40" t="n"/>
-      <c r="F70" s="40" t="n"/>
+      <c r="C70" s="74" t="n"/>
+      <c r="D70" s="74" t="n"/>
+      <c r="E70" s="74" t="n"/>
+      <c r="F70" s="74" t="n"/>
       <c r="G70" s="35" t="n"/>
       <c r="H70" s="35" t="n"/>
       <c r="I70" s="30" t="n"/>
@@ -17552,10 +17601,10 @@
           <t>May/Jun_2021</t>
         </is>
       </c>
-      <c r="C71" s="49" t="n"/>
-      <c r="D71" s="49" t="n"/>
-      <c r="E71" s="49" t="n"/>
-      <c r="F71" s="49" t="n"/>
+      <c r="C71" s="40" t="n"/>
+      <c r="D71" s="40" t="n"/>
+      <c r="E71" s="40" t="n"/>
+      <c r="F71" s="40" t="n"/>
       <c r="G71" s="35" t="n"/>
       <c r="H71" s="35" t="n"/>
       <c r="I71" s="30" t="n"/>
@@ -17568,10 +17617,10 @@
           <t>May/Jun_2022</t>
         </is>
       </c>
-      <c r="C72" s="53" t="n"/>
-      <c r="D72" s="53" t="n"/>
-      <c r="E72" s="53" t="n"/>
-      <c r="F72" s="53" t="n"/>
+      <c r="C72" s="40" t="n"/>
+      <c r="D72" s="40" t="n"/>
+      <c r="E72" s="40" t="n"/>
+      <c r="F72" s="40" t="n"/>
       <c r="G72" s="35" t="n"/>
       <c r="H72" s="35" t="n"/>
       <c r="I72" s="30" t="n"/>
@@ -17606,17 +17655,17 @@
           <t>Forces</t>
         </is>
       </c>
-      <c r="D75" s="72" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Electrostatics</t>
         </is>
       </c>
-      <c r="E75" s="72" t="inlineStr">
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>Magnetism</t>
         </is>
       </c>
-      <c r="F75" s="72" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>Electric Circuits</t>
         </is>
@@ -17630,9 +17679,9 @@
     <row r="76" ht="15" customHeight="1" s="24">
       <c r="B76" s="69" t="n"/>
       <c r="C76" s="71" t="n"/>
-      <c r="D76" s="70" t="n"/>
-      <c r="E76" s="70" t="n"/>
-      <c r="F76" s="70" t="n"/>
+      <c r="D76" s="71" t="n"/>
+      <c r="E76" s="71" t="n"/>
+      <c r="F76" s="71" t="n"/>
       <c r="G76" s="35" t="n"/>
       <c r="H76" s="35" t="n"/>
       <c r="I76" s="30" t="n"/>
@@ -17661,10 +17710,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C78" s="45" t="n"/>
-      <c r="D78" s="45" t="n"/>
-      <c r="E78" s="45" t="n"/>
-      <c r="F78" s="45" t="n"/>
+      <c r="C78" s="40" t="n"/>
+      <c r="D78" s="40" t="n"/>
+      <c r="E78" s="40" t="n"/>
+      <c r="F78" s="40" t="n"/>
       <c r="G78" s="57" t="n"/>
       <c r="H78" s="57" t="n"/>
       <c r="I78" s="30" t="n"/>
@@ -17742,9 +17791,9 @@
         </is>
       </c>
       <c r="C83" s="40" t="n"/>
-      <c r="D83" s="49" t="n"/>
-      <c r="E83" s="49" t="n"/>
-      <c r="F83" s="49" t="n"/>
+      <c r="D83" s="40" t="n"/>
+      <c r="E83" s="40" t="n"/>
+      <c r="F83" s="40" t="n"/>
       <c r="G83" s="57" t="n"/>
       <c r="H83" s="57" t="n"/>
       <c r="I83" s="30" t="n"/>
@@ -17757,10 +17806,10 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C84" s="53" t="n"/>
-      <c r="D84" s="53" t="n"/>
-      <c r="E84" s="53" t="n"/>
-      <c r="F84" s="53" t="n"/>
+      <c r="C84" s="40" t="n"/>
+      <c r="D84" s="40" t="n"/>
+      <c r="E84" s="40" t="n"/>
+      <c r="F84" s="40" t="n"/>
       <c r="G84" s="57" t="n"/>
       <c r="H84" s="57" t="n"/>
       <c r="I84" s="30" t="n"/>
@@ -17805,7 +17854,7 @@
           <t>Waves, Sound &amp; Light</t>
         </is>
       </c>
-      <c r="F87" s="72" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>Heat &amp; Thermodynamics</t>
         </is>
@@ -17821,7 +17870,7 @@
       <c r="C88" s="71" t="n"/>
       <c r="D88" s="71" t="n"/>
       <c r="E88" s="71" t="n"/>
-      <c r="F88" s="70" t="n"/>
+      <c r="F88" s="71" t="n"/>
       <c r="G88" s="35" t="n"/>
       <c r="H88" s="35" t="n"/>
       <c r="I88" s="30" t="n"/>
@@ -17837,7 +17886,7 @@
       <c r="C89" s="40" t="n"/>
       <c r="D89" s="40" t="n"/>
       <c r="E89" s="40" t="n"/>
-      <c r="F89" s="45" t="n"/>
+      <c r="F89" s="40" t="n"/>
       <c r="G89" s="35" t="n"/>
       <c r="H89" s="35" t="n"/>
       <c r="I89" s="30" t="n"/>
@@ -17850,10 +17899,10 @@
           <t>Feb/Mar_2016</t>
         </is>
       </c>
-      <c r="C90" s="45" t="n"/>
-      <c r="D90" s="45" t="n"/>
-      <c r="E90" s="45" t="n"/>
-      <c r="F90" s="45" t="n"/>
+      <c r="C90" s="40" t="n"/>
+      <c r="D90" s="40" t="n"/>
+      <c r="E90" s="40" t="n"/>
+      <c r="F90" s="40" t="n"/>
       <c r="G90" s="35" t="n"/>
       <c r="H90" s="35" t="n"/>
       <c r="I90" s="30" t="n"/>
@@ -17930,10 +17979,10 @@
           <t>Feb/Mar_2021</t>
         </is>
       </c>
-      <c r="C95" s="49" t="n"/>
-      <c r="D95" s="49" t="n"/>
-      <c r="E95" s="49" t="n"/>
-      <c r="F95" s="49" t="n"/>
+      <c r="C95" s="40" t="n"/>
+      <c r="D95" s="40" t="n"/>
+      <c r="E95" s="40" t="n"/>
+      <c r="F95" s="40" t="n"/>
       <c r="G95" s="35" t="n"/>
       <c r="H95" s="35" t="n"/>
       <c r="I95" s="30" t="n"/>
@@ -17946,17 +17995,16 @@
           <t>Feb/Mar_2022</t>
         </is>
       </c>
-      <c r="C96" s="53" t="n"/>
-      <c r="D96" s="53" t="n"/>
-      <c r="E96" s="53" t="n"/>
-      <c r="F96" s="53" t="n"/>
+      <c r="C96" s="40" t="n"/>
+      <c r="D96" s="40" t="n"/>
+      <c r="E96" s="40" t="n"/>
+      <c r="F96" s="40" t="n"/>
       <c r="G96" s="35" t="n"/>
       <c r="H96" s="35" t="n"/>
       <c r="I96" s="30" t="n"/>
       <c r="J96" s="30" t="n"/>
       <c r="K96" s="30" t="n"/>
     </row>
-    <row r="97"/>
   </sheetData>
   <mergeCells count="48">
     <mergeCell ref="F15:F16"/>
@@ -17974,9 +18022,9 @@
     <mergeCell ref="E87:E88"/>
     <mergeCell ref="D75:D76"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="F51:F52"/>
     <mergeCell ref="F75:F76"/>
+    <mergeCell ref="B86:F86"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="D87:D88"/>
